--- a/Expereiments/MessageFiltering.xlsx
+++ b/Expereiments/MessageFiltering.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="95">
   <si>
     <t>#</t>
   </si>
@@ -78,41 +78,239 @@
     <t xml:space="preserve"> FasText Embeddig</t>
   </si>
   <si>
-    <t xml:space="preserve"> FasText Embeddig For Named Entites</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> FasText Embeddig with weights</t>
-  </si>
-  <si>
     <t>Embedding Tweets with Fastext Model</t>
   </si>
   <si>
-    <t xml:space="preserve">Weighting the Embedding of the Named Entities </t>
-  </si>
-  <si>
-    <t>Embeding thhe Named Entities Only</t>
-  </si>
-  <si>
-    <t>Embedding Tweets with AraBert Nodel</t>
-  </si>
-  <si>
     <t xml:space="preserve"> AraBert Embeddig</t>
   </si>
   <si>
-    <t xml:space="preserve"> AraBert Embeddig with weights</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AraBert Embeddig   </t>
-  </si>
-  <si>
     <t>Naïve Baise</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> mBert Embeddig</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TF-IDF Embeddig</t>
+  </si>
+  <si>
+    <t>Embedding Tweets with AraBert Model</t>
+  </si>
+  <si>
+    <t>Embedding Tweets with mBert Model</t>
+  </si>
+  <si>
+    <t>Embedding Tweets with TF-IDF Model</t>
+  </si>
+  <si>
+    <t> 0.84</t>
+  </si>
+  <si>
+    <t> 0.82</t>
+  </si>
+  <si>
+    <t>0.86 </t>
+  </si>
+  <si>
+    <t>0.81 </t>
+  </si>
+  <si>
+    <t>0.77 </t>
+  </si>
+  <si>
+    <t>0.86  </t>
+  </si>
+  <si>
+    <t> 0.81</t>
+  </si>
+  <si>
+    <t>0.89 </t>
+  </si>
+  <si>
+    <t>0.87 </t>
+  </si>
+  <si>
+    <t>0.75 </t>
+  </si>
+  <si>
+    <t>0.84 </t>
+  </si>
+  <si>
+    <t>0.95 </t>
+  </si>
+  <si>
+    <t>0.91 </t>
+  </si>
+  <si>
+    <t>0.79 </t>
+  </si>
+  <si>
+    <t>0.76 </t>
+  </si>
+  <si>
+    <t>0.85 </t>
+  </si>
+  <si>
+    <t>0.88 </t>
+  </si>
+  <si>
+    <t>0.67 </t>
+  </si>
+  <si>
+    <t>0.68 </t>
+  </si>
+  <si>
+    <t> 0.86</t>
+  </si>
+  <si>
+    <t>0.82 </t>
+  </si>
+  <si>
+    <t>0.92 </t>
+  </si>
+  <si>
+    <t> 0.90</t>
+  </si>
+  <si>
+    <t> 0.85</t>
+  </si>
+  <si>
+    <t>086 </t>
+  </si>
+  <si>
+    <t> 0.91</t>
+  </si>
+  <si>
+    <t> 0.83</t>
+  </si>
+  <si>
+    <t>0.78 </t>
+  </si>
+  <si>
+    <t> 0.99</t>
+  </si>
+  <si>
+    <t>1.00 </t>
+  </si>
+  <si>
+    <t>0.99 </t>
+  </si>
+  <si>
+    <t> 0.87</t>
+  </si>
+  <si>
+    <t> 0.76</t>
+  </si>
+  <si>
+    <t>0.80 </t>
+  </si>
+  <si>
+    <t> 0.88</t>
+  </si>
+  <si>
+    <t> 0.73</t>
+  </si>
+  <si>
+    <t>0.74 </t>
+  </si>
+  <si>
+    <t>0.83 </t>
+  </si>
+  <si>
+    <t> 0.89</t>
+  </si>
+  <si>
+    <t>Exp. 2</t>
+  </si>
+  <si>
+    <t>Exp. 3</t>
+  </si>
+  <si>
+    <t>Exp. 4</t>
+  </si>
+  <si>
+    <t> 0.93</t>
+  </si>
+  <si>
+    <t> 0.80</t>
+  </si>
+  <si>
+    <t>0.97 </t>
+  </si>
+  <si>
+    <t>0.90 </t>
+  </si>
+  <si>
+    <t> 0.74</t>
+  </si>
+  <si>
+    <t>0.71 </t>
+  </si>
+  <si>
+    <t>0.70 </t>
+  </si>
+  <si>
+    <t> 0.78</t>
+  </si>
+  <si>
+    <t>0.73 </t>
+  </si>
+  <si>
+    <t>0.58 </t>
+  </si>
+  <si>
+    <t> 0.67</t>
+  </si>
+  <si>
+    <t>0.62 </t>
+  </si>
+  <si>
+    <t>0.56 </t>
+  </si>
+  <si>
+    <t>0.53 </t>
+  </si>
+  <si>
+    <t>0.93 </t>
+  </si>
+  <si>
+    <t>0.61 </t>
+  </si>
+  <si>
+    <t>0.69 </t>
+  </si>
+  <si>
+    <t>0.98 </t>
+  </si>
+  <si>
+    <t>0.60 </t>
+  </si>
+  <si>
+    <t>0.65 </t>
+  </si>
+  <si>
+    <t>0.55 </t>
+  </si>
+  <si>
+    <t>0.44 </t>
+  </si>
+  <si>
+    <t>Embedding Tweets with Fastext + NE Weight</t>
+  </si>
+  <si>
+    <t>Embedding Tweets with AraBert + NE Weight</t>
+  </si>
+  <si>
+    <t>Embedding Tweets with mBert + NE Weight</t>
+  </si>
+  <si>
+    <t>Embedding Tweets with TF-IDF + NE Weight</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,8 +339,48 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,8 +435,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4C6E7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -334,25 +584,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -366,7 +611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -376,12 +621,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -394,55 +633,96 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -492,7 +772,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -832,25 +1112,25 @@
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
       <c r="U2" s="3"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
@@ -869,25 +1149,25 @@
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
       <c r="U3" s="3"/>
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
@@ -906,23 +1186,23 @@
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="39"/>
-      <c r="S4" s="39"/>
-      <c r="T4" s="39"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="50"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="50"/>
       <c r="U4" s="3"/>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
@@ -944,30 +1224,30 @@
       <c r="D5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="33"/>
-      <c r="G5" s="34" t="s">
+      <c r="F5" s="44"/>
+      <c r="G5" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="40" t="s">
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="41"/>
-      <c r="M5" s="34" t="s">
+      <c r="L5" s="52"/>
+      <c r="M5" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="36"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
+      <c r="T5" s="47"/>
       <c r="U5" s="3"/>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
@@ -986,31 +1266,31 @@
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="48" t="s">
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="N6" s="49"/>
-      <c r="O6" s="48" t="s">
+      <c r="N6" s="60"/>
+      <c r="O6" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="48" t="s">
+      <c r="P6" s="60"/>
+      <c r="Q6" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="R6" s="49"/>
-      <c r="S6" s="48" t="s">
+      <c r="R6" s="60"/>
+      <c r="S6" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="T6" s="49"/>
+      <c r="T6" s="60"/>
       <c r="U6" s="3"/>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
@@ -1029,15 +1309,15 @@
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1080,31 +1360,47 @@
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="L8" s="28"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8" s="36"/>
+      <c r="M8" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="O8" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="P8" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="R8" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="T8" s="15" t="s">
+        <v>31</v>
+      </c>
       <c r="U8" s="3"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
@@ -1123,25 +1419,41 @@
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="L9" s="29"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L9" s="38"/>
+      <c r="M9" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="O9" s="16">
+        <v>0.93</v>
+      </c>
+      <c r="P9" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q9" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="R9" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="S9" s="16">
+        <v>0.81</v>
+      </c>
+      <c r="T9" s="16" t="s">
+        <v>36</v>
+      </c>
       <c r="U9" s="3"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
@@ -1160,25 +1472,41 @@
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="L10" s="28"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L10" s="36"/>
+      <c r="M10" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="P10" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="S10" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="T10" s="17" t="s">
+        <v>40</v>
+      </c>
       <c r="U10" s="3"/>
       <c r="V10" s="4"/>
       <c r="W10" s="4"/>
@@ -1197,25 +1525,41 @@
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="L11" s="30"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="39"/>
+      <c r="M11" s="16">
+        <v>0.73</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="O11" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="P11" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q11" s="16">
+        <v>0.78</v>
+      </c>
+      <c r="R11" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="S11" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="T11" s="16" t="s">
+        <v>45</v>
+      </c>
       <c r="U11" s="3"/>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
@@ -1234,29 +1578,41 @@
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="28" t="s">
+      <c r="D12" s="41"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="28"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="15">
+        <v>0.84</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="P12" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q12" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="R12" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S12" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="T12" s="15" t="s">
+        <v>41</v>
+      </c>
       <c r="U12" s="3"/>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
@@ -1275,25 +1631,45 @@
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="29"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="34"/>
+      <c r="G13" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L13" s="36"/>
+      <c r="M13" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="O13" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="P13" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q13" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="R13" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="S13" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="T13" s="17" t="s">
+        <v>40</v>
+      </c>
       <c r="U13" s="3"/>
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
@@ -1312,25 +1688,41 @@
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="28" t="s">
+      <c r="D14" s="41"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="L14" s="28"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="O14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="P14" s="16">
+        <v>0.82</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>0.91</v>
+      </c>
+      <c r="R14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="S14" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="T14" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="U14" s="3"/>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
@@ -1349,25 +1741,41 @@
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="L15" s="30"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" s="36"/>
+      <c r="M15" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="P15" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q15" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="R15" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="S15" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="T15" s="18" t="s">
+        <v>31</v>
+      </c>
       <c r="U15" s="3"/>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
@@ -1386,29 +1794,41 @@
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="L16" s="28"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="6"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="39"/>
+      <c r="M16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q16" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="R16" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="S16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="T16" s="16" t="s">
+        <v>63</v>
+      </c>
       <c r="U16" s="3"/>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
@@ -1427,25 +1847,41 @@
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="L17" s="29"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L17" s="36"/>
+      <c r="M17" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="O17" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="P17" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="Q17" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="R17" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="S17" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="T17" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="U17" s="3"/>
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
@@ -1464,25 +1900,45 @@
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="L18" s="28"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="34"/>
+      <c r="G18" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L18" s="36"/>
+      <c r="M18" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="N18" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="O18" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="P18" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q18" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="R18" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="S18" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="T18" s="18" t="s">
+        <v>41</v>
+      </c>
       <c r="U18" s="3"/>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
@@ -1501,25 +1957,41 @@
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="L19" s="30"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19" s="38"/>
+      <c r="M19" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="N19" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O19" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="P19" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q19" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="R19" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="S19" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="T19" s="29" t="s">
+        <v>60</v>
+      </c>
       <c r="U19" s="3"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
@@ -1538,31 +2010,41 @@
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="L20" s="28"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" s="36"/>
+      <c r="M20" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="N20" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O20" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="P20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="R20" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="S20" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="T20" s="15" t="s">
+        <v>31</v>
+      </c>
       <c r="U20" s="3"/>
       <c r="V20" s="4"/>
       <c r="W20" s="4"/>
@@ -1581,25 +2063,41 @@
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="L21" s="29"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="39"/>
+      <c r="M21" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="O21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="P21" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q21" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="R21" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="S21" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="T21" s="16" t="s">
+        <v>45</v>
+      </c>
       <c r="U21" s="3"/>
       <c r="V21" s="4"/>
       <c r="W21" s="4"/>
@@ -1618,25 +2116,41 @@
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="L22" s="28"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" s="36"/>
+      <c r="M22" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O22" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="P22" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q22" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="R22" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S22" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="T22" s="15" t="s">
+        <v>41</v>
+      </c>
       <c r="U22" s="3"/>
       <c r="V22" s="4"/>
       <c r="W22" s="4"/>
@@ -1655,25 +2169,45 @@
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="L23" s="30"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="13"/>
-      <c r="S23" s="13"/>
-      <c r="T23" s="13"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="34"/>
+      <c r="G23" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L23" s="36"/>
+      <c r="M23" s="18">
+        <v>0.99</v>
+      </c>
+      <c r="N23" s="18">
+        <v>0.78</v>
+      </c>
+      <c r="O23" s="18">
+        <v>0.99</v>
+      </c>
+      <c r="P23" s="18">
+        <v>0.82</v>
+      </c>
+      <c r="Q23" s="18">
+        <v>0.99</v>
+      </c>
+      <c r="R23" s="18">
+        <v>0.87</v>
+      </c>
+      <c r="S23" s="18">
+        <v>0.98</v>
+      </c>
+      <c r="T23" s="18">
+        <v>0.78</v>
+      </c>
       <c r="U23" s="3"/>
       <c r="V23" s="4"/>
       <c r="W23" s="4"/>
@@ -1692,29 +2226,41 @@
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="21"/>
-      <c r="G24" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="L24" s="28"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L24" s="38"/>
+      <c r="M24" s="16">
+        <v>0.84</v>
+      </c>
+      <c r="N24" s="16">
+        <v>0.81</v>
+      </c>
+      <c r="O24" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="P24" s="16">
+        <v>0.83</v>
+      </c>
+      <c r="Q24" s="16">
+        <v>0.89</v>
+      </c>
+      <c r="R24" s="16">
+        <v>0.9</v>
+      </c>
+      <c r="S24" s="16">
+        <v>0.82</v>
+      </c>
+      <c r="T24" s="19">
+        <v>0.78</v>
+      </c>
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
       <c r="W24" s="4"/>
@@ -1733,25 +2279,41 @@
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="29" t="s">
+      <c r="D25" s="41"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="L25" s="29"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
+      <c r="L25" s="36"/>
+      <c r="M25" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="N25" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="O25" s="15">
+        <v>0.93</v>
+      </c>
+      <c r="P25" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="Q25" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="R25" s="15">
+        <v>0.84</v>
+      </c>
+      <c r="S25" s="15">
+        <v>0.84</v>
+      </c>
+      <c r="T25" s="15">
+        <v>0.74</v>
+      </c>
       <c r="U25" s="3"/>
       <c r="V25" s="4"/>
       <c r="W25" s="4"/>
@@ -1770,25 +2332,41 @@
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="L26" s="28"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="6"/>
-      <c r="T26" s="6"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="39"/>
+      <c r="M26" s="16">
+        <v>0.69</v>
+      </c>
+      <c r="N26" s="16">
+        <v>0.74</v>
+      </c>
+      <c r="O26" s="16">
+        <v>0.67</v>
+      </c>
+      <c r="P26" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="Q26" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="R26" s="16">
+        <v>0.83</v>
+      </c>
+      <c r="S26" s="16">
+        <v>0.67</v>
+      </c>
+      <c r="T26" s="16">
+        <v>0.69</v>
+      </c>
       <c r="U26" s="3"/>
       <c r="V26" s="4"/>
       <c r="W26" s="4"/>
@@ -1807,25 +2385,41 @@
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="L27" s="30"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="13"/>
-      <c r="Q27" s="13"/>
-      <c r="R27" s="13"/>
-      <c r="S27" s="13"/>
-      <c r="T27" s="13"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L27" s="36"/>
+      <c r="M27" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="N27" s="15">
+        <v>0.79</v>
+      </c>
+      <c r="O27" s="15">
+        <v>0.93</v>
+      </c>
+      <c r="P27" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="Q27" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="R27" s="15">
+        <v>0.84</v>
+      </c>
+      <c r="S27" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="T27" s="15">
+        <v>0.73</v>
+      </c>
       <c r="U27" s="3"/>
       <c r="V27" s="4"/>
       <c r="W27" s="4"/>
@@ -1844,29 +2438,47 @@
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F28" s="21"/>
-      <c r="G28" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="L28" s="28"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
+      <c r="D28" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="34"/>
+      <c r="G28" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L28" s="36"/>
+      <c r="M28" s="23">
+        <v>0.83</v>
+      </c>
+      <c r="N28" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="O28" s="23">
+        <v>0.92</v>
+      </c>
+      <c r="P28" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="Q28" s="23">
+        <v>0.84</v>
+      </c>
+      <c r="R28" s="23">
+        <v>0.83</v>
+      </c>
+      <c r="S28" s="23">
+        <v>0.79</v>
+      </c>
+      <c r="T28" s="23">
+        <v>0.74</v>
+      </c>
       <c r="U28" s="3"/>
       <c r="V28" s="4"/>
       <c r="W28" s="4"/>
@@ -1885,25 +2497,41 @@
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="L29" s="29"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L29" s="38"/>
+      <c r="M29" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="N29" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="O29" s="16">
+        <v>0.92</v>
+      </c>
+      <c r="P29" s="16">
+        <v>0.87</v>
+      </c>
+      <c r="Q29" s="16">
+        <v>0.87</v>
+      </c>
+      <c r="R29" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="S29" s="16">
+        <v>0.82</v>
+      </c>
+      <c r="T29" s="16">
+        <v>0.75</v>
+      </c>
       <c r="U29" s="3"/>
       <c r="V29" s="4"/>
       <c r="W29" s="4"/>
@@ -1922,25 +2550,41 @@
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="L30" s="28"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="6"/>
-      <c r="T30" s="6"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L30" s="36"/>
+      <c r="M30" s="15">
+        <v>0.85</v>
+      </c>
+      <c r="N30" s="15">
+        <v>0.81</v>
+      </c>
+      <c r="O30" s="15">
+        <v>0.91</v>
+      </c>
+      <c r="P30" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="Q30" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="R30" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="S30" s="15">
+        <v>0.83</v>
+      </c>
+      <c r="T30" s="15">
+        <v>0.76</v>
+      </c>
       <c r="U30" s="3"/>
       <c r="V30" s="4"/>
       <c r="W30" s="4"/>
@@ -1959,25 +2603,41 @@
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
-      <c r="J31" s="25"/>
-      <c r="K31" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="L31" s="30"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="13"/>
-      <c r="Q31" s="13"/>
-      <c r="R31" s="13"/>
-      <c r="S31" s="13"/>
-      <c r="T31" s="13"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="39"/>
+      <c r="M31" s="16">
+        <v>0.73</v>
+      </c>
+      <c r="N31" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="O31" s="16">
+        <v>0.86</v>
+      </c>
+      <c r="P31" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="Q31" s="16">
+        <v>0.77</v>
+      </c>
+      <c r="R31" s="16">
+        <v>0.81</v>
+      </c>
+      <c r="S31" s="16">
+        <v>0.66</v>
+      </c>
+      <c r="T31" s="16">
+        <v>0.68</v>
+      </c>
       <c r="U31" s="3"/>
       <c r="V31" s="4"/>
       <c r="W31" s="4"/>
@@ -1996,23 +2656,41 @@
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
-      <c r="T32" s="16"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L32" s="36"/>
+      <c r="M32" s="15">
+        <v>0.84</v>
+      </c>
+      <c r="N32" s="17">
+        <v>0.81</v>
+      </c>
+      <c r="O32" s="15">
+        <v>0.91</v>
+      </c>
+      <c r="P32" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="Q32" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="R32" s="15">
+        <v>0.86</v>
+      </c>
+      <c r="S32" s="15">
+        <v>0.81</v>
+      </c>
+      <c r="T32" s="15">
+        <v>0.76</v>
+      </c>
       <c r="U32" s="3"/>
       <c r="V32" s="4"/>
       <c r="W32" s="4"/>
@@ -2031,23 +2709,45 @@
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="16"/>
-      <c r="S33" s="16"/>
-      <c r="T33" s="16"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="34"/>
+      <c r="G33" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L33" s="36"/>
+      <c r="M33" s="15">
+        <v>0.84</v>
+      </c>
+      <c r="N33" s="15">
+        <v>0.81</v>
+      </c>
+      <c r="O33" s="15">
+        <v>0.96</v>
+      </c>
+      <c r="P33" s="15">
+        <v>0.93</v>
+      </c>
+      <c r="Q33" s="15">
+        <v>0.83</v>
+      </c>
+      <c r="R33" s="15">
+        <v>0.83</v>
+      </c>
+      <c r="S33" s="15">
+        <v>0.79</v>
+      </c>
+      <c r="T33" s="15">
+        <v>0.74</v>
+      </c>
       <c r="U33" s="3"/>
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
@@ -2066,23 +2766,41 @@
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="15"/>
-      <c r="R34" s="15"/>
-      <c r="S34" s="15"/>
-      <c r="T34" s="15"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L34" s="38"/>
+      <c r="M34" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="N34" s="19">
+        <v>0.83</v>
+      </c>
+      <c r="O34" s="16">
+        <v>0.9</v>
+      </c>
+      <c r="P34" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="Q34" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="R34" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="S34" s="16">
+        <v>0.82</v>
+      </c>
+      <c r="T34" s="19">
+        <v>0.79</v>
+      </c>
       <c r="U34" s="3"/>
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
@@ -2101,23 +2819,41 @@
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="16"/>
-      <c r="O35" s="16"/>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="16"/>
-      <c r="S35" s="16"/>
-      <c r="T35" s="16"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L35" s="36"/>
+      <c r="M35" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="N35" s="15">
+        <v>0.83</v>
+      </c>
+      <c r="O35" s="15">
+        <v>0.93</v>
+      </c>
+      <c r="P35" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="Q35" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="R35" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="S35" s="15">
+        <v>0.86</v>
+      </c>
+      <c r="T35" s="15">
+        <v>0.79</v>
+      </c>
       <c r="U35" s="3"/>
       <c r="V35" s="4"/>
       <c r="W35" s="4"/>
@@ -2136,23 +2872,41 @@
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="17"/>
-      <c r="T36" s="17"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="39"/>
+      <c r="M36" s="16">
+        <v>0.78</v>
+      </c>
+      <c r="N36" s="16">
+        <v>0.79</v>
+      </c>
+      <c r="O36" s="16">
+        <v>0.78</v>
+      </c>
+      <c r="P36" s="16">
+        <v>0.78</v>
+      </c>
+      <c r="Q36" s="16">
+        <v>0.89</v>
+      </c>
+      <c r="R36" s="16">
+        <v>0.91</v>
+      </c>
+      <c r="S36" s="16">
+        <v>0.77</v>
+      </c>
+      <c r="T36" s="16">
+        <v>0.76</v>
+      </c>
       <c r="U36" s="3"/>
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
@@ -2171,23 +2925,41 @@
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="15"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="15"/>
-      <c r="R37" s="15"/>
-      <c r="S37" s="15"/>
-      <c r="T37" s="15"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L37" s="36"/>
+      <c r="M37" s="15">
+        <v>0.86</v>
+      </c>
+      <c r="N37" s="15">
+        <v>0.83</v>
+      </c>
+      <c r="O37" s="15">
+        <v>0.91</v>
+      </c>
+      <c r="P37" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="Q37" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="R37" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="S37" s="15">
+        <v>0.84</v>
+      </c>
+      <c r="T37" s="17">
+        <v>0.79</v>
+      </c>
       <c r="U37" s="3"/>
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
@@ -2206,23 +2978,29 @@
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="18"/>
-      <c r="N38" s="18"/>
-      <c r="O38" s="18"/>
-      <c r="P38" s="18"/>
-      <c r="Q38" s="18"/>
-      <c r="R38" s="18"/>
-      <c r="S38" s="18"/>
-      <c r="T38" s="18"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="34"/>
+      <c r="G38" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L38" s="36"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="15"/>
       <c r="U38" s="3"/>
       <c r="V38" s="4"/>
       <c r="W38" s="4"/>
@@ -2241,23 +3019,41 @@
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="15"/>
-      <c r="O39" s="15"/>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="15"/>
-      <c r="R39" s="15"/>
-      <c r="S39" s="15"/>
-      <c r="T39" s="15"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L39" s="38"/>
+      <c r="M39" s="16">
+        <v>0.83</v>
+      </c>
+      <c r="N39" s="16">
+        <v>0.79</v>
+      </c>
+      <c r="O39" s="16">
+        <v>0.86</v>
+      </c>
+      <c r="P39" s="16">
+        <v>0.82</v>
+      </c>
+      <c r="Q39" s="16">
+        <v>0.89</v>
+      </c>
+      <c r="R39" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="S39" s="16">
+        <v>0.81</v>
+      </c>
+      <c r="T39" s="16">
+        <v>0.75</v>
+      </c>
       <c r="U39" s="3"/>
       <c r="V39" s="4"/>
       <c r="W39" s="4"/>
@@ -2276,23 +3072,41 @@
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="18"/>
-      <c r="N40" s="18"/>
-      <c r="O40" s="18"/>
-      <c r="P40" s="18"/>
-      <c r="Q40" s="18"/>
-      <c r="R40" s="18"/>
-      <c r="S40" s="18"/>
-      <c r="T40" s="18"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L40" s="36"/>
+      <c r="M40" s="15">
+        <v>0.84</v>
+      </c>
+      <c r="N40" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="O40" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="P40" s="15">
+        <v>0.86</v>
+      </c>
+      <c r="Q40" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="R40" s="15">
+        <v>0.86</v>
+      </c>
+      <c r="S40" s="15">
+        <v>0.81</v>
+      </c>
+      <c r="T40" s="15">
+        <v>0.75</v>
+      </c>
       <c r="U40" s="3"/>
       <c r="V40" s="4"/>
       <c r="W40" s="4"/>
@@ -2311,23 +3125,41 @@
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
-      <c r="M41" s="15"/>
-      <c r="N41" s="15"/>
-      <c r="O41" s="15"/>
-      <c r="P41" s="15"/>
-      <c r="Q41" s="15"/>
-      <c r="R41" s="15"/>
-      <c r="S41" s="15"/>
-      <c r="T41" s="15"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="39"/>
+      <c r="M41" s="16">
+        <v>0.67</v>
+      </c>
+      <c r="N41" s="16">
+        <v>0.65</v>
+      </c>
+      <c r="O41" s="16">
+        <v>0.66</v>
+      </c>
+      <c r="P41" s="16">
+        <v>0.64</v>
+      </c>
+      <c r="Q41" s="16">
+        <v>0.83</v>
+      </c>
+      <c r="R41" s="16">
+        <v>0.84</v>
+      </c>
+      <c r="S41" s="16">
+        <v>0.65</v>
+      </c>
+      <c r="T41" s="16">
+        <v>0.63</v>
+      </c>
       <c r="U41" s="3"/>
       <c r="V41" s="4"/>
       <c r="W41" s="4"/>
@@ -2346,23 +3178,41 @@
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="18"/>
-      <c r="N42" s="18"/>
-      <c r="O42" s="18"/>
-      <c r="P42" s="18"/>
-      <c r="Q42" s="18"/>
-      <c r="R42" s="18"/>
-      <c r="S42" s="18"/>
-      <c r="T42" s="18"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L42" s="36"/>
+      <c r="M42" s="15">
+        <v>0.85</v>
+      </c>
+      <c r="N42" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="O42" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="P42" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="Q42" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="R42" s="15">
+        <v>0.86</v>
+      </c>
+      <c r="S42" s="15">
+        <v>0.82</v>
+      </c>
+      <c r="T42" s="15">
+        <v>0.75</v>
+      </c>
       <c r="U42" s="3"/>
       <c r="V42" s="4"/>
       <c r="W42" s="4"/>
@@ -2381,23 +3231,45 @@
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
-      <c r="M43" s="15"/>
-      <c r="N43" s="15"/>
-      <c r="O43" s="15"/>
-      <c r="P43" s="15"/>
-      <c r="Q43" s="15"/>
-      <c r="R43" s="15"/>
-      <c r="S43" s="15"/>
-      <c r="T43" s="15"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" s="34"/>
+      <c r="G43" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L43" s="36"/>
+      <c r="M43" s="16">
+        <v>0.83</v>
+      </c>
+      <c r="N43" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="O43" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="P43" s="16">
+        <v>0.83</v>
+      </c>
+      <c r="Q43" s="16">
+        <v>0.87</v>
+      </c>
+      <c r="R43" s="16">
+        <v>0.82</v>
+      </c>
+      <c r="S43" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="T43" s="16">
+        <v>0.75</v>
+      </c>
       <c r="U43" s="3"/>
       <c r="V43" s="4"/>
       <c r="W43" s="4"/>
@@ -2416,23 +3288,41 @@
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="14"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
-      <c r="M44" s="18"/>
-      <c r="N44" s="18"/>
-      <c r="O44" s="18"/>
-      <c r="P44" s="18"/>
-      <c r="Q44" s="18"/>
-      <c r="R44" s="18"/>
-      <c r="S44" s="18"/>
-      <c r="T44" s="18"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="35"/>
+      <c r="I44" s="35"/>
+      <c r="J44" s="35"/>
+      <c r="K44" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L44" s="38"/>
+      <c r="M44" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="N44" s="18">
+        <v>0.74</v>
+      </c>
+      <c r="O44" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="P44" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q44" s="18">
+        <v>0.73</v>
+      </c>
+      <c r="R44" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="S44" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="T44" s="18" t="s">
+        <v>82</v>
+      </c>
       <c r="U44" s="3"/>
       <c r="V44" s="4"/>
       <c r="W44" s="4"/>
@@ -2451,23 +3341,41 @@
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
-      <c r="N45" s="15"/>
-      <c r="O45" s="15"/>
-      <c r="P45" s="15"/>
-      <c r="Q45" s="15"/>
-      <c r="R45" s="15"/>
-      <c r="S45" s="15"/>
-      <c r="T45" s="15"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="35"/>
+      <c r="I45" s="35"/>
+      <c r="J45" s="35"/>
+      <c r="K45" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L45" s="36"/>
+      <c r="M45" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="N45" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="O45" s="31">
+        <v>0.49</v>
+      </c>
+      <c r="P45" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q45" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="R45" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="S45" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="T45" s="31" t="s">
+        <v>89</v>
+      </c>
       <c r="U45" s="3"/>
       <c r="V45" s="4"/>
       <c r="W45" s="4"/>
@@ -2486,23 +3394,41 @@
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="18"/>
-      <c r="N46" s="18"/>
-      <c r="O46" s="18"/>
-      <c r="P46" s="18"/>
-      <c r="Q46" s="18"/>
-      <c r="R46" s="18"/>
-      <c r="S46" s="18"/>
-      <c r="T46" s="18"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="35"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" s="39"/>
+      <c r="M46" s="32">
+        <v>0.85</v>
+      </c>
+      <c r="N46" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="O46" s="32">
+        <v>0.92</v>
+      </c>
+      <c r="P46" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q46" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R46" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="S46" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="T46" s="32" t="s">
+        <v>75</v>
+      </c>
       <c r="U46" s="3"/>
       <c r="V46" s="4"/>
       <c r="W46" s="4"/>
@@ -2521,23 +3447,41 @@
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="15"/>
-      <c r="N47" s="15"/>
-      <c r="O47" s="15"/>
-      <c r="P47" s="15"/>
-      <c r="Q47" s="15"/>
-      <c r="R47" s="15"/>
-      <c r="S47" s="15"/>
-      <c r="T47" s="15"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="35"/>
+      <c r="J47" s="35"/>
+      <c r="K47" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L47" s="36"/>
+      <c r="M47" s="15">
+        <v>0.86</v>
+      </c>
+      <c r="N47" s="15">
+        <v>0.83</v>
+      </c>
+      <c r="O47" s="15">
+        <v>0.91</v>
+      </c>
+      <c r="P47" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="Q47" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="R47" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="S47" s="15">
+        <v>0.84</v>
+      </c>
+      <c r="T47" s="15">
+        <v>0.79</v>
+      </c>
       <c r="U47" s="3"/>
       <c r="V47" s="4"/>
       <c r="W47" s="4"/>
@@ -2556,23 +3500,31 @@
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="19"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-      <c r="R48" s="17"/>
-      <c r="S48" s="17"/>
-      <c r="T48" s="17"/>
+      <c r="D48" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="E48" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" s="34"/>
+      <c r="G48" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" s="35"/>
+      <c r="I48" s="35"/>
+      <c r="J48" s="35"/>
+      <c r="K48" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L48" s="36"/>
+      <c r="M48" s="33"/>
+      <c r="N48" s="33"/>
+      <c r="O48" s="33"/>
+      <c r="P48" s="33"/>
+      <c r="Q48" s="33"/>
+      <c r="R48" s="33"/>
+      <c r="S48" s="33"/>
+      <c r="T48" s="33"/>
       <c r="U48" s="3"/>
       <c r="V48" s="4"/>
       <c r="W48" s="4"/>
@@ -2591,23 +3543,25 @@
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="19"/>
-      <c r="J49" s="19"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="17"/>
-      <c r="S49" s="17"/>
-      <c r="T49" s="17"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="35"/>
+      <c r="H49" s="35"/>
+      <c r="I49" s="35"/>
+      <c r="J49" s="35"/>
+      <c r="K49" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L49" s="38"/>
+      <c r="M49" s="21"/>
+      <c r="N49" s="21"/>
+      <c r="O49" s="21"/>
+      <c r="P49" s="21"/>
+      <c r="Q49" s="21"/>
+      <c r="R49" s="21"/>
+      <c r="S49" s="21"/>
+      <c r="T49" s="21"/>
       <c r="U49" s="3"/>
       <c r="V49" s="4"/>
       <c r="W49" s="4"/>
@@ -2626,23 +3580,25 @@
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="19"/>
-      <c r="K50" s="15"/>
-      <c r="L50" s="15"/>
-      <c r="M50" s="17"/>
-      <c r="N50" s="17"/>
-      <c r="O50" s="17"/>
-      <c r="P50" s="16"/>
-      <c r="Q50" s="17"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="17"/>
-      <c r="T50" s="17"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="35"/>
+      <c r="J50" s="35"/>
+      <c r="K50" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L50" s="36"/>
+      <c r="M50" s="20"/>
+      <c r="N50" s="22"/>
+      <c r="O50" s="20"/>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="20"/>
+      <c r="R50" s="20"/>
+      <c r="S50" s="20"/>
+      <c r="T50" s="22"/>
       <c r="U50" s="3"/>
       <c r="V50" s="4"/>
       <c r="W50" s="4"/>
@@ -2661,23 +3617,25 @@
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="19"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" s="17"/>
-      <c r="O51" s="17"/>
-      <c r="P51" s="17"/>
-      <c r="Q51" s="17"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="17"/>
-      <c r="T51" s="17"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="35"/>
+      <c r="I51" s="35"/>
+      <c r="J51" s="35"/>
+      <c r="K51" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="39"/>
+      <c r="M51" s="21"/>
+      <c r="N51" s="21"/>
+      <c r="O51" s="21"/>
+      <c r="P51" s="21"/>
+      <c r="Q51" s="21"/>
+      <c r="R51" s="21"/>
+      <c r="S51" s="21"/>
+      <c r="T51" s="21"/>
       <c r="U51" s="3"/>
       <c r="V51" s="4"/>
       <c r="W51" s="4"/>
@@ -2696,23 +3654,25 @@
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="19"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="17"/>
-      <c r="S52" s="17"/>
-      <c r="T52" s="17"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L52" s="36"/>
+      <c r="M52" s="20"/>
+      <c r="N52" s="20"/>
+      <c r="O52" s="20"/>
+      <c r="P52" s="20"/>
+      <c r="Q52" s="20"/>
+      <c r="R52" s="20"/>
+      <c r="S52" s="20"/>
+      <c r="T52" s="20"/>
       <c r="U52" s="3"/>
       <c r="V52" s="4"/>
       <c r="W52" s="4"/>
@@ -2731,23 +3691,45 @@
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="19"/>
-      <c r="J53" s="19"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="17"/>
-      <c r="O53" s="17"/>
-      <c r="P53" s="17"/>
-      <c r="Q53" s="17"/>
-      <c r="R53" s="17"/>
-      <c r="S53" s="17"/>
-      <c r="T53" s="17"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" s="34"/>
+      <c r="G53" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L53" s="36"/>
+      <c r="M53" s="24">
+        <v>0.73</v>
+      </c>
+      <c r="N53" s="24">
+        <v>0.75</v>
+      </c>
+      <c r="O53" s="24">
+        <v>0.95</v>
+      </c>
+      <c r="P53" s="24">
+        <v>0.94</v>
+      </c>
+      <c r="Q53" s="24">
+        <v>0.73</v>
+      </c>
+      <c r="R53" s="24">
+        <v>0.77</v>
+      </c>
+      <c r="S53" s="24">
+        <v>0.6</v>
+      </c>
+      <c r="T53" s="24">
+        <v>0.6</v>
+      </c>
       <c r="U53" s="3"/>
       <c r="V53" s="4"/>
       <c r="W53" s="4"/>
@@ -2766,23 +3748,41 @@
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="19"/>
-      <c r="J54" s="19"/>
-      <c r="K54" s="15"/>
-      <c r="L54" s="15"/>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17"/>
-      <c r="O54" s="17"/>
-      <c r="P54" s="17"/>
-      <c r="Q54" s="17"/>
-      <c r="R54" s="17"/>
-      <c r="S54" s="17"/>
-      <c r="T54" s="17"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="35"/>
+      <c r="I54" s="35"/>
+      <c r="J54" s="35"/>
+      <c r="K54" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L54" s="38"/>
+      <c r="M54" s="25">
+        <v>0.76</v>
+      </c>
+      <c r="N54" s="26">
+        <v>0.74</v>
+      </c>
+      <c r="O54" s="25">
+        <v>0.9</v>
+      </c>
+      <c r="P54" s="25">
+        <v>0.89</v>
+      </c>
+      <c r="Q54" s="25">
+        <v>0.78</v>
+      </c>
+      <c r="R54" s="25">
+        <v>0.78</v>
+      </c>
+      <c r="S54" s="25">
+        <v>0.69</v>
+      </c>
+      <c r="T54" s="26">
+        <v>0.63</v>
+      </c>
       <c r="U54" s="3"/>
       <c r="V54" s="4"/>
       <c r="W54" s="4"/>
@@ -2801,23 +3801,41 @@
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="19"/>
-      <c r="J55" s="19"/>
-      <c r="K55" s="17"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17"/>
-      <c r="O55" s="17"/>
-      <c r="P55" s="17"/>
-      <c r="Q55" s="17"/>
-      <c r="R55" s="17"/>
-      <c r="S55" s="17"/>
-      <c r="T55" s="17"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="35"/>
+      <c r="H55" s="35"/>
+      <c r="I55" s="35"/>
+      <c r="J55" s="35"/>
+      <c r="K55" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L55" s="36"/>
+      <c r="M55" s="24">
+        <v>0.82</v>
+      </c>
+      <c r="N55" s="24">
+        <v>0.74</v>
+      </c>
+      <c r="O55" s="24">
+        <v>0.95</v>
+      </c>
+      <c r="P55" s="24">
+        <v>0.88</v>
+      </c>
+      <c r="Q55" s="24">
+        <v>0.82</v>
+      </c>
+      <c r="R55" s="24">
+        <v>0.78</v>
+      </c>
+      <c r="S55" s="24">
+        <v>0.77</v>
+      </c>
+      <c r="T55" s="24">
+        <v>0.64</v>
+      </c>
       <c r="U55" s="3"/>
       <c r="V55" s="4"/>
       <c r="W55" s="4"/>
@@ -2836,23 +3854,41 @@
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="19"/>
-      <c r="J56" s="19"/>
-      <c r="K56" s="15"/>
-      <c r="L56" s="15"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
-      <c r="Q56" s="17"/>
-      <c r="R56" s="17"/>
-      <c r="S56" s="17"/>
-      <c r="T56" s="17"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="35"/>
+      <c r="J56" s="35"/>
+      <c r="K56" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L56" s="39"/>
+      <c r="M56" s="16">
+        <v>0.64</v>
+      </c>
+      <c r="N56" s="16">
+        <v>0.65</v>
+      </c>
+      <c r="O56" s="16">
+        <v>0.67</v>
+      </c>
+      <c r="P56" s="16">
+        <v>0.69</v>
+      </c>
+      <c r="Q56" s="16">
+        <v>0.78</v>
+      </c>
+      <c r="R56" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="S56" s="16">
+        <v>0.61</v>
+      </c>
+      <c r="T56" s="16">
+        <v>0.61</v>
+      </c>
       <c r="U56" s="3"/>
       <c r="V56" s="4"/>
       <c r="W56" s="4"/>
@@ -2871,23 +3907,41 @@
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="19"/>
-      <c r="J57" s="19"/>
-      <c r="K57" s="17"/>
-      <c r="L57" s="17"/>
-      <c r="M57" s="17"/>
-      <c r="N57" s="17"/>
-      <c r="O57" s="17"/>
-      <c r="P57" s="17"/>
-      <c r="Q57" s="17"/>
-      <c r="R57" s="17"/>
-      <c r="S57" s="17"/>
-      <c r="T57" s="17"/>
+      <c r="D57" s="41"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="35"/>
+      <c r="J57" s="35"/>
+      <c r="K57" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L57" s="36"/>
+      <c r="M57" s="15">
+        <v>0.78</v>
+      </c>
+      <c r="N57" s="17">
+        <v>0.73</v>
+      </c>
+      <c r="O57" s="15">
+        <v>0.94</v>
+      </c>
+      <c r="P57" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="Q57" s="15">
+        <v>0.78</v>
+      </c>
+      <c r="R57" s="15">
+        <v>0.78</v>
+      </c>
+      <c r="S57" s="15">
+        <v>0.71</v>
+      </c>
+      <c r="T57" s="17">
+        <v>0.63</v>
+      </c>
       <c r="U57" s="3"/>
       <c r="V57" s="4"/>
       <c r="W57" s="4"/>
@@ -2906,23 +3960,45 @@
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="19"/>
-      <c r="J58" s="19"/>
-      <c r="K58" s="15"/>
-      <c r="L58" s="15"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="17"/>
-      <c r="O58" s="17"/>
-      <c r="P58" s="17"/>
-      <c r="Q58" s="17"/>
-      <c r="R58" s="16"/>
-      <c r="S58" s="17"/>
-      <c r="T58" s="17"/>
+      <c r="D58" s="41"/>
+      <c r="E58" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="F58" s="34"/>
+      <c r="G58" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="H58" s="35"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="35"/>
+      <c r="K58" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L58" s="36"/>
+      <c r="M58" s="23">
+        <v>0.73</v>
+      </c>
+      <c r="N58" s="23">
+        <v>0.75</v>
+      </c>
+      <c r="O58" s="23">
+        <v>0.95</v>
+      </c>
+      <c r="P58" s="23">
+        <v>0.94</v>
+      </c>
+      <c r="Q58" s="23">
+        <v>0.73</v>
+      </c>
+      <c r="R58" s="23">
+        <v>0.77</v>
+      </c>
+      <c r="S58" s="23">
+        <v>0.6</v>
+      </c>
+      <c r="T58" s="23">
+        <v>0.6</v>
+      </c>
       <c r="U58" s="3"/>
       <c r="V58" s="4"/>
       <c r="W58" s="4"/>
@@ -2941,23 +4017,41 @@
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="19"/>
-      <c r="J59" s="19"/>
-      <c r="K59" s="17"/>
-      <c r="L59" s="17"/>
-      <c r="M59" s="17"/>
-      <c r="N59" s="17"/>
-      <c r="O59" s="17"/>
-      <c r="P59" s="17"/>
-      <c r="Q59" s="17"/>
-      <c r="R59" s="17"/>
-      <c r="S59" s="17"/>
-      <c r="T59" s="17"/>
+      <c r="D59" s="41"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="35"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L59" s="38"/>
+      <c r="M59" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="N59" s="16">
+        <v>0.73</v>
+      </c>
+      <c r="O59" s="16">
+        <v>0.9</v>
+      </c>
+      <c r="P59" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="Q59" s="16">
+        <v>0.77</v>
+      </c>
+      <c r="R59" s="16">
+        <v>0.78</v>
+      </c>
+      <c r="S59" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="T59" s="16">
+        <v>0.62</v>
+      </c>
       <c r="U59" s="3"/>
       <c r="V59" s="4"/>
       <c r="W59" s="4"/>
@@ -2976,23 +4070,41 @@
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="19"/>
-      <c r="J60" s="19"/>
-      <c r="K60" s="15"/>
-      <c r="L60" s="15"/>
-      <c r="M60" s="17"/>
-      <c r="N60" s="17"/>
-      <c r="O60" s="17"/>
-      <c r="P60" s="17"/>
-      <c r="Q60" s="17"/>
-      <c r="R60" s="17"/>
-      <c r="S60" s="17"/>
-      <c r="T60" s="17"/>
+      <c r="D60" s="41"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="35"/>
+      <c r="I60" s="35"/>
+      <c r="J60" s="35"/>
+      <c r="K60" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L60" s="36"/>
+      <c r="M60" s="15">
+        <v>0.82</v>
+      </c>
+      <c r="N60" s="15">
+        <v>0.74</v>
+      </c>
+      <c r="O60" s="15">
+        <v>0.95</v>
+      </c>
+      <c r="P60" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="Q60" s="15">
+        <v>0.82</v>
+      </c>
+      <c r="R60" s="15">
+        <v>0.78</v>
+      </c>
+      <c r="S60" s="15">
+        <v>0.77</v>
+      </c>
+      <c r="T60" s="15">
+        <v>0.64</v>
+      </c>
       <c r="U60" s="3"/>
       <c r="V60" s="4"/>
       <c r="W60" s="4"/>
@@ -3011,23 +4123,41 @@
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="19"/>
-      <c r="K61" s="17"/>
-      <c r="L61" s="17"/>
-      <c r="M61" s="17"/>
-      <c r="N61" s="17"/>
-      <c r="O61" s="17"/>
-      <c r="P61" s="17"/>
-      <c r="Q61" s="17"/>
-      <c r="R61" s="17"/>
-      <c r="S61" s="17"/>
-      <c r="T61" s="17"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="34"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="35"/>
+      <c r="I61" s="35"/>
+      <c r="J61" s="35"/>
+      <c r="K61" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L61" s="39"/>
+      <c r="M61" s="16">
+        <v>0.64</v>
+      </c>
+      <c r="N61" s="16">
+        <v>0.65</v>
+      </c>
+      <c r="O61" s="16">
+        <v>0.67</v>
+      </c>
+      <c r="P61" s="16">
+        <v>0.69</v>
+      </c>
+      <c r="Q61" s="16">
+        <v>0.78</v>
+      </c>
+      <c r="R61" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="S61" s="16">
+        <v>0.61</v>
+      </c>
+      <c r="T61" s="16">
+        <v>0.61</v>
+      </c>
       <c r="U61" s="3"/>
       <c r="V61" s="4"/>
       <c r="W61" s="4"/>
@@ -3046,23 +4176,41 @@
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="19"/>
-      <c r="J62" s="19"/>
-      <c r="K62" s="15"/>
-      <c r="L62" s="15"/>
-      <c r="M62" s="17"/>
-      <c r="N62" s="17"/>
-      <c r="O62" s="17"/>
-      <c r="P62" s="17"/>
-      <c r="Q62" s="17"/>
-      <c r="R62" s="17"/>
-      <c r="S62" s="17"/>
-      <c r="T62" s="17"/>
+      <c r="D62" s="41"/>
+      <c r="E62" s="34"/>
+      <c r="F62" s="34"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="35"/>
+      <c r="J62" s="35"/>
+      <c r="K62" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L62" s="36"/>
+      <c r="M62" s="15">
+        <v>0.78</v>
+      </c>
+      <c r="N62" s="15">
+        <v>0.73</v>
+      </c>
+      <c r="O62" s="15">
+        <v>0.94</v>
+      </c>
+      <c r="P62" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="Q62" s="15">
+        <v>0.78</v>
+      </c>
+      <c r="R62" s="15">
+        <v>0.78</v>
+      </c>
+      <c r="S62" s="15">
+        <v>0.78</v>
+      </c>
+      <c r="T62" s="15">
+        <v>0.73</v>
+      </c>
       <c r="U62" s="3"/>
       <c r="V62" s="4"/>
       <c r="W62" s="4"/>
@@ -3081,23 +4229,45 @@
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="19"/>
-      <c r="J63" s="19"/>
-      <c r="K63" s="17"/>
-      <c r="L63" s="17"/>
-      <c r="M63" s="17"/>
-      <c r="N63" s="17"/>
-      <c r="O63" s="17"/>
-      <c r="P63" s="17"/>
-      <c r="Q63" s="17"/>
-      <c r="R63" s="17"/>
-      <c r="S63" s="17"/>
-      <c r="T63" s="17"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63" s="34"/>
+      <c r="G63" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H63" s="35"/>
+      <c r="I63" s="35"/>
+      <c r="J63" s="35"/>
+      <c r="K63" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L63" s="36"/>
+      <c r="M63" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="N63" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="O63" s="15">
+        <v>0.96</v>
+      </c>
+      <c r="P63" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q63" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="R63" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="S63" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="T63" s="15" t="s">
+        <v>77</v>
+      </c>
       <c r="U63" s="3"/>
       <c r="V63" s="4"/>
       <c r="W63" s="4"/>
@@ -3116,23 +4286,41 @@
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
-      <c r="K64" s="15"/>
-      <c r="L64" s="15"/>
-      <c r="M64" s="17"/>
-      <c r="N64" s="17"/>
-      <c r="O64" s="17"/>
-      <c r="P64" s="17"/>
-      <c r="Q64" s="17"/>
-      <c r="R64" s="17"/>
-      <c r="S64" s="17"/>
-      <c r="T64" s="17"/>
+      <c r="D64" s="41"/>
+      <c r="E64" s="34"/>
+      <c r="F64" s="34"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="35"/>
+      <c r="I64" s="35"/>
+      <c r="J64" s="35"/>
+      <c r="K64" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L64" s="38"/>
+      <c r="M64" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N64" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O64" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="P64" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q64" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="R64" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="S64" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="T64" s="19" t="s">
+        <v>63</v>
+      </c>
       <c r="U64" s="3"/>
       <c r="V64" s="4"/>
       <c r="W64" s="4"/>
@@ -3151,23 +4339,41 @@
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="19"/>
-      <c r="K65" s="17"/>
-      <c r="L65" s="17"/>
-      <c r="M65" s="17"/>
-      <c r="N65" s="17"/>
-      <c r="O65" s="17"/>
-      <c r="P65" s="17"/>
-      <c r="Q65" s="17"/>
-      <c r="R65" s="17"/>
-      <c r="S65" s="17"/>
-      <c r="T65" s="17"/>
+      <c r="D65" s="41"/>
+      <c r="E65" s="34"/>
+      <c r="F65" s="34"/>
+      <c r="G65" s="35"/>
+      <c r="H65" s="35"/>
+      <c r="I65" s="35"/>
+      <c r="J65" s="35"/>
+      <c r="K65" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L65" s="36"/>
+      <c r="M65" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="O65" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="P65" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q65" s="15">
+        <v>0.76</v>
+      </c>
+      <c r="R65" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="S65" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="T65" s="15" t="s">
+        <v>78</v>
+      </c>
       <c r="U65" s="3"/>
       <c r="V65" s="4"/>
       <c r="W65" s="4"/>
@@ -3186,23 +4392,41 @@
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="14"/>
-      <c r="J66" s="14"/>
-      <c r="K66" s="15"/>
-      <c r="L66" s="15"/>
-      <c r="M66" s="17"/>
-      <c r="N66" s="17"/>
-      <c r="O66" s="17"/>
-      <c r="P66" s="17"/>
-      <c r="Q66" s="17"/>
-      <c r="R66" s="17"/>
-      <c r="S66" s="17"/>
-      <c r="T66" s="17"/>
+      <c r="D66" s="41"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="34"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="35"/>
+      <c r="I66" s="35"/>
+      <c r="J66" s="35"/>
+      <c r="K66" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L66" s="39"/>
+      <c r="M66" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="N66" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="O66" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="P66" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="R66" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="S66" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="T66" s="16" t="s">
+        <v>84</v>
+      </c>
       <c r="U66" s="3"/>
       <c r="V66" s="4"/>
       <c r="W66" s="4"/>
@@ -3221,23 +4445,41 @@
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="14"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="15"/>
-      <c r="L67" s="15"/>
-      <c r="M67" s="15"/>
-      <c r="N67" s="15"/>
-      <c r="O67" s="15"/>
-      <c r="P67" s="15"/>
-      <c r="Q67" s="15"/>
-      <c r="R67" s="15"/>
-      <c r="S67" s="15"/>
-      <c r="T67" s="15"/>
+      <c r="D67" s="41"/>
+      <c r="E67" s="34"/>
+      <c r="F67" s="34"/>
+      <c r="G67" s="35"/>
+      <c r="H67" s="35"/>
+      <c r="I67" s="35"/>
+      <c r="J67" s="35"/>
+      <c r="K67" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L67" s="36"/>
+      <c r="M67" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="N67" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="O67" s="15">
+        <v>0.92</v>
+      </c>
+      <c r="P67" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q67" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="R67" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="S67" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="T67" s="15" t="s">
+        <v>84</v>
+      </c>
       <c r="U67" s="3"/>
       <c r="V67" s="4"/>
       <c r="W67" s="4"/>
@@ -3256,23 +4498,47 @@
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="14"/>
-      <c r="K68" s="15"/>
-      <c r="L68" s="15"/>
-      <c r="M68" s="17"/>
-      <c r="N68" s="17"/>
-      <c r="O68" s="17"/>
-      <c r="P68" s="17"/>
-      <c r="Q68" s="17"/>
-      <c r="R68" s="17"/>
-      <c r="S68" s="17"/>
-      <c r="T68" s="17"/>
+      <c r="D68" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="E68" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" s="34"/>
+      <c r="G68" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" s="35"/>
+      <c r="I68" s="35"/>
+      <c r="J68" s="35"/>
+      <c r="K68" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L68" s="36"/>
+      <c r="M68" s="28">
+        <v>0.83</v>
+      </c>
+      <c r="N68" s="28">
+        <v>0.82</v>
+      </c>
+      <c r="O68" s="28">
+        <v>0.89</v>
+      </c>
+      <c r="P68" s="28">
+        <v>0.87</v>
+      </c>
+      <c r="Q68" s="28">
+        <v>0.87</v>
+      </c>
+      <c r="R68" s="28">
+        <v>0.87</v>
+      </c>
+      <c r="S68" s="28">
+        <v>0.8</v>
+      </c>
+      <c r="T68" s="28">
+        <v>0.87</v>
+      </c>
       <c r="U68" s="3"/>
       <c r="V68" s="4"/>
       <c r="W68" s="4"/>
@@ -3291,23 +4557,41 @@
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="14"/>
-      <c r="J69" s="14"/>
-      <c r="K69" s="15"/>
-      <c r="L69" s="15"/>
-      <c r="M69" s="15"/>
-      <c r="N69" s="15"/>
-      <c r="O69" s="15"/>
-      <c r="P69" s="15"/>
-      <c r="Q69" s="15"/>
-      <c r="R69" s="15"/>
-      <c r="S69" s="15"/>
-      <c r="T69" s="15"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="34"/>
+      <c r="F69" s="34"/>
+      <c r="G69" s="35"/>
+      <c r="H69" s="35"/>
+      <c r="I69" s="35"/>
+      <c r="J69" s="35"/>
+      <c r="K69" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L69" s="38"/>
+      <c r="M69" s="25">
+        <v>0.83</v>
+      </c>
+      <c r="N69" s="25">
+        <v>0.79</v>
+      </c>
+      <c r="O69" s="25">
+        <v>0.9</v>
+      </c>
+      <c r="P69" s="25">
+        <v>0.88</v>
+      </c>
+      <c r="Q69" s="25">
+        <v>0.85</v>
+      </c>
+      <c r="R69" s="25">
+        <v>0.84</v>
+      </c>
+      <c r="S69" s="25">
+        <v>0.79</v>
+      </c>
+      <c r="T69" s="25">
+        <v>0.72</v>
+      </c>
       <c r="U69" s="3"/>
       <c r="V69" s="4"/>
       <c r="W69" s="4"/>
@@ -3326,23 +4610,41 @@
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="15"/>
-      <c r="L70" s="15"/>
-      <c r="M70" s="17"/>
-      <c r="N70" s="17"/>
-      <c r="O70" s="17"/>
-      <c r="P70" s="17"/>
-      <c r="Q70" s="17"/>
-      <c r="R70" s="17"/>
-      <c r="S70" s="17"/>
-      <c r="T70" s="17"/>
+      <c r="D70" s="41"/>
+      <c r="E70" s="34"/>
+      <c r="F70" s="34"/>
+      <c r="G70" s="35"/>
+      <c r="H70" s="35"/>
+      <c r="I70" s="35"/>
+      <c r="J70" s="35"/>
+      <c r="K70" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L70" s="36"/>
+      <c r="M70" s="24">
+        <v>0.84</v>
+      </c>
+      <c r="N70" s="24">
+        <v>0.82</v>
+      </c>
+      <c r="O70" s="24">
+        <v>0.91</v>
+      </c>
+      <c r="P70" s="24">
+        <v>0.88</v>
+      </c>
+      <c r="Q70" s="24">
+        <v>0.87</v>
+      </c>
+      <c r="R70" s="24">
+        <v>0.87</v>
+      </c>
+      <c r="S70" s="24">
+        <v>0.81</v>
+      </c>
+      <c r="T70" s="24">
+        <v>0.77</v>
+      </c>
       <c r="U70" s="3"/>
       <c r="V70" s="4"/>
       <c r="W70" s="4"/>
@@ -3361,23 +4663,41 @@
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="14"/>
-      <c r="J71" s="14"/>
-      <c r="K71" s="15"/>
-      <c r="L71" s="15"/>
-      <c r="M71" s="15"/>
-      <c r="N71" s="15"/>
-      <c r="O71" s="15"/>
-      <c r="P71" s="15"/>
-      <c r="Q71" s="15"/>
-      <c r="R71" s="15"/>
-      <c r="S71" s="15"/>
-      <c r="T71" s="15"/>
+      <c r="D71" s="41"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="34"/>
+      <c r="G71" s="35"/>
+      <c r="H71" s="35"/>
+      <c r="I71" s="35"/>
+      <c r="J71" s="35"/>
+      <c r="K71" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L71" s="39"/>
+      <c r="M71" s="25">
+        <v>0.74</v>
+      </c>
+      <c r="N71" s="25">
+        <v>0.75</v>
+      </c>
+      <c r="O71" s="25">
+        <v>0.85</v>
+      </c>
+      <c r="P71" s="25">
+        <v>0.85</v>
+      </c>
+      <c r="Q71" s="25">
+        <v>0.78</v>
+      </c>
+      <c r="R71" s="25">
+        <v>0.81</v>
+      </c>
+      <c r="S71" s="25">
+        <v>0.68</v>
+      </c>
+      <c r="T71" s="25">
+        <v>0.68</v>
+      </c>
       <c r="U71" s="3"/>
       <c r="V71" s="4"/>
       <c r="W71" s="4"/>
@@ -3396,23 +4716,41 @@
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="19"/>
-      <c r="I72" s="19"/>
-      <c r="J72" s="19"/>
-      <c r="K72" s="15"/>
-      <c r="L72" s="15"/>
-      <c r="M72" s="17"/>
-      <c r="N72" s="17"/>
-      <c r="O72" s="17"/>
-      <c r="P72" s="17"/>
-      <c r="Q72" s="17"/>
-      <c r="R72" s="17"/>
-      <c r="S72" s="17"/>
-      <c r="T72" s="17"/>
+      <c r="D72" s="41"/>
+      <c r="E72" s="34"/>
+      <c r="F72" s="34"/>
+      <c r="G72" s="35"/>
+      <c r="H72" s="35"/>
+      <c r="I72" s="35"/>
+      <c r="J72" s="35"/>
+      <c r="K72" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L72" s="36"/>
+      <c r="M72" s="24">
+        <v>0.83</v>
+      </c>
+      <c r="N72" s="27">
+        <v>0.83</v>
+      </c>
+      <c r="O72" s="24">
+        <v>0.9</v>
+      </c>
+      <c r="P72" s="24">
+        <v>0.89</v>
+      </c>
+      <c r="Q72" s="24">
+        <v>0.85</v>
+      </c>
+      <c r="R72" s="24">
+        <v>0.87</v>
+      </c>
+      <c r="S72" s="24">
+        <v>0.8</v>
+      </c>
+      <c r="T72" s="24">
+        <v>0.78</v>
+      </c>
       <c r="U72" s="3"/>
       <c r="V72" s="4"/>
       <c r="W72" s="4"/>
@@ -3431,23 +4769,45 @@
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="19"/>
-      <c r="J73" s="19"/>
-      <c r="K73" s="17"/>
-      <c r="L73" s="17"/>
-      <c r="M73" s="17"/>
-      <c r="N73" s="17"/>
-      <c r="O73" s="17"/>
-      <c r="P73" s="17"/>
-      <c r="Q73" s="17"/>
-      <c r="R73" s="17"/>
-      <c r="S73" s="17"/>
-      <c r="T73" s="17"/>
+      <c r="D73" s="41"/>
+      <c r="E73" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="F73" s="34"/>
+      <c r="G73" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="H73" s="35"/>
+      <c r="I73" s="35"/>
+      <c r="J73" s="35"/>
+      <c r="K73" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L73" s="36"/>
+      <c r="M73" s="23">
+        <v>0.87</v>
+      </c>
+      <c r="N73" s="23">
+        <v>0.82</v>
+      </c>
+      <c r="O73" s="23">
+        <v>0.91</v>
+      </c>
+      <c r="P73" s="23">
+        <v>0.88</v>
+      </c>
+      <c r="Q73" s="23">
+        <v>0.9</v>
+      </c>
+      <c r="R73" s="23">
+        <v>0.88</v>
+      </c>
+      <c r="S73" s="23">
+        <v>0.85</v>
+      </c>
+      <c r="T73" s="23">
+        <v>0.88</v>
+      </c>
       <c r="U73" s="3"/>
       <c r="V73" s="4"/>
       <c r="W73" s="4"/>
@@ -3466,23 +4826,41 @@
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="19"/>
-      <c r="H74" s="19"/>
-      <c r="I74" s="19"/>
-      <c r="J74" s="19"/>
-      <c r="K74" s="15"/>
-      <c r="L74" s="15"/>
-      <c r="M74" s="17"/>
-      <c r="N74" s="17"/>
-      <c r="O74" s="17"/>
-      <c r="P74" s="16"/>
-      <c r="Q74" s="17"/>
-      <c r="R74" s="17"/>
-      <c r="S74" s="17"/>
-      <c r="T74" s="17"/>
+      <c r="D74" s="41"/>
+      <c r="E74" s="34"/>
+      <c r="F74" s="34"/>
+      <c r="G74" s="35"/>
+      <c r="H74" s="35"/>
+      <c r="I74" s="35"/>
+      <c r="J74" s="35"/>
+      <c r="K74" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L74" s="38"/>
+      <c r="M74" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="N74" s="16">
+        <v>0.81</v>
+      </c>
+      <c r="O74" s="16">
+        <v>0.89</v>
+      </c>
+      <c r="P74" s="16">
+        <v>0.86</v>
+      </c>
+      <c r="Q74" s="16">
+        <v>0.89</v>
+      </c>
+      <c r="R74" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="S74" s="16">
+        <v>0.83</v>
+      </c>
+      <c r="T74" s="16">
+        <v>0.77</v>
+      </c>
       <c r="U74" s="3"/>
       <c r="V74" s="4"/>
       <c r="W74" s="4"/>
@@ -3501,23 +4879,41 @@
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="19"/>
-      <c r="H75" s="19"/>
-      <c r="I75" s="19"/>
-      <c r="J75" s="19"/>
-      <c r="K75" s="17"/>
-      <c r="L75" s="17"/>
-      <c r="M75" s="17"/>
-      <c r="N75" s="17"/>
-      <c r="O75" s="17"/>
-      <c r="P75" s="17"/>
-      <c r="Q75" s="17"/>
-      <c r="R75" s="17"/>
-      <c r="S75" s="17"/>
-      <c r="T75" s="17"/>
+      <c r="D75" s="41"/>
+      <c r="E75" s="34"/>
+      <c r="F75" s="34"/>
+      <c r="G75" s="35"/>
+      <c r="H75" s="35"/>
+      <c r="I75" s="35"/>
+      <c r="J75" s="35"/>
+      <c r="K75" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L75" s="36"/>
+      <c r="M75" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="N75" s="15">
+        <v>0.82</v>
+      </c>
+      <c r="O75" s="15">
+        <v>0.92</v>
+      </c>
+      <c r="P75" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="Q75" s="15">
+        <v>0.91</v>
+      </c>
+      <c r="R75" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="S75" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="T75" s="15">
+        <v>0.78</v>
+      </c>
       <c r="U75" s="3"/>
       <c r="V75" s="4"/>
       <c r="W75" s="4"/>
@@ -3536,23 +4932,41 @@
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="19"/>
-      <c r="H76" s="19"/>
-      <c r="I76" s="19"/>
-      <c r="J76" s="19"/>
-      <c r="K76" s="15"/>
-      <c r="L76" s="15"/>
-      <c r="M76" s="17"/>
-      <c r="N76" s="17"/>
-      <c r="O76" s="17"/>
-      <c r="P76" s="17"/>
-      <c r="Q76" s="17"/>
-      <c r="R76" s="17"/>
-      <c r="S76" s="17"/>
-      <c r="T76" s="17"/>
+      <c r="D76" s="41"/>
+      <c r="E76" s="34"/>
+      <c r="F76" s="34"/>
+      <c r="G76" s="35"/>
+      <c r="H76" s="35"/>
+      <c r="I76" s="35"/>
+      <c r="J76" s="35"/>
+      <c r="K76" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L76" s="39"/>
+      <c r="M76" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="N76" s="16">
+        <v>0.77</v>
+      </c>
+      <c r="O76" s="16">
+        <v>0.79</v>
+      </c>
+      <c r="P76" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="Q76" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="R76" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="S76" s="16">
+        <v>0.73</v>
+      </c>
+      <c r="T76" s="16">
+        <v>0.74</v>
+      </c>
       <c r="U76" s="3"/>
       <c r="V76" s="4"/>
       <c r="W76" s="4"/>
@@ -3571,23 +4985,41 @@
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="19"/>
-      <c r="H77" s="19"/>
-      <c r="I77" s="19"/>
-      <c r="J77" s="19"/>
-      <c r="K77" s="17"/>
-      <c r="L77" s="17"/>
-      <c r="M77" s="17"/>
-      <c r="N77" s="17"/>
-      <c r="O77" s="17"/>
-      <c r="P77" s="17"/>
-      <c r="Q77" s="17"/>
-      <c r="R77" s="17"/>
-      <c r="S77" s="17"/>
-      <c r="T77" s="17"/>
+      <c r="D77" s="41"/>
+      <c r="E77" s="34"/>
+      <c r="F77" s="34"/>
+      <c r="G77" s="35"/>
+      <c r="H77" s="35"/>
+      <c r="I77" s="35"/>
+      <c r="J77" s="35"/>
+      <c r="K77" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L77" s="36"/>
+      <c r="M77" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="N77" s="17">
+        <v>0.83</v>
+      </c>
+      <c r="O77" s="15">
+        <v>0.92</v>
+      </c>
+      <c r="P77" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="Q77" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="R77" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="S77" s="15">
+        <v>0.85</v>
+      </c>
+      <c r="T77" s="17">
+        <v>0.79</v>
+      </c>
       <c r="U77" s="3"/>
       <c r="V77" s="4"/>
       <c r="W77" s="4"/>
@@ -3606,23 +5038,45 @@
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="19"/>
-      <c r="H78" s="19"/>
-      <c r="I78" s="19"/>
-      <c r="J78" s="19"/>
-      <c r="K78" s="15"/>
-      <c r="L78" s="15"/>
-      <c r="M78" s="17"/>
-      <c r="N78" s="17"/>
-      <c r="O78" s="17"/>
-      <c r="P78" s="17"/>
-      <c r="Q78" s="17"/>
-      <c r="R78" s="17"/>
-      <c r="S78" s="17"/>
-      <c r="T78" s="17"/>
+      <c r="D78" s="41"/>
+      <c r="E78" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="F78" s="34"/>
+      <c r="G78" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="H78" s="35"/>
+      <c r="I78" s="35"/>
+      <c r="J78" s="35"/>
+      <c r="K78" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L78" s="36"/>
+      <c r="M78" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="N78" s="15">
+        <v>0.82</v>
+      </c>
+      <c r="O78" s="15">
+        <v>0.91</v>
+      </c>
+      <c r="P78" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="Q78" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="R78" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="S78" s="15">
+        <v>0.85</v>
+      </c>
+      <c r="T78" s="15">
+        <v>0.78</v>
+      </c>
       <c r="U78" s="3"/>
       <c r="V78" s="4"/>
       <c r="W78" s="4"/>
@@ -3641,23 +5095,41 @@
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="19"/>
-      <c r="H79" s="19"/>
-      <c r="I79" s="19"/>
-      <c r="J79" s="19"/>
-      <c r="K79" s="17"/>
-      <c r="L79" s="17"/>
-      <c r="M79" s="17"/>
-      <c r="N79" s="17"/>
-      <c r="O79" s="17"/>
-      <c r="P79" s="17"/>
-      <c r="Q79" s="17"/>
-      <c r="R79" s="17"/>
-      <c r="S79" s="17"/>
-      <c r="T79" s="17"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="34"/>
+      <c r="F79" s="34"/>
+      <c r="G79" s="35"/>
+      <c r="H79" s="35"/>
+      <c r="I79" s="35"/>
+      <c r="J79" s="35"/>
+      <c r="K79" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L79" s="38"/>
+      <c r="M79" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="N79" s="16">
+        <v>0.81</v>
+      </c>
+      <c r="O79" s="16">
+        <v>0.89</v>
+      </c>
+      <c r="P79" s="16">
+        <v>0.86</v>
+      </c>
+      <c r="Q79" s="16">
+        <v>0.89</v>
+      </c>
+      <c r="R79" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="S79" s="16">
+        <v>0.83</v>
+      </c>
+      <c r="T79" s="16">
+        <v>0.77</v>
+      </c>
       <c r="U79" s="3"/>
       <c r="V79" s="4"/>
       <c r="W79" s="4"/>
@@ -3676,23 +5148,41 @@
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="19"/>
-      <c r="H80" s="19"/>
-      <c r="I80" s="19"/>
-      <c r="J80" s="19"/>
-      <c r="K80" s="15"/>
-      <c r="L80" s="15"/>
-      <c r="M80" s="17"/>
-      <c r="N80" s="17"/>
-      <c r="O80" s="17"/>
-      <c r="P80" s="17"/>
-      <c r="Q80" s="17"/>
-      <c r="R80" s="17"/>
-      <c r="S80" s="17"/>
-      <c r="T80" s="17"/>
+      <c r="D80" s="41"/>
+      <c r="E80" s="34"/>
+      <c r="F80" s="34"/>
+      <c r="G80" s="35"/>
+      <c r="H80" s="35"/>
+      <c r="I80" s="35"/>
+      <c r="J80" s="35"/>
+      <c r="K80" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L80" s="36"/>
+      <c r="M80" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="N80" s="15">
+        <v>0.82</v>
+      </c>
+      <c r="O80" s="15">
+        <v>0.92</v>
+      </c>
+      <c r="P80" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="Q80" s="15">
+        <v>0.91</v>
+      </c>
+      <c r="R80" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="S80" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="T80" s="15">
+        <v>0.78</v>
+      </c>
       <c r="U80" s="3"/>
       <c r="V80" s="4"/>
       <c r="W80" s="4"/>
@@ -3711,23 +5201,41 @@
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="19"/>
-      <c r="H81" s="19"/>
-      <c r="I81" s="19"/>
-      <c r="J81" s="19"/>
-      <c r="K81" s="17"/>
-      <c r="L81" s="17"/>
-      <c r="M81" s="17"/>
-      <c r="N81" s="17"/>
-      <c r="O81" s="17"/>
-      <c r="P81" s="17"/>
-      <c r="Q81" s="17"/>
-      <c r="R81" s="17"/>
-      <c r="S81" s="17"/>
-      <c r="T81" s="17"/>
+      <c r="D81" s="41"/>
+      <c r="E81" s="34"/>
+      <c r="F81" s="34"/>
+      <c r="G81" s="35"/>
+      <c r="H81" s="35"/>
+      <c r="I81" s="35"/>
+      <c r="J81" s="35"/>
+      <c r="K81" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L81" s="39"/>
+      <c r="M81" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="N81" s="16">
+        <v>0.77</v>
+      </c>
+      <c r="O81" s="16">
+        <v>0.79</v>
+      </c>
+      <c r="P81" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="Q81" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="R81" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="S81" s="16">
+        <v>0.73</v>
+      </c>
+      <c r="T81" s="16">
+        <v>0.74</v>
+      </c>
       <c r="U81" s="3"/>
       <c r="V81" s="4"/>
       <c r="W81" s="4"/>
@@ -3746,23 +5254,41 @@
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="19"/>
-      <c r="H82" s="19"/>
-      <c r="I82" s="19"/>
-      <c r="J82" s="19"/>
-      <c r="K82" s="15"/>
-      <c r="L82" s="15"/>
-      <c r="M82" s="17"/>
-      <c r="N82" s="17"/>
-      <c r="O82" s="17"/>
-      <c r="P82" s="17"/>
-      <c r="Q82" s="17"/>
-      <c r="R82" s="16"/>
-      <c r="S82" s="17"/>
-      <c r="T82" s="17"/>
+      <c r="D82" s="41"/>
+      <c r="E82" s="34"/>
+      <c r="F82" s="34"/>
+      <c r="G82" s="35"/>
+      <c r="H82" s="35"/>
+      <c r="I82" s="35"/>
+      <c r="J82" s="35"/>
+      <c r="K82" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L82" s="36"/>
+      <c r="M82" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="N82" s="15">
+        <v>0.83</v>
+      </c>
+      <c r="O82" s="15">
+        <v>0.92</v>
+      </c>
+      <c r="P82" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="Q82" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="R82" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="S82" s="15">
+        <v>0.85</v>
+      </c>
+      <c r="T82" s="17">
+        <v>0.79</v>
+      </c>
       <c r="U82" s="3"/>
       <c r="V82" s="4"/>
       <c r="W82" s="4"/>
@@ -3781,23 +5307,45 @@
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="19"/>
-      <c r="H83" s="19"/>
-      <c r="I83" s="19"/>
-      <c r="J83" s="19"/>
-      <c r="K83" s="17"/>
-      <c r="L83" s="17"/>
-      <c r="M83" s="17"/>
-      <c r="N83" s="17"/>
-      <c r="O83" s="17"/>
-      <c r="P83" s="17"/>
-      <c r="Q83" s="17"/>
-      <c r="R83" s="17"/>
-      <c r="S83" s="17"/>
-      <c r="T83" s="17"/>
+      <c r="D83" s="41"/>
+      <c r="E83" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F83" s="34"/>
+      <c r="G83" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H83" s="35"/>
+      <c r="I83" s="35"/>
+      <c r="J83" s="35"/>
+      <c r="K83" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="L83" s="36"/>
+      <c r="M83" s="30">
+        <v>0.96</v>
+      </c>
+      <c r="N83" s="30">
+        <v>0.81</v>
+      </c>
+      <c r="O83" s="30">
+        <v>0.98</v>
+      </c>
+      <c r="P83" s="30">
+        <v>0.88</v>
+      </c>
+      <c r="Q83" s="30">
+        <v>0.97</v>
+      </c>
+      <c r="R83" s="30">
+        <v>0.86</v>
+      </c>
+      <c r="S83" s="30">
+        <v>0.96</v>
+      </c>
+      <c r="T83" s="30">
+        <v>0.76</v>
+      </c>
       <c r="U83" s="3"/>
       <c r="V83" s="4"/>
       <c r="W83" s="4"/>
@@ -3816,23 +5364,41 @@
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="19"/>
-      <c r="H84" s="19"/>
-      <c r="I84" s="19"/>
-      <c r="J84" s="19"/>
-      <c r="K84" s="15"/>
-      <c r="L84" s="15"/>
-      <c r="M84" s="17"/>
-      <c r="N84" s="17"/>
-      <c r="O84" s="17"/>
-      <c r="P84" s="17"/>
-      <c r="Q84" s="17"/>
-      <c r="R84" s="17"/>
-      <c r="S84" s="17"/>
-      <c r="T84" s="17"/>
+      <c r="D84" s="41"/>
+      <c r="E84" s="34"/>
+      <c r="F84" s="34"/>
+      <c r="G84" s="35"/>
+      <c r="H84" s="35"/>
+      <c r="I84" s="35"/>
+      <c r="J84" s="35"/>
+      <c r="K84" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L84" s="38"/>
+      <c r="M84" s="25">
+        <v>0.85</v>
+      </c>
+      <c r="N84" s="26">
+        <v>0.83</v>
+      </c>
+      <c r="O84" s="25">
+        <v>0.89</v>
+      </c>
+      <c r="P84" s="25">
+        <v>0.86</v>
+      </c>
+      <c r="Q84" s="25">
+        <v>0.9</v>
+      </c>
+      <c r="R84" s="25">
+        <v>0.9</v>
+      </c>
+      <c r="S84" s="25">
+        <v>0.83</v>
+      </c>
+      <c r="T84" s="26">
+        <v>0.8</v>
+      </c>
       <c r="U84" s="3"/>
       <c r="V84" s="4"/>
       <c r="W84" s="4"/>
@@ -3851,23 +5417,41 @@
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="19"/>
-      <c r="H85" s="19"/>
-      <c r="I85" s="19"/>
-      <c r="J85" s="19"/>
-      <c r="K85" s="17"/>
-      <c r="L85" s="17"/>
-      <c r="M85" s="17"/>
-      <c r="N85" s="17"/>
-      <c r="O85" s="17"/>
-      <c r="P85" s="17"/>
-      <c r="Q85" s="17"/>
-      <c r="R85" s="17"/>
-      <c r="S85" s="17"/>
-      <c r="T85" s="17"/>
+      <c r="D85" s="41"/>
+      <c r="E85" s="34"/>
+      <c r="F85" s="34"/>
+      <c r="G85" s="35"/>
+      <c r="H85" s="35"/>
+      <c r="I85" s="35"/>
+      <c r="J85" s="35"/>
+      <c r="K85" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L85" s="36"/>
+      <c r="M85" s="24">
+        <v>0.84</v>
+      </c>
+      <c r="N85" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="O85" s="24">
+        <v>0.89</v>
+      </c>
+      <c r="P85" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q85" s="24">
+        <v>0.88</v>
+      </c>
+      <c r="R85" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="S85" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="T85" s="24" t="s">
+        <v>31</v>
+      </c>
       <c r="U85" s="3"/>
       <c r="V85" s="4"/>
       <c r="W85" s="4"/>
@@ -3886,23 +5470,41 @@
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="19"/>
-      <c r="H86" s="19"/>
-      <c r="I86" s="19"/>
-      <c r="J86" s="19"/>
-      <c r="K86" s="15"/>
-      <c r="L86" s="15"/>
-      <c r="M86" s="17"/>
-      <c r="N86" s="17"/>
-      <c r="O86" s="17"/>
-      <c r="P86" s="17"/>
-      <c r="Q86" s="17"/>
-      <c r="R86" s="17"/>
-      <c r="S86" s="17"/>
-      <c r="T86" s="17"/>
+      <c r="D86" s="41"/>
+      <c r="E86" s="34"/>
+      <c r="F86" s="34"/>
+      <c r="G86" s="35"/>
+      <c r="H86" s="35"/>
+      <c r="I86" s="35"/>
+      <c r="J86" s="35"/>
+      <c r="K86" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L86" s="39"/>
+      <c r="M86" s="25">
+        <v>0.71</v>
+      </c>
+      <c r="N86" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="O86" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="P86" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q86" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="R86" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="S86" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="T86" s="25" t="s">
+        <v>44</v>
+      </c>
       <c r="U86" s="3"/>
       <c r="V86" s="4"/>
       <c r="W86" s="4"/>
@@ -3919,23 +5521,41 @@
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.35">
       <c r="C87" s="3"/>
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="19"/>
-      <c r="H87" s="19"/>
-      <c r="I87" s="19"/>
-      <c r="J87" s="19"/>
-      <c r="K87" s="17"/>
-      <c r="L87" s="17"/>
-      <c r="M87" s="17"/>
-      <c r="N87" s="17"/>
-      <c r="O87" s="17"/>
-      <c r="P87" s="17"/>
-      <c r="Q87" s="17"/>
-      <c r="R87" s="17"/>
-      <c r="S87" s="17"/>
-      <c r="T87" s="17"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="34"/>
+      <c r="F87" s="34"/>
+      <c r="G87" s="35"/>
+      <c r="H87" s="35"/>
+      <c r="I87" s="35"/>
+      <c r="J87" s="35"/>
+      <c r="K87" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="L87" s="36"/>
+      <c r="M87" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="N87" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="O87" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="P87" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q87" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="R87" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="S87" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="T87" s="24" t="s">
+        <v>54</v>
+      </c>
       <c r="U87" s="3"/>
       <c r="V87" s="4"/>
       <c r="W87" s="4"/>
@@ -3952,23 +5572,23 @@
     </row>
     <row r="88" spans="1:33" x14ac:dyDescent="0.35">
       <c r="C88" s="3"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="19"/>
-      <c r="H88" s="19"/>
-      <c r="I88" s="19"/>
-      <c r="J88" s="19"/>
-      <c r="K88" s="15"/>
-      <c r="L88" s="15"/>
-      <c r="M88" s="17"/>
-      <c r="N88" s="17"/>
-      <c r="O88" s="17"/>
-      <c r="P88" s="17"/>
-      <c r="Q88" s="17"/>
-      <c r="R88" s="17"/>
-      <c r="S88" s="17"/>
-      <c r="T88" s="17"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="14"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+      <c r="K88" s="12"/>
+      <c r="L88" s="12"/>
+      <c r="M88" s="13"/>
+      <c r="N88" s="13"/>
+      <c r="O88" s="13"/>
+      <c r="P88" s="13"/>
+      <c r="Q88" s="13"/>
+      <c r="R88" s="13"/>
+      <c r="S88" s="13"/>
+      <c r="T88" s="13"/>
       <c r="U88" s="3"/>
       <c r="V88" s="4"/>
       <c r="W88" s="4"/>
@@ -3985,23 +5605,23 @@
     </row>
     <row r="89" spans="1:33" x14ac:dyDescent="0.35">
       <c r="C89" s="3"/>
-      <c r="D89" s="14"/>
-      <c r="E89" s="14"/>
-      <c r="F89" s="14"/>
-      <c r="G89" s="19"/>
-      <c r="H89" s="19"/>
-      <c r="I89" s="19"/>
-      <c r="J89" s="19"/>
-      <c r="K89" s="17"/>
-      <c r="L89" s="17"/>
-      <c r="M89" s="17"/>
-      <c r="N89" s="17"/>
-      <c r="O89" s="17"/>
-      <c r="P89" s="17"/>
-      <c r="Q89" s="17"/>
-      <c r="R89" s="17"/>
-      <c r="S89" s="17"/>
-      <c r="T89" s="17"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="14"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="14"/>
+      <c r="K89" s="13"/>
+      <c r="L89" s="13"/>
+      <c r="M89" s="13"/>
+      <c r="N89" s="13"/>
+      <c r="O89" s="13"/>
+      <c r="P89" s="13"/>
+      <c r="Q89" s="13"/>
+      <c r="R89" s="13"/>
+      <c r="S89" s="13"/>
+      <c r="T89" s="13"/>
       <c r="U89" s="3"/>
       <c r="V89" s="4"/>
       <c r="W89" s="4"/>
@@ -4018,23 +5638,23 @@
     </row>
     <row r="90" spans="1:33" x14ac:dyDescent="0.35">
       <c r="C90" s="3"/>
-      <c r="D90" s="14"/>
-      <c r="E90" s="14"/>
-      <c r="F90" s="14"/>
-      <c r="G90" s="14"/>
-      <c r="H90" s="14"/>
-      <c r="I90" s="14"/>
-      <c r="J90" s="14"/>
-      <c r="K90" s="15"/>
-      <c r="L90" s="15"/>
-      <c r="M90" s="17"/>
-      <c r="N90" s="17"/>
-      <c r="O90" s="17"/>
-      <c r="P90" s="17"/>
-      <c r="Q90" s="17"/>
-      <c r="R90" s="17"/>
-      <c r="S90" s="17"/>
-      <c r="T90" s="17"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="11"/>
+      <c r="I90" s="11"/>
+      <c r="J90" s="11"/>
+      <c r="K90" s="12"/>
+      <c r="L90" s="12"/>
+      <c r="M90" s="13"/>
+      <c r="N90" s="13"/>
+      <c r="O90" s="13"/>
+      <c r="P90" s="13"/>
+      <c r="Q90" s="13"/>
+      <c r="R90" s="13"/>
+      <c r="S90" s="13"/>
+      <c r="T90" s="13"/>
       <c r="U90" s="3"/>
       <c r="V90" s="4"/>
       <c r="W90" s="4"/>
@@ -4051,23 +5671,23 @@
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.35">
       <c r="C91" s="3"/>
-      <c r="D91" s="14"/>
-      <c r="E91" s="14"/>
-      <c r="F91" s="14"/>
-      <c r="G91" s="14"/>
-      <c r="H91" s="14"/>
-      <c r="I91" s="14"/>
-      <c r="J91" s="14"/>
-      <c r="K91" s="15"/>
-      <c r="L91" s="15"/>
-      <c r="M91" s="15"/>
-      <c r="N91" s="15"/>
-      <c r="O91" s="15"/>
-      <c r="P91" s="15"/>
-      <c r="Q91" s="15"/>
-      <c r="R91" s="15"/>
-      <c r="S91" s="15"/>
-      <c r="T91" s="15"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="11"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="11"/>
+      <c r="K91" s="12"/>
+      <c r="L91" s="12"/>
+      <c r="M91" s="12"/>
+      <c r="N91" s="12"/>
+      <c r="O91" s="12"/>
+      <c r="P91" s="12"/>
+      <c r="Q91" s="12"/>
+      <c r="R91" s="12"/>
+      <c r="S91" s="12"/>
+      <c r="T91" s="12"/>
       <c r="U91" s="3"/>
       <c r="V91" s="4"/>
       <c r="W91" s="4"/>
@@ -4084,23 +5704,23 @@
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.35">
       <c r="C92" s="3"/>
-      <c r="D92" s="10"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="10"/>
-      <c r="H92" s="10"/>
-      <c r="I92" s="10"/>
-      <c r="J92" s="10"/>
-      <c r="K92" s="11"/>
-      <c r="L92" s="11"/>
-      <c r="M92" s="12"/>
-      <c r="N92" s="12"/>
-      <c r="O92" s="12"/>
-      <c r="P92" s="12"/>
-      <c r="Q92" s="12"/>
-      <c r="R92" s="12"/>
-      <c r="S92" s="12"/>
-      <c r="T92" s="12"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="8"/>
+      <c r="J92" s="8"/>
+      <c r="K92" s="9"/>
+      <c r="L92" s="9"/>
+      <c r="M92" s="10"/>
+      <c r="N92" s="10"/>
+      <c r="O92" s="10"/>
+      <c r="P92" s="10"/>
+      <c r="Q92" s="10"/>
+      <c r="R92" s="10"/>
+      <c r="S92" s="10"/>
+      <c r="T92" s="10"/>
       <c r="U92" s="3"/>
       <c r="V92" s="4"/>
       <c r="W92" s="4"/>
@@ -4117,23 +5737,23 @@
     </row>
     <row r="93" spans="1:33" x14ac:dyDescent="0.35">
       <c r="C93" s="3"/>
-      <c r="D93" s="10"/>
-      <c r="E93" s="10"/>
-      <c r="F93" s="10"/>
-      <c r="G93" s="10"/>
-      <c r="H93" s="10"/>
-      <c r="I93" s="10"/>
-      <c r="J93" s="10"/>
-      <c r="K93" s="11"/>
-      <c r="L93" s="11"/>
-      <c r="M93" s="11"/>
-      <c r="N93" s="11"/>
-      <c r="O93" s="11"/>
-      <c r="P93" s="11"/>
-      <c r="Q93" s="11"/>
-      <c r="R93" s="11"/>
-      <c r="S93" s="11"/>
-      <c r="T93" s="11"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="9"/>
+      <c r="L93" s="9"/>
+      <c r="M93" s="9"/>
+      <c r="N93" s="9"/>
+      <c r="O93" s="9"/>
+      <c r="P93" s="9"/>
+      <c r="Q93" s="9"/>
+      <c r="R93" s="9"/>
+      <c r="S93" s="9"/>
+      <c r="T93" s="9"/>
       <c r="U93" s="3"/>
       <c r="V93" s="4"/>
       <c r="W93" s="4"/>
@@ -4150,23 +5770,23 @@
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.35">
       <c r="C94" s="3"/>
-      <c r="D94" s="10"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="11"/>
-      <c r="L94" s="11"/>
-      <c r="M94" s="12"/>
-      <c r="N94" s="12"/>
-      <c r="O94" s="12"/>
-      <c r="P94" s="12"/>
-      <c r="Q94" s="12"/>
-      <c r="R94" s="12"/>
-      <c r="S94" s="12"/>
-      <c r="T94" s="12"/>
+      <c r="D94" s="8"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="8"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="9"/>
+      <c r="L94" s="9"/>
+      <c r="M94" s="10"/>
+      <c r="N94" s="10"/>
+      <c r="O94" s="10"/>
+      <c r="P94" s="10"/>
+      <c r="Q94" s="10"/>
+      <c r="R94" s="10"/>
+      <c r="S94" s="10"/>
+      <c r="T94" s="10"/>
       <c r="U94" s="3"/>
       <c r="V94" s="4"/>
       <c r="W94" s="4"/>
@@ -4183,23 +5803,23 @@
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.35">
       <c r="C95" s="3"/>
-      <c r="D95" s="10"/>
-      <c r="E95" s="10"/>
-      <c r="F95" s="10"/>
-      <c r="G95" s="10"/>
-      <c r="H95" s="10"/>
-      <c r="I95" s="10"/>
-      <c r="J95" s="10"/>
-      <c r="K95" s="11"/>
-      <c r="L95" s="11"/>
-      <c r="M95" s="11"/>
-      <c r="N95" s="11"/>
-      <c r="O95" s="11"/>
-      <c r="P95" s="11"/>
-      <c r="Q95" s="11"/>
-      <c r="R95" s="11"/>
-      <c r="S95" s="11"/>
-      <c r="T95" s="11"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="8"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="9"/>
+      <c r="L95" s="9"/>
+      <c r="M95" s="9"/>
+      <c r="N95" s="9"/>
+      <c r="O95" s="9"/>
+      <c r="P95" s="9"/>
+      <c r="Q95" s="9"/>
+      <c r="R95" s="9"/>
+      <c r="S95" s="9"/>
+      <c r="T95" s="9"/>
       <c r="U95" s="3"/>
       <c r="V95" s="4"/>
       <c r="W95" s="4"/>
@@ -4550,28 +6170,28 @@
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
-      <c r="H108" s="7"/>
-      <c r="I108" s="7"/>
-      <c r="J108" s="7"/>
-      <c r="K108" s="7"/>
-      <c r="L108" s="7"/>
-      <c r="M108" s="7"/>
-      <c r="N108" s="7"/>
-      <c r="O108" s="7"/>
-      <c r="P108" s="7"/>
-      <c r="Q108" s="7"/>
-      <c r="R108" s="7"/>
-      <c r="S108" s="7"/>
-      <c r="T108" s="7"/>
-      <c r="U108" s="7"/>
-      <c r="V108" s="7"/>
-      <c r="W108" s="7"/>
-      <c r="X108" s="7"/>
-      <c r="Y108" s="7"/>
-      <c r="Z108" s="7"/>
-      <c r="AA108" s="7"/>
-      <c r="AB108" s="7"/>
-      <c r="AC108" s="7"/>
+      <c r="H108" s="5"/>
+      <c r="I108" s="5"/>
+      <c r="J108" s="5"/>
+      <c r="K108" s="5"/>
+      <c r="L108" s="5"/>
+      <c r="M108" s="5"/>
+      <c r="N108" s="5"/>
+      <c r="O108" s="5"/>
+      <c r="P108" s="5"/>
+      <c r="Q108" s="5"/>
+      <c r="R108" s="5"/>
+      <c r="S108" s="5"/>
+      <c r="T108" s="5"/>
+      <c r="U108" s="5"/>
+      <c r="V108" s="5"/>
+      <c r="W108" s="5"/>
+      <c r="X108" s="5"/>
+      <c r="Y108" s="5"/>
+      <c r="Z108" s="5"/>
+      <c r="AA108" s="5"/>
+      <c r="AB108" s="5"/>
+      <c r="AC108" s="5"/>
     </row>
     <row r="109" spans="3:33" x14ac:dyDescent="0.35">
       <c r="C109" s="3"/>
@@ -4579,509 +6199,490 @@
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
-      <c r="H109" s="7"/>
-      <c r="I109" s="7"/>
-      <c r="J109" s="7"/>
-      <c r="K109" s="7"/>
-      <c r="L109" s="7"/>
-      <c r="M109" s="7"/>
-      <c r="N109" s="7"/>
-      <c r="O109" s="7"/>
-      <c r="P109" s="7"/>
-      <c r="Q109" s="7"/>
-      <c r="R109" s="7"/>
-      <c r="S109" s="7"/>
-      <c r="T109" s="7"/>
-      <c r="U109" s="7"/>
-      <c r="V109" s="7"/>
-      <c r="W109" s="7"/>
-      <c r="X109" s="7"/>
-      <c r="Y109" s="7"/>
-      <c r="Z109" s="7"/>
-      <c r="AA109" s="7"/>
-      <c r="AB109" s="7"/>
-      <c r="AC109" s="7"/>
+      <c r="H109" s="5"/>
+      <c r="I109" s="5"/>
+      <c r="J109" s="5"/>
+      <c r="K109" s="5"/>
+      <c r="L109" s="5"/>
+      <c r="M109" s="5"/>
+      <c r="N109" s="5"/>
+      <c r="O109" s="5"/>
+      <c r="P109" s="5"/>
+      <c r="Q109" s="5"/>
+      <c r="R109" s="5"/>
+      <c r="S109" s="5"/>
+      <c r="T109" s="5"/>
+      <c r="U109" s="5"/>
+      <c r="V109" s="5"/>
+      <c r="W109" s="5"/>
+      <c r="X109" s="5"/>
+      <c r="Y109" s="5"/>
+      <c r="Z109" s="5"/>
+      <c r="AA109" s="5"/>
+      <c r="AB109" s="5"/>
+      <c r="AC109" s="5"/>
     </row>
     <row r="110" spans="3:33" x14ac:dyDescent="0.35">
-      <c r="H110" s="7"/>
-      <c r="I110" s="7"/>
-      <c r="J110" s="7"/>
-      <c r="K110" s="7"/>
-      <c r="L110" s="7"/>
-      <c r="M110" s="7"/>
-      <c r="N110" s="7"/>
-      <c r="O110" s="7"/>
-      <c r="P110" s="7"/>
-      <c r="Q110" s="7"/>
-      <c r="R110" s="7"/>
-      <c r="S110" s="7"/>
-      <c r="T110" s="7"/>
-      <c r="U110" s="7"/>
-      <c r="V110" s="7"/>
-      <c r="W110" s="7"/>
-      <c r="X110" s="7"/>
-      <c r="Y110" s="7"/>
-      <c r="Z110" s="7"/>
-      <c r="AA110" s="7"/>
-      <c r="AB110" s="7"/>
-      <c r="AC110" s="7"/>
+      <c r="H110" s="5"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5"/>
+      <c r="L110" s="5"/>
+      <c r="M110" s="5"/>
+      <c r="N110" s="5"/>
+      <c r="O110" s="5"/>
+      <c r="P110" s="5"/>
+      <c r="Q110" s="5"/>
+      <c r="R110" s="5"/>
+      <c r="S110" s="5"/>
+      <c r="T110" s="5"/>
+      <c r="U110" s="5"/>
+      <c r="V110" s="5"/>
+      <c r="W110" s="5"/>
+      <c r="X110" s="5"/>
+      <c r="Y110" s="5"/>
+      <c r="Z110" s="5"/>
+      <c r="AA110" s="5"/>
+      <c r="AB110" s="5"/>
+      <c r="AC110" s="5"/>
     </row>
     <row r="111" spans="3:33" x14ac:dyDescent="0.35">
-      <c r="H111" s="7"/>
-      <c r="I111" s="7"/>
-      <c r="J111" s="7"/>
-      <c r="K111" s="7"/>
-      <c r="L111" s="7"/>
-      <c r="M111" s="7"/>
-      <c r="N111" s="7"/>
-      <c r="O111" s="7"/>
-      <c r="P111" s="7"/>
-      <c r="Q111" s="7"/>
-      <c r="R111" s="7"/>
-      <c r="S111" s="7"/>
-      <c r="T111" s="7"/>
-      <c r="U111" s="7"/>
-      <c r="V111" s="7"/>
-      <c r="W111" s="7"/>
-      <c r="X111" s="7"/>
-      <c r="Y111" s="7"/>
-      <c r="Z111" s="7"/>
-      <c r="AA111" s="7"/>
-      <c r="AB111" s="7"/>
-      <c r="AC111" s="7"/>
+      <c r="H111" s="5"/>
+      <c r="I111" s="5"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
+      <c r="L111" s="5"/>
+      <c r="M111" s="5"/>
+      <c r="N111" s="5"/>
+      <c r="O111" s="5"/>
+      <c r="P111" s="5"/>
+      <c r="Q111" s="5"/>
+      <c r="R111" s="5"/>
+      <c r="S111" s="5"/>
+      <c r="T111" s="5"/>
+      <c r="U111" s="5"/>
+      <c r="V111" s="5"/>
+      <c r="W111" s="5"/>
+      <c r="X111" s="5"/>
+      <c r="Y111" s="5"/>
+      <c r="Z111" s="5"/>
+      <c r="AA111" s="5"/>
+      <c r="AB111" s="5"/>
+      <c r="AC111" s="5"/>
     </row>
     <row r="112" spans="3:33" x14ac:dyDescent="0.35">
-      <c r="H112" s="7"/>
-      <c r="I112" s="8"/>
-      <c r="J112" s="8"/>
-      <c r="K112" s="8"/>
-      <c r="L112" s="8"/>
-      <c r="M112" s="8"/>
-      <c r="N112" s="8"/>
-      <c r="O112" s="9"/>
-      <c r="P112" s="9"/>
-      <c r="Q112" s="7"/>
-      <c r="R112" s="7"/>
-      <c r="S112" s="7"/>
-      <c r="T112" s="7"/>
-      <c r="U112" s="7"/>
-      <c r="V112" s="7"/>
-      <c r="W112" s="7"/>
-      <c r="X112" s="7"/>
-      <c r="Y112" s="7"/>
-      <c r="Z112" s="7"/>
-      <c r="AA112" s="7"/>
-      <c r="AB112" s="7"/>
-      <c r="AC112" s="7"/>
+      <c r="H112" s="5"/>
+      <c r="I112" s="6"/>
+      <c r="J112" s="6"/>
+      <c r="K112" s="6"/>
+      <c r="L112" s="6"/>
+      <c r="M112" s="6"/>
+      <c r="N112" s="6"/>
+      <c r="O112" s="7"/>
+      <c r="P112" s="7"/>
+      <c r="Q112" s="5"/>
+      <c r="R112" s="5"/>
+      <c r="S112" s="5"/>
+      <c r="T112" s="5"/>
+      <c r="U112" s="5"/>
+      <c r="V112" s="5"/>
+      <c r="W112" s="5"/>
+      <c r="X112" s="5"/>
+      <c r="Y112" s="5"/>
+      <c r="Z112" s="5"/>
+      <c r="AA112" s="5"/>
+      <c r="AB112" s="5"/>
+      <c r="AC112" s="5"/>
     </row>
     <row r="113" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H113" s="7"/>
-      <c r="I113" s="8"/>
-      <c r="J113" s="8"/>
-      <c r="K113" s="8"/>
-      <c r="L113" s="8"/>
-      <c r="M113" s="8"/>
-      <c r="N113" s="8"/>
-      <c r="O113" s="9"/>
-      <c r="P113" s="9"/>
-      <c r="Q113" s="9"/>
-      <c r="R113" s="9"/>
-      <c r="S113" s="9"/>
-      <c r="T113" s="9"/>
-      <c r="U113" s="9"/>
-      <c r="V113" s="9"/>
-      <c r="W113" s="9"/>
-      <c r="X113" s="9"/>
-      <c r="Y113" s="7"/>
-      <c r="Z113" s="7"/>
-      <c r="AA113" s="7"/>
-      <c r="AB113" s="7"/>
-      <c r="AC113" s="7"/>
+      <c r="H113" s="5"/>
+      <c r="I113" s="6"/>
+      <c r="J113" s="6"/>
+      <c r="K113" s="6"/>
+      <c r="L113" s="6"/>
+      <c r="M113" s="6"/>
+      <c r="N113" s="6"/>
+      <c r="O113" s="7"/>
+      <c r="P113" s="7"/>
+      <c r="Q113" s="7"/>
+      <c r="R113" s="7"/>
+      <c r="S113" s="7"/>
+      <c r="T113" s="7"/>
+      <c r="U113" s="7"/>
+      <c r="V113" s="7"/>
+      <c r="W113" s="7"/>
+      <c r="X113" s="7"/>
+      <c r="Y113" s="5"/>
+      <c r="Z113" s="5"/>
+      <c r="AA113" s="5"/>
+      <c r="AB113" s="5"/>
+      <c r="AC113" s="5"/>
     </row>
     <row r="114" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H114" s="7"/>
-      <c r="I114" s="8"/>
-      <c r="J114" s="8"/>
-      <c r="K114" s="8"/>
-      <c r="L114" s="8"/>
-      <c r="M114" s="8"/>
-      <c r="N114" s="8"/>
-      <c r="O114" s="9"/>
-      <c r="P114" s="9"/>
-      <c r="Q114" s="7"/>
-      <c r="R114" s="7"/>
-      <c r="S114" s="7"/>
-      <c r="T114" s="7"/>
-      <c r="U114" s="7"/>
-      <c r="V114" s="7"/>
-      <c r="W114" s="7"/>
-      <c r="X114" s="7"/>
-      <c r="Y114" s="7"/>
-      <c r="Z114" s="7"/>
-      <c r="AA114" s="7"/>
-      <c r="AB114" s="7"/>
-      <c r="AC114" s="7"/>
+      <c r="H114" s="5"/>
+      <c r="I114" s="6"/>
+      <c r="J114" s="6"/>
+      <c r="K114" s="6"/>
+      <c r="L114" s="6"/>
+      <c r="M114" s="6"/>
+      <c r="N114" s="6"/>
+      <c r="O114" s="7"/>
+      <c r="P114" s="7"/>
+      <c r="Q114" s="5"/>
+      <c r="R114" s="5"/>
+      <c r="S114" s="5"/>
+      <c r="T114" s="5"/>
+      <c r="U114" s="5"/>
+      <c r="V114" s="5"/>
+      <c r="W114" s="5"/>
+      <c r="X114" s="5"/>
+      <c r="Y114" s="5"/>
+      <c r="Z114" s="5"/>
+      <c r="AA114" s="5"/>
+      <c r="AB114" s="5"/>
+      <c r="AC114" s="5"/>
     </row>
     <row r="115" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H115" s="7"/>
-      <c r="I115" s="8"/>
-      <c r="J115" s="8"/>
-      <c r="K115" s="8"/>
-      <c r="L115" s="8"/>
-      <c r="M115" s="8"/>
-      <c r="N115" s="8"/>
-      <c r="O115" s="9"/>
-      <c r="P115" s="9"/>
-      <c r="Q115" s="9"/>
-      <c r="R115" s="9"/>
-      <c r="S115" s="9"/>
-      <c r="T115" s="9"/>
-      <c r="U115" s="9"/>
-      <c r="V115" s="9"/>
-      <c r="W115" s="9"/>
-      <c r="X115" s="9"/>
-      <c r="Y115" s="7"/>
-      <c r="Z115" s="7"/>
-      <c r="AA115" s="7"/>
-      <c r="AB115" s="7"/>
-      <c r="AC115" s="7"/>
+      <c r="H115" s="5"/>
+      <c r="I115" s="6"/>
+      <c r="J115" s="6"/>
+      <c r="K115" s="6"/>
+      <c r="L115" s="6"/>
+      <c r="M115" s="6"/>
+      <c r="N115" s="6"/>
+      <c r="O115" s="7"/>
+      <c r="P115" s="7"/>
+      <c r="Q115" s="7"/>
+      <c r="R115" s="7"/>
+      <c r="S115" s="7"/>
+      <c r="T115" s="7"/>
+      <c r="U115" s="7"/>
+      <c r="V115" s="7"/>
+      <c r="W115" s="7"/>
+      <c r="X115" s="7"/>
+      <c r="Y115" s="5"/>
+      <c r="Z115" s="5"/>
+      <c r="AA115" s="5"/>
+      <c r="AB115" s="5"/>
+      <c r="AC115" s="5"/>
     </row>
     <row r="116" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H116" s="7"/>
-      <c r="I116" s="8"/>
-      <c r="J116" s="8"/>
-      <c r="K116" s="8"/>
-      <c r="L116" s="8"/>
-      <c r="M116" s="8"/>
-      <c r="N116" s="8"/>
-      <c r="O116" s="9"/>
-      <c r="P116" s="9"/>
-      <c r="Q116" s="7"/>
-      <c r="R116" s="7"/>
-      <c r="S116" s="7"/>
-      <c r="T116" s="7"/>
-      <c r="U116" s="7"/>
-      <c r="V116" s="7"/>
-      <c r="W116" s="7"/>
-      <c r="X116" s="7"/>
-      <c r="Y116" s="7"/>
-      <c r="Z116" s="7"/>
-      <c r="AA116" s="7"/>
-      <c r="AB116" s="7"/>
-      <c r="AC116" s="7"/>
+      <c r="H116" s="5"/>
+      <c r="I116" s="6"/>
+      <c r="J116" s="6"/>
+      <c r="K116" s="6"/>
+      <c r="L116" s="6"/>
+      <c r="M116" s="6"/>
+      <c r="N116" s="6"/>
+      <c r="O116" s="7"/>
+      <c r="P116" s="7"/>
+      <c r="Q116" s="5"/>
+      <c r="R116" s="5"/>
+      <c r="S116" s="5"/>
+      <c r="T116" s="5"/>
+      <c r="U116" s="5"/>
+      <c r="V116" s="5"/>
+      <c r="W116" s="5"/>
+      <c r="X116" s="5"/>
+      <c r="Y116" s="5"/>
+      <c r="Z116" s="5"/>
+      <c r="AA116" s="5"/>
+      <c r="AB116" s="5"/>
+      <c r="AC116" s="5"/>
     </row>
     <row r="117" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H117" s="7"/>
-      <c r="I117" s="8"/>
-      <c r="J117" s="8"/>
-      <c r="K117" s="8"/>
-      <c r="L117" s="8"/>
-      <c r="M117" s="8"/>
-      <c r="N117" s="8"/>
-      <c r="O117" s="9"/>
-      <c r="P117" s="9"/>
-      <c r="Q117" s="9"/>
-      <c r="R117" s="9"/>
-      <c r="S117" s="9"/>
-      <c r="T117" s="9"/>
-      <c r="U117" s="9"/>
-      <c r="V117" s="9"/>
-      <c r="W117" s="9"/>
-      <c r="X117" s="9"/>
-      <c r="Y117" s="7"/>
-      <c r="Z117" s="7"/>
-      <c r="AA117" s="7"/>
-      <c r="AB117" s="7"/>
-      <c r="AC117" s="7"/>
+      <c r="H117" s="5"/>
+      <c r="I117" s="6"/>
+      <c r="J117" s="6"/>
+      <c r="K117" s="6"/>
+      <c r="L117" s="6"/>
+      <c r="M117" s="6"/>
+      <c r="N117" s="6"/>
+      <c r="O117" s="7"/>
+      <c r="P117" s="7"/>
+      <c r="Q117" s="7"/>
+      <c r="R117" s="7"/>
+      <c r="S117" s="7"/>
+      <c r="T117" s="7"/>
+      <c r="U117" s="7"/>
+      <c r="V117" s="7"/>
+      <c r="W117" s="7"/>
+      <c r="X117" s="7"/>
+      <c r="Y117" s="5"/>
+      <c r="Z117" s="5"/>
+      <c r="AA117" s="5"/>
+      <c r="AB117" s="5"/>
+      <c r="AC117" s="5"/>
     </row>
     <row r="118" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H118" s="7"/>
-      <c r="I118" s="8"/>
-      <c r="J118" s="8"/>
-      <c r="K118" s="8"/>
-      <c r="L118" s="8"/>
-      <c r="M118" s="8"/>
-      <c r="N118" s="8"/>
-      <c r="O118" s="9"/>
-      <c r="P118" s="9"/>
-      <c r="Q118" s="7"/>
-      <c r="R118" s="7"/>
-      <c r="S118" s="7"/>
-      <c r="T118" s="7"/>
-      <c r="U118" s="7"/>
-      <c r="V118" s="7"/>
-      <c r="W118" s="7"/>
-      <c r="X118" s="7"/>
-      <c r="Y118" s="7"/>
-      <c r="Z118" s="7"/>
-      <c r="AA118" s="7"/>
-      <c r="AB118" s="7"/>
-      <c r="AC118" s="7"/>
+      <c r="H118" s="5"/>
+      <c r="I118" s="6"/>
+      <c r="J118" s="6"/>
+      <c r="K118" s="6"/>
+      <c r="L118" s="6"/>
+      <c r="M118" s="6"/>
+      <c r="N118" s="6"/>
+      <c r="O118" s="7"/>
+      <c r="P118" s="7"/>
+      <c r="Q118" s="5"/>
+      <c r="R118" s="5"/>
+      <c r="S118" s="5"/>
+      <c r="T118" s="5"/>
+      <c r="U118" s="5"/>
+      <c r="V118" s="5"/>
+      <c r="W118" s="5"/>
+      <c r="X118" s="5"/>
+      <c r="Y118" s="5"/>
+      <c r="Z118" s="5"/>
+      <c r="AA118" s="5"/>
+      <c r="AB118" s="5"/>
+      <c r="AC118" s="5"/>
     </row>
     <row r="119" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H119" s="7"/>
-      <c r="I119" s="8"/>
-      <c r="J119" s="8"/>
-      <c r="K119" s="8"/>
-      <c r="L119" s="8"/>
-      <c r="M119" s="8"/>
-      <c r="N119" s="8"/>
-      <c r="O119" s="9"/>
-      <c r="P119" s="9"/>
-      <c r="Q119" s="9"/>
-      <c r="R119" s="9"/>
-      <c r="S119" s="9"/>
-      <c r="T119" s="9"/>
-      <c r="U119" s="9"/>
-      <c r="V119" s="9"/>
-      <c r="W119" s="9"/>
-      <c r="X119" s="9"/>
-      <c r="Y119" s="7"/>
-      <c r="Z119" s="7"/>
-      <c r="AA119" s="7"/>
-      <c r="AB119" s="7"/>
-      <c r="AC119" s="7"/>
+      <c r="H119" s="5"/>
+      <c r="I119" s="6"/>
+      <c r="J119" s="6"/>
+      <c r="K119" s="6"/>
+      <c r="L119" s="6"/>
+      <c r="M119" s="6"/>
+      <c r="N119" s="6"/>
+      <c r="O119" s="7"/>
+      <c r="P119" s="7"/>
+      <c r="Q119" s="7"/>
+      <c r="R119" s="7"/>
+      <c r="S119" s="7"/>
+      <c r="T119" s="7"/>
+      <c r="U119" s="7"/>
+      <c r="V119" s="7"/>
+      <c r="W119" s="7"/>
+      <c r="X119" s="7"/>
+      <c r="Y119" s="5"/>
+      <c r="Z119" s="5"/>
+      <c r="AA119" s="5"/>
+      <c r="AB119" s="5"/>
+      <c r="AC119" s="5"/>
     </row>
     <row r="120" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H120" s="7"/>
-      <c r="I120" s="7"/>
-      <c r="J120" s="7"/>
-      <c r="K120" s="7"/>
-      <c r="L120" s="7"/>
-      <c r="M120" s="7"/>
-      <c r="N120" s="7"/>
-      <c r="O120" s="7"/>
-      <c r="P120" s="7"/>
-      <c r="Q120" s="7"/>
-      <c r="R120" s="7"/>
-      <c r="S120" s="7"/>
-      <c r="T120" s="7"/>
-      <c r="U120" s="7"/>
-      <c r="V120" s="7"/>
-      <c r="W120" s="7"/>
-      <c r="X120" s="7"/>
-      <c r="Y120" s="7"/>
-      <c r="Z120" s="7"/>
-      <c r="AA120" s="7"/>
-      <c r="AB120" s="7"/>
-      <c r="AC120" s="7"/>
+      <c r="H120" s="5"/>
+      <c r="I120" s="5"/>
+      <c r="J120" s="5"/>
+      <c r="K120" s="5"/>
+      <c r="L120" s="5"/>
+      <c r="M120" s="5"/>
+      <c r="N120" s="5"/>
+      <c r="O120" s="5"/>
+      <c r="P120" s="5"/>
+      <c r="Q120" s="5"/>
+      <c r="R120" s="5"/>
+      <c r="S120" s="5"/>
+      <c r="T120" s="5"/>
+      <c r="U120" s="5"/>
+      <c r="V120" s="5"/>
+      <c r="W120" s="5"/>
+      <c r="X120" s="5"/>
+      <c r="Y120" s="5"/>
+      <c r="Z120" s="5"/>
+      <c r="AA120" s="5"/>
+      <c r="AB120" s="5"/>
+      <c r="AC120" s="5"/>
     </row>
     <row r="121" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H121" s="7"/>
-      <c r="I121" s="7"/>
-      <c r="J121" s="7"/>
-      <c r="K121" s="7"/>
-      <c r="L121" s="7"/>
-      <c r="M121" s="7"/>
-      <c r="N121" s="7"/>
-      <c r="O121" s="7"/>
-      <c r="P121" s="7"/>
-      <c r="Q121" s="7"/>
-      <c r="R121" s="7"/>
-      <c r="S121" s="7"/>
-      <c r="T121" s="7"/>
-      <c r="U121" s="7"/>
-      <c r="V121" s="7"/>
-      <c r="W121" s="7"/>
-      <c r="X121" s="7"/>
-      <c r="Y121" s="7"/>
-      <c r="Z121" s="7"/>
-      <c r="AA121" s="7"/>
-      <c r="AB121" s="7"/>
-      <c r="AC121" s="7"/>
+      <c r="H121" s="5"/>
+      <c r="I121" s="5"/>
+      <c r="J121" s="5"/>
+      <c r="K121" s="5"/>
+      <c r="L121" s="5"/>
+      <c r="M121" s="5"/>
+      <c r="N121" s="5"/>
+      <c r="O121" s="5"/>
+      <c r="P121" s="5"/>
+      <c r="Q121" s="5"/>
+      <c r="R121" s="5"/>
+      <c r="S121" s="5"/>
+      <c r="T121" s="5"/>
+      <c r="U121" s="5"/>
+      <c r="V121" s="5"/>
+      <c r="W121" s="5"/>
+      <c r="X121" s="5"/>
+      <c r="Y121" s="5"/>
+      <c r="Z121" s="5"/>
+      <c r="AA121" s="5"/>
+      <c r="AB121" s="5"/>
+      <c r="AC121" s="5"/>
     </row>
     <row r="122" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H122" s="7"/>
-      <c r="I122" s="7"/>
-      <c r="J122" s="7"/>
-      <c r="K122" s="7"/>
-      <c r="L122" s="7"/>
-      <c r="M122" s="7"/>
-      <c r="N122" s="7"/>
-      <c r="O122" s="7"/>
-      <c r="P122" s="7"/>
-      <c r="Q122" s="7"/>
-      <c r="R122" s="7"/>
-      <c r="S122" s="7"/>
-      <c r="T122" s="7"/>
-      <c r="U122" s="7"/>
-      <c r="V122" s="7"/>
-      <c r="W122" s="7"/>
-      <c r="X122" s="7"/>
-      <c r="Y122" s="7"/>
-      <c r="Z122" s="7"/>
-      <c r="AA122" s="7"/>
-      <c r="AB122" s="7"/>
-      <c r="AC122" s="7"/>
+      <c r="H122" s="5"/>
+      <c r="I122" s="5"/>
+      <c r="J122" s="5"/>
+      <c r="K122" s="5"/>
+      <c r="L122" s="5"/>
+      <c r="M122" s="5"/>
+      <c r="N122" s="5"/>
+      <c r="O122" s="5"/>
+      <c r="P122" s="5"/>
+      <c r="Q122" s="5"/>
+      <c r="R122" s="5"/>
+      <c r="S122" s="5"/>
+      <c r="T122" s="5"/>
+      <c r="U122" s="5"/>
+      <c r="V122" s="5"/>
+      <c r="W122" s="5"/>
+      <c r="X122" s="5"/>
+      <c r="Y122" s="5"/>
+      <c r="Z122" s="5"/>
+      <c r="AA122" s="5"/>
+      <c r="AB122" s="5"/>
+      <c r="AC122" s="5"/>
     </row>
     <row r="123" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H123" s="7"/>
-      <c r="I123" s="7"/>
-      <c r="J123" s="7"/>
-      <c r="K123" s="7"/>
-      <c r="L123" s="7"/>
-      <c r="M123" s="7"/>
-      <c r="N123" s="7"/>
-      <c r="O123" s="7"/>
-      <c r="P123" s="7"/>
-      <c r="Q123" s="7"/>
-      <c r="R123" s="7"/>
-      <c r="S123" s="7"/>
-      <c r="T123" s="7"/>
-      <c r="U123" s="7"/>
-      <c r="V123" s="7"/>
-      <c r="W123" s="7"/>
-      <c r="X123" s="7"/>
-      <c r="Y123" s="7"/>
-      <c r="Z123" s="7"/>
-      <c r="AA123" s="7"/>
-      <c r="AB123" s="7"/>
-      <c r="AC123" s="7"/>
+      <c r="H123" s="5"/>
+      <c r="I123" s="5"/>
+      <c r="J123" s="5"/>
+      <c r="K123" s="5"/>
+      <c r="L123" s="5"/>
+      <c r="M123" s="5"/>
+      <c r="N123" s="5"/>
+      <c r="O123" s="5"/>
+      <c r="P123" s="5"/>
+      <c r="Q123" s="5"/>
+      <c r="R123" s="5"/>
+      <c r="S123" s="5"/>
+      <c r="T123" s="5"/>
+      <c r="U123" s="5"/>
+      <c r="V123" s="5"/>
+      <c r="W123" s="5"/>
+      <c r="X123" s="5"/>
+      <c r="Y123" s="5"/>
+      <c r="Z123" s="5"/>
+      <c r="AA123" s="5"/>
+      <c r="AB123" s="5"/>
+      <c r="AC123" s="5"/>
     </row>
     <row r="124" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H124" s="7"/>
-      <c r="I124" s="7"/>
-      <c r="J124" s="7"/>
-      <c r="K124" s="7"/>
-      <c r="L124" s="7"/>
-      <c r="M124" s="7"/>
-      <c r="N124" s="7"/>
-      <c r="O124" s="7"/>
-      <c r="P124" s="7"/>
-      <c r="Q124" s="7"/>
-      <c r="R124" s="7"/>
-      <c r="S124" s="7"/>
-      <c r="T124" s="7"/>
-      <c r="U124" s="7"/>
-      <c r="V124" s="7"/>
-      <c r="W124" s="7"/>
-      <c r="X124" s="7"/>
-      <c r="Y124" s="7"/>
-      <c r="Z124" s="7"/>
-      <c r="AA124" s="7"/>
-      <c r="AB124" s="7"/>
-      <c r="AC124" s="7"/>
+      <c r="H124" s="5"/>
+      <c r="I124" s="5"/>
+      <c r="J124" s="5"/>
+      <c r="K124" s="5"/>
+      <c r="L124" s="5"/>
+      <c r="M124" s="5"/>
+      <c r="N124" s="5"/>
+      <c r="O124" s="5"/>
+      <c r="P124" s="5"/>
+      <c r="Q124" s="5"/>
+      <c r="R124" s="5"/>
+      <c r="S124" s="5"/>
+      <c r="T124" s="5"/>
+      <c r="U124" s="5"/>
+      <c r="V124" s="5"/>
+      <c r="W124" s="5"/>
+      <c r="X124" s="5"/>
+      <c r="Y124" s="5"/>
+      <c r="Z124" s="5"/>
+      <c r="AA124" s="5"/>
+      <c r="AB124" s="5"/>
+      <c r="AC124" s="5"/>
     </row>
     <row r="125" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H125" s="7"/>
-      <c r="I125" s="7"/>
-      <c r="J125" s="7"/>
-      <c r="K125" s="7"/>
-      <c r="L125" s="7"/>
-      <c r="M125" s="7"/>
-      <c r="N125" s="7"/>
-      <c r="O125" s="7"/>
-      <c r="P125" s="7"/>
-      <c r="Q125" s="7"/>
-      <c r="R125" s="7"/>
-      <c r="S125" s="7"/>
-      <c r="T125" s="7"/>
-      <c r="U125" s="7"/>
-      <c r="V125" s="7"/>
-      <c r="W125" s="7"/>
-      <c r="X125" s="7"/>
-      <c r="Y125" s="7"/>
-      <c r="Z125" s="7"/>
-      <c r="AA125" s="7"/>
-      <c r="AB125" s="7"/>
-      <c r="AC125" s="7"/>
+      <c r="H125" s="5"/>
+      <c r="I125" s="5"/>
+      <c r="J125" s="5"/>
+      <c r="K125" s="5"/>
+      <c r="L125" s="5"/>
+      <c r="M125" s="5"/>
+      <c r="N125" s="5"/>
+      <c r="O125" s="5"/>
+      <c r="P125" s="5"/>
+      <c r="Q125" s="5"/>
+      <c r="R125" s="5"/>
+      <c r="S125" s="5"/>
+      <c r="T125" s="5"/>
+      <c r="U125" s="5"/>
+      <c r="V125" s="5"/>
+      <c r="W125" s="5"/>
+      <c r="X125" s="5"/>
+      <c r="Y125" s="5"/>
+      <c r="Z125" s="5"/>
+      <c r="AA125" s="5"/>
+      <c r="AB125" s="5"/>
+      <c r="AC125" s="5"/>
     </row>
     <row r="126" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H126" s="7"/>
-      <c r="I126" s="7"/>
-      <c r="J126" s="7"/>
-      <c r="K126" s="7"/>
-      <c r="L126" s="7"/>
-      <c r="M126" s="7"/>
-      <c r="N126" s="7"/>
-      <c r="O126" s="7"/>
-      <c r="P126" s="7"/>
-      <c r="Q126" s="7"/>
-      <c r="R126" s="7"/>
-      <c r="S126" s="7"/>
-      <c r="T126" s="7"/>
-      <c r="U126" s="7"/>
-      <c r="V126" s="7"/>
-      <c r="W126" s="7"/>
-      <c r="X126" s="7"/>
-      <c r="Y126" s="7"/>
-      <c r="Z126" s="7"/>
-      <c r="AA126" s="7"/>
-      <c r="AB126" s="7"/>
-      <c r="AC126" s="7"/>
+      <c r="H126" s="5"/>
+      <c r="I126" s="5"/>
+      <c r="J126" s="5"/>
+      <c r="K126" s="5"/>
+      <c r="L126" s="5"/>
+      <c r="M126" s="5"/>
+      <c r="N126" s="5"/>
+      <c r="O126" s="5"/>
+      <c r="P126" s="5"/>
+      <c r="Q126" s="5"/>
+      <c r="R126" s="5"/>
+      <c r="S126" s="5"/>
+      <c r="T126" s="5"/>
+      <c r="U126" s="5"/>
+      <c r="V126" s="5"/>
+      <c r="W126" s="5"/>
+      <c r="X126" s="5"/>
+      <c r="Y126" s="5"/>
+      <c r="Z126" s="5"/>
+      <c r="AA126" s="5"/>
+      <c r="AB126" s="5"/>
+      <c r="AC126" s="5"/>
     </row>
     <row r="127" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H127" s="7"/>
-      <c r="I127" s="7"/>
-      <c r="J127" s="7"/>
-      <c r="K127" s="7"/>
-      <c r="L127" s="7"/>
-      <c r="M127" s="7"/>
-      <c r="N127" s="7"/>
-      <c r="O127" s="7"/>
-      <c r="P127" s="7"/>
-      <c r="Q127" s="7"/>
-      <c r="R127" s="7"/>
-      <c r="S127" s="7"/>
-      <c r="T127" s="7"/>
-      <c r="U127" s="7"/>
-      <c r="V127" s="7"/>
-      <c r="W127" s="7"/>
-      <c r="X127" s="7"/>
-      <c r="Y127" s="7"/>
-      <c r="Z127" s="7"/>
-      <c r="AA127" s="7"/>
-      <c r="AB127" s="7"/>
-      <c r="AC127" s="7"/>
+      <c r="H127" s="5"/>
+      <c r="I127" s="5"/>
+      <c r="J127" s="5"/>
+      <c r="K127" s="5"/>
+      <c r="L127" s="5"/>
+      <c r="M127" s="5"/>
+      <c r="N127" s="5"/>
+      <c r="O127" s="5"/>
+      <c r="P127" s="5"/>
+      <c r="Q127" s="5"/>
+      <c r="R127" s="5"/>
+      <c r="S127" s="5"/>
+      <c r="T127" s="5"/>
+      <c r="U127" s="5"/>
+      <c r="V127" s="5"/>
+      <c r="W127" s="5"/>
+      <c r="X127" s="5"/>
+      <c r="Y127" s="5"/>
+      <c r="Z127" s="5"/>
+      <c r="AA127" s="5"/>
+      <c r="AB127" s="5"/>
+      <c r="AC127" s="5"/>
     </row>
     <row r="128" spans="8:29" x14ac:dyDescent="0.35">
-      <c r="H128" s="7"/>
-      <c r="I128" s="7"/>
-      <c r="J128" s="7"/>
-      <c r="K128" s="7"/>
-      <c r="L128" s="7"/>
-      <c r="M128" s="7"/>
-      <c r="N128" s="7"/>
-      <c r="O128" s="7"/>
-      <c r="P128" s="7"/>
-      <c r="Q128" s="7"/>
-      <c r="R128" s="7"/>
-      <c r="S128" s="7"/>
-      <c r="T128" s="7"/>
-      <c r="U128" s="7"/>
-      <c r="V128" s="7"/>
-      <c r="W128" s="7"/>
-      <c r="X128" s="7"/>
-      <c r="Y128" s="7"/>
-      <c r="Z128" s="7"/>
-      <c r="AA128" s="7"/>
-      <c r="AB128" s="7"/>
-      <c r="AC128" s="7"/>
+      <c r="H128" s="5"/>
+      <c r="I128" s="5"/>
+      <c r="J128" s="5"/>
+      <c r="K128" s="5"/>
+      <c r="L128" s="5"/>
+      <c r="M128" s="5"/>
+      <c r="N128" s="5"/>
+      <c r="O128" s="5"/>
+      <c r="P128" s="5"/>
+      <c r="Q128" s="5"/>
+      <c r="R128" s="5"/>
+      <c r="S128" s="5"/>
+      <c r="T128" s="5"/>
+      <c r="U128" s="5"/>
+      <c r="V128" s="5"/>
+      <c r="W128" s="5"/>
+      <c r="X128" s="5"/>
+      <c r="Y128" s="5"/>
+      <c r="Z128" s="5"/>
+      <c r="AA128" s="5"/>
+      <c r="AB128" s="5"/>
+      <c r="AC128" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="52">
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="K22:L22"/>
+  <mergeCells count="130">
+    <mergeCell ref="G23:J27"/>
+    <mergeCell ref="G8:J12"/>
+    <mergeCell ref="E8:F12"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K10:L10"/>
@@ -5098,20 +6699,117 @@
     <mergeCell ref="M5:T5"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="O6:P6"/>
-    <mergeCell ref="E16:F19"/>
-    <mergeCell ref="G16:J19"/>
-    <mergeCell ref="D8:D19"/>
-    <mergeCell ref="D20:D31"/>
-    <mergeCell ref="E20:F23"/>
-    <mergeCell ref="G20:J23"/>
-    <mergeCell ref="E24:F27"/>
-    <mergeCell ref="G24:J27"/>
-    <mergeCell ref="E28:F31"/>
-    <mergeCell ref="G28:J31"/>
-    <mergeCell ref="G8:J11"/>
-    <mergeCell ref="E8:F11"/>
-    <mergeCell ref="E12:F15"/>
-    <mergeCell ref="G12:J15"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="D8:D27"/>
+    <mergeCell ref="E13:F17"/>
+    <mergeCell ref="G13:J17"/>
+    <mergeCell ref="E18:F22"/>
+    <mergeCell ref="G18:J22"/>
+    <mergeCell ref="E23:F27"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="D28:D47"/>
+    <mergeCell ref="E28:F32"/>
+    <mergeCell ref="G28:J32"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="E33:F37"/>
+    <mergeCell ref="G33:J37"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="E38:F42"/>
+    <mergeCell ref="E43:F47"/>
+    <mergeCell ref="G43:J47"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="G38:J42"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="D48:D67"/>
+    <mergeCell ref="E48:F52"/>
+    <mergeCell ref="G48:J52"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="E53:F57"/>
+    <mergeCell ref="G53:J57"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="E58:F62"/>
+    <mergeCell ref="E63:F67"/>
+    <mergeCell ref="G63:J67"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="K66:L66"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="G58:J62"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="K59:L59"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="D68:D87"/>
+    <mergeCell ref="E68:F72"/>
+    <mergeCell ref="G68:J72"/>
+    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="K71:L71"/>
+    <mergeCell ref="K72:L72"/>
+    <mergeCell ref="E73:F77"/>
+    <mergeCell ref="G73:J77"/>
+    <mergeCell ref="K73:L73"/>
+    <mergeCell ref="K74:L74"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="K77:L77"/>
+    <mergeCell ref="E78:F82"/>
+    <mergeCell ref="E83:F87"/>
+    <mergeCell ref="G83:J87"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="K84:L84"/>
+    <mergeCell ref="K85:L85"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="G78:J82"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="K82:L82"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Expereiments/MessageFiltering.xlsx
+++ b/Expereiments/MessageFiltering.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="108">
   <si>
     <t>#</t>
   </si>
@@ -304,6 +304,45 @@
   </si>
   <si>
     <t>Embedding Tweets with TF-IDF + NE Weight</t>
+  </si>
+  <si>
+    <t>Embedding NE with Fastext Model</t>
+  </si>
+  <si>
+    <t>Embedding NE with AraBert Model</t>
+  </si>
+  <si>
+    <t>Embedding NE with mBert Model</t>
+  </si>
+  <si>
+    <t>Embedding NE with TF-IDF Model</t>
+  </si>
+  <si>
+    <t>Embedding Tweets with Fastext Model Plcaceholders</t>
+  </si>
+  <si>
+    <t>Embedding Tweets with AraBert Model Plcaceholders</t>
+  </si>
+  <si>
+    <t>Embedding Tweets with mBert Model Plcaceholders</t>
+  </si>
+  <si>
+    <t>Embedding Tweets with TF-IDF Model Plcaceholders</t>
+  </si>
+  <si>
+    <t>AraBert</t>
+  </si>
+  <si>
+    <t>mBert</t>
+  </si>
+  <si>
+    <t>TF-IDF</t>
+  </si>
+  <si>
+    <t>FasText +NE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AraBert + NE</t>
   </si>
 </sst>
 </file>
@@ -700,12 +739,6 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -722,6 +755,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -796,6 +835,887 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ar-SA"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Filtering Results</a:t>
+            </a:r>
+            <a:endParaRPr lang="ar-SY"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$I$302:$L$302</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v> FasText Embeddig</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>AraBert</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>mBert</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>TF-IDF</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$I$303:$L$303</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E9AA-4585-A262-EE9AB22B28A2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="429399872"/>
+        <c:axId val="429395280"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="429399872"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="429395280"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="429395280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="429399872"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>550333</xdr:colOff>
+      <xdr:row>301</xdr:row>
+      <xdr:rowOff>134761</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>268111</xdr:colOff>
+      <xdr:row>316</xdr:row>
+      <xdr:rowOff>126294</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="مخطط 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1061,7 +1981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG128"/>
+  <dimension ref="A1:AG303"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="6.1796875" customWidth="1"/>
@@ -1069,7 +1989,7 @@
     <col min="4" max="4" width="9.1796875" customWidth="1"/>
     <col min="5" max="5" width="11.453125" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="10" max="10" width="14.90625" customWidth="1"/>
+    <col min="10" max="10" width="19.453125" customWidth="1"/>
     <col min="11" max="11" width="15.453125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1273,8 +2193,8 @@
       <c r="H6" s="54"/>
       <c r="I6" s="54"/>
       <c r="J6" s="55"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
       <c r="M6" s="59" t="s">
         <v>4</v>
       </c>
@@ -1316,8 +2236,8 @@
       <c r="H7" s="57"/>
       <c r="I7" s="57"/>
       <c r="J7" s="58"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
       <c r="M7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1360,23 +2280,23 @@
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="35" t="s">
+      <c r="F8" s="40"/>
+      <c r="G8" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="36" t="s">
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="36"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="15" t="s">
         <v>27</v>
       </c>
@@ -1419,17 +2339,17 @@
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="37" t="s">
+      <c r="D9" s="39"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L9" s="38"/>
+      <c r="L9" s="36"/>
       <c r="M9" s="16" t="s">
         <v>32</v>
       </c>
@@ -1472,17 +2392,17 @@
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="36" t="s">
+      <c r="D10" s="39"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L10" s="36"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="15" t="s">
         <v>34</v>
       </c>
@@ -1525,17 +2445,17 @@
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="39" t="s">
+      <c r="D11" s="39"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="39"/>
+      <c r="L11" s="37"/>
       <c r="M11" s="16">
         <v>0.73</v>
       </c>
@@ -1578,17 +2498,17 @@
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="36" t="s">
+      <c r="D12" s="39"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="36"/>
+      <c r="L12" s="34"/>
       <c r="M12" s="15">
         <v>0.84</v>
       </c>
@@ -1631,21 +2551,21 @@
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="34" t="s">
+      <c r="D13" s="39"/>
+      <c r="E13" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="35" t="s">
+      <c r="F13" s="40"/>
+      <c r="G13" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="36" t="s">
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L13" s="36"/>
+      <c r="L13" s="34"/>
       <c r="M13" s="15" t="s">
         <v>46</v>
       </c>
@@ -1688,17 +2608,17 @@
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="37" t="s">
+      <c r="D14" s="39"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L14" s="38"/>
+      <c r="L14" s="36"/>
       <c r="M14" s="16" t="s">
         <v>50</v>
       </c>
@@ -1741,17 +2661,17 @@
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="36" t="s">
+      <c r="D15" s="39"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L15" s="36"/>
+      <c r="L15" s="34"/>
       <c r="M15" s="18" t="s">
         <v>55</v>
       </c>
@@ -1794,17 +2714,17 @@
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="39" t="s">
+      <c r="D16" s="39"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L16" s="39"/>
+      <c r="L16" s="37"/>
       <c r="M16" s="16" t="s">
         <v>59</v>
       </c>
@@ -1847,17 +2767,17 @@
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="36" t="s">
+      <c r="D17" s="39"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L17" s="36"/>
+      <c r="L17" s="34"/>
       <c r="M17" s="15" t="s">
         <v>58</v>
       </c>
@@ -1900,21 +2820,21 @@
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="34" t="s">
+      <c r="D18" s="39"/>
+      <c r="E18" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="34"/>
-      <c r="G18" s="35" t="s">
+      <c r="F18" s="40"/>
+      <c r="G18" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="36" t="s">
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L18" s="36"/>
+      <c r="L18" s="34"/>
       <c r="M18" s="18" t="s">
         <v>69</v>
       </c>
@@ -1957,17 +2877,17 @@
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="37" t="s">
+      <c r="D19" s="39"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L19" s="38"/>
+      <c r="L19" s="36"/>
       <c r="M19" s="16" t="s">
         <v>46</v>
       </c>
@@ -2010,17 +2930,17 @@
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="36" t="s">
+      <c r="D20" s="39"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L20" s="36"/>
+      <c r="L20" s="34"/>
       <c r="M20" s="15" t="s">
         <v>50</v>
       </c>
@@ -2063,17 +2983,17 @@
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="39" t="s">
+      <c r="D21" s="39"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L21" s="39"/>
+      <c r="L21" s="37"/>
       <c r="M21" s="16" t="s">
         <v>73</v>
       </c>
@@ -2116,17 +3036,17 @@
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="36" t="s">
+      <c r="D22" s="39"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L22" s="36"/>
+      <c r="L22" s="34"/>
       <c r="M22" s="15" t="s">
         <v>27</v>
       </c>
@@ -2169,21 +3089,21 @@
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="34" t="s">
+      <c r="D23" s="39"/>
+      <c r="E23" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="34"/>
-      <c r="G23" s="35" t="s">
+      <c r="F23" s="40"/>
+      <c r="G23" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="36" t="s">
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L23" s="36"/>
+      <c r="L23" s="34"/>
       <c r="M23" s="18">
         <v>0.99</v>
       </c>
@@ -2226,17 +3146,17 @@
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="37" t="s">
+      <c r="D24" s="39"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L24" s="38"/>
+      <c r="L24" s="36"/>
       <c r="M24" s="16">
         <v>0.84</v>
       </c>
@@ -2279,17 +3199,17 @@
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="36" t="s">
+      <c r="D25" s="39"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L25" s="36"/>
+      <c r="L25" s="34"/>
       <c r="M25" s="15">
         <v>0.87</v>
       </c>
@@ -2332,17 +3252,17 @@
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="39" t="s">
+      <c r="D26" s="39"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L26" s="39"/>
+      <c r="L26" s="37"/>
       <c r="M26" s="16">
         <v>0.69</v>
       </c>
@@ -2385,17 +3305,17 @@
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="36" t="s">
+      <c r="D27" s="39"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L27" s="36"/>
+      <c r="L27" s="34"/>
       <c r="M27" s="15">
         <v>0.89</v>
       </c>
@@ -2438,23 +3358,23 @@
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="40" t="s">
+      <c r="D28" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="34" t="s">
+      <c r="E28" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="34"/>
-      <c r="G28" s="35" t="s">
+      <c r="F28" s="40"/>
+      <c r="G28" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="36" t="s">
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L28" s="36"/>
+      <c r="L28" s="34"/>
       <c r="M28" s="23">
         <v>0.83</v>
       </c>
@@ -2497,17 +3417,17 @@
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="37" t="s">
+      <c r="D29" s="39"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L29" s="38"/>
+      <c r="L29" s="36"/>
       <c r="M29" s="16">
         <v>0.85</v>
       </c>
@@ -2550,17 +3470,17 @@
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="36" t="s">
+      <c r="D30" s="39"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L30" s="36"/>
+      <c r="L30" s="34"/>
       <c r="M30" s="15">
         <v>0.85</v>
       </c>
@@ -2603,17 +3523,17 @@
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="39" t="s">
+      <c r="D31" s="39"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="39"/>
+      <c r="L31" s="37"/>
       <c r="M31" s="16">
         <v>0.73</v>
       </c>
@@ -2656,17 +3576,17 @@
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="36" t="s">
+      <c r="D32" s="39"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L32" s="36"/>
+      <c r="L32" s="34"/>
       <c r="M32" s="15">
         <v>0.84</v>
       </c>
@@ -2709,21 +3629,21 @@
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="34" t="s">
+      <c r="D33" s="39"/>
+      <c r="E33" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="34"/>
-      <c r="G33" s="35" t="s">
+      <c r="F33" s="40"/>
+      <c r="G33" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="H33" s="35"/>
-      <c r="I33" s="35"/>
-      <c r="J33" s="35"/>
-      <c r="K33" s="36" t="s">
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L33" s="36"/>
+      <c r="L33" s="34"/>
       <c r="M33" s="15">
         <v>0.84</v>
       </c>
@@ -2766,17 +3686,17 @@
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="37" t="s">
+      <c r="D34" s="39"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L34" s="38"/>
+      <c r="L34" s="36"/>
       <c r="M34" s="16">
         <v>0.85</v>
       </c>
@@ -2819,17 +3739,17 @@
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="35"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="35"/>
-      <c r="J35" s="35"/>
-      <c r="K35" s="36" t="s">
+      <c r="D35" s="39"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="41"/>
+      <c r="K35" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L35" s="36"/>
+      <c r="L35" s="34"/>
       <c r="M35" s="15">
         <v>0.88</v>
       </c>
@@ -2872,17 +3792,17 @@
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="39" t="s">
+      <c r="D36" s="39"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="41"/>
+      <c r="K36" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L36" s="39"/>
+      <c r="L36" s="37"/>
       <c r="M36" s="16">
         <v>0.78</v>
       </c>
@@ -2925,17 +3845,17 @@
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="36" t="s">
+      <c r="D37" s="39"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="41"/>
+      <c r="K37" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L37" s="36"/>
+      <c r="L37" s="34"/>
       <c r="M37" s="15">
         <v>0.86</v>
       </c>
@@ -2978,21 +3898,21 @@
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="34" t="s">
+      <c r="D38" s="39"/>
+      <c r="E38" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F38" s="34"/>
-      <c r="G38" s="35" t="s">
+      <c r="F38" s="40"/>
+      <c r="G38" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="35"/>
-      <c r="K38" s="36" t="s">
+      <c r="H38" s="41"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="41"/>
+      <c r="K38" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L38" s="36"/>
+      <c r="L38" s="34"/>
       <c r="M38" s="15"/>
       <c r="N38" s="15"/>
       <c r="O38" s="15"/>
@@ -3019,17 +3939,17 @@
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="35"/>
-      <c r="J39" s="35"/>
-      <c r="K39" s="37" t="s">
+      <c r="D39" s="39"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="41"/>
+      <c r="I39" s="41"/>
+      <c r="J39" s="41"/>
+      <c r="K39" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L39" s="38"/>
+      <c r="L39" s="36"/>
       <c r="M39" s="16">
         <v>0.83</v>
       </c>
@@ -3072,17 +3992,17 @@
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="36" t="s">
+      <c r="D40" s="39"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="41"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="41"/>
+      <c r="K40" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L40" s="36"/>
+      <c r="L40" s="34"/>
       <c r="M40" s="15">
         <v>0.84</v>
       </c>
@@ -3125,17 +4045,17 @@
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="35"/>
-      <c r="I41" s="35"/>
-      <c r="J41" s="35"/>
-      <c r="K41" s="39" t="s">
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="41"/>
+      <c r="J41" s="41"/>
+      <c r="K41" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L41" s="39"/>
+      <c r="L41" s="37"/>
       <c r="M41" s="16">
         <v>0.67</v>
       </c>
@@ -3178,17 +4098,17 @@
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="35"/>
-      <c r="I42" s="35"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="36" t="s">
+      <c r="D42" s="39"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="41"/>
+      <c r="I42" s="41"/>
+      <c r="J42" s="41"/>
+      <c r="K42" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L42" s="36"/>
+      <c r="L42" s="34"/>
       <c r="M42" s="15">
         <v>0.85</v>
       </c>
@@ -3231,21 +4151,21 @@
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="34" t="s">
+      <c r="D43" s="39"/>
+      <c r="E43" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="F43" s="34"/>
-      <c r="G43" s="35" t="s">
+      <c r="F43" s="40"/>
+      <c r="G43" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="H43" s="35"/>
-      <c r="I43" s="35"/>
-      <c r="J43" s="35"/>
-      <c r="K43" s="36" t="s">
+      <c r="H43" s="41"/>
+      <c r="I43" s="41"/>
+      <c r="J43" s="41"/>
+      <c r="K43" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L43" s="36"/>
+      <c r="L43" s="34"/>
       <c r="M43" s="16">
         <v>0.83</v>
       </c>
@@ -3288,17 +4208,17 @@
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="35"/>
-      <c r="K44" s="37" t="s">
+      <c r="D44" s="39"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="41"/>
+      <c r="J44" s="41"/>
+      <c r="K44" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L44" s="38"/>
+      <c r="L44" s="36"/>
       <c r="M44" s="18">
         <v>0.75</v>
       </c>
@@ -3341,17 +4261,17 @@
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
-      <c r="J45" s="35"/>
-      <c r="K45" s="36" t="s">
+      <c r="D45" s="39"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="41"/>
+      <c r="J45" s="41"/>
+      <c r="K45" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L45" s="36"/>
+      <c r="L45" s="34"/>
       <c r="M45" s="31" t="s">
         <v>88</v>
       </c>
@@ -3394,17 +4314,17 @@
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="39" t="s">
+      <c r="D46" s="39"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="41"/>
+      <c r="J46" s="41"/>
+      <c r="K46" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L46" s="39"/>
+      <c r="L46" s="37"/>
       <c r="M46" s="32">
         <v>0.85</v>
       </c>
@@ -3447,17 +4367,17 @@
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="34"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
-      <c r="J47" s="35"/>
-      <c r="K47" s="36" t="s">
+      <c r="D47" s="39"/>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="41"/>
+      <c r="J47" s="41"/>
+      <c r="K47" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L47" s="36"/>
+      <c r="L47" s="34"/>
       <c r="M47" s="15">
         <v>0.86</v>
       </c>
@@ -3500,23 +4420,23 @@
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
-      <c r="D48" s="40" t="s">
+      <c r="D48" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="E48" s="34" t="s">
+      <c r="E48" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F48" s="34"/>
-      <c r="G48" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="H48" s="35"/>
-      <c r="I48" s="35"/>
-      <c r="J48" s="35"/>
-      <c r="K48" s="36" t="s">
+      <c r="F48" s="40"/>
+      <c r="G48" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="H48" s="41"/>
+      <c r="I48" s="41"/>
+      <c r="J48" s="41"/>
+      <c r="K48" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L48" s="36"/>
+      <c r="L48" s="34"/>
       <c r="M48" s="33"/>
       <c r="N48" s="33"/>
       <c r="O48" s="33"/>
@@ -3543,17 +4463,17 @@
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="35"/>
-      <c r="H49" s="35"/>
-      <c r="I49" s="35"/>
-      <c r="J49" s="35"/>
-      <c r="K49" s="37" t="s">
+      <c r="D49" s="39"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41"/>
+      <c r="J49" s="41"/>
+      <c r="K49" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L49" s="38"/>
+      <c r="L49" s="36"/>
       <c r="M49" s="21"/>
       <c r="N49" s="21"/>
       <c r="O49" s="21"/>
@@ -3580,17 +4500,17 @@
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="35"/>
-      <c r="I50" s="35"/>
-      <c r="J50" s="35"/>
-      <c r="K50" s="36" t="s">
+      <c r="D50" s="39"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="41"/>
+      <c r="J50" s="41"/>
+      <c r="K50" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L50" s="36"/>
+      <c r="L50" s="34"/>
       <c r="M50" s="20"/>
       <c r="N50" s="22"/>
       <c r="O50" s="20"/>
@@ -3617,17 +4537,17 @@
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="34"/>
-      <c r="F51" s="34"/>
-      <c r="G51" s="35"/>
-      <c r="H51" s="35"/>
-      <c r="I51" s="35"/>
-      <c r="J51" s="35"/>
-      <c r="K51" s="39" t="s">
+      <c r="D51" s="39"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="41"/>
+      <c r="I51" s="41"/>
+      <c r="J51" s="41"/>
+      <c r="K51" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L51" s="39"/>
+      <c r="L51" s="37"/>
       <c r="M51" s="21"/>
       <c r="N51" s="21"/>
       <c r="O51" s="21"/>
@@ -3654,17 +4574,17 @@
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="35"/>
-      <c r="J52" s="35"/>
-      <c r="K52" s="36" t="s">
+      <c r="D52" s="39"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="41"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="41"/>
+      <c r="J52" s="41"/>
+      <c r="K52" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L52" s="36"/>
+      <c r="L52" s="34"/>
       <c r="M52" s="20"/>
       <c r="N52" s="20"/>
       <c r="O52" s="20"/>
@@ -3691,21 +4611,21 @@
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="34" t="s">
+      <c r="D53" s="39"/>
+      <c r="E53" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="F53" s="34"/>
-      <c r="G53" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="H53" s="35"/>
-      <c r="I53" s="35"/>
-      <c r="J53" s="35"/>
-      <c r="K53" s="36" t="s">
+      <c r="F53" s="40"/>
+      <c r="G53" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="H53" s="41"/>
+      <c r="I53" s="41"/>
+      <c r="J53" s="41"/>
+      <c r="K53" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L53" s="36"/>
+      <c r="L53" s="34"/>
       <c r="M53" s="24">
         <v>0.73</v>
       </c>
@@ -3748,17 +4668,17 @@
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="35"/>
-      <c r="I54" s="35"/>
-      <c r="J54" s="35"/>
-      <c r="K54" s="37" t="s">
+      <c r="D54" s="39"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="41"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="41"/>
+      <c r="J54" s="41"/>
+      <c r="K54" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L54" s="38"/>
+      <c r="L54" s="36"/>
       <c r="M54" s="25">
         <v>0.76</v>
       </c>
@@ -3801,17 +4721,17 @@
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="34"/>
-      <c r="F55" s="34"/>
-      <c r="G55" s="35"/>
-      <c r="H55" s="35"/>
-      <c r="I55" s="35"/>
-      <c r="J55" s="35"/>
-      <c r="K55" s="36" t="s">
+      <c r="D55" s="39"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="41"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="41"/>
+      <c r="J55" s="41"/>
+      <c r="K55" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L55" s="36"/>
+      <c r="L55" s="34"/>
       <c r="M55" s="24">
         <v>0.82</v>
       </c>
@@ -3854,17 +4774,17 @@
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
-      <c r="D56" s="41"/>
-      <c r="E56" s="34"/>
-      <c r="F56" s="34"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="35"/>
-      <c r="I56" s="35"/>
-      <c r="J56" s="35"/>
-      <c r="K56" s="39" t="s">
+      <c r="D56" s="39"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="41"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="41"/>
+      <c r="J56" s="41"/>
+      <c r="K56" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L56" s="39"/>
+      <c r="L56" s="37"/>
       <c r="M56" s="16">
         <v>0.64</v>
       </c>
@@ -3907,17 +4827,17 @@
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
-      <c r="D57" s="41"/>
-      <c r="E57" s="34"/>
-      <c r="F57" s="34"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="35"/>
-      <c r="I57" s="35"/>
-      <c r="J57" s="35"/>
-      <c r="K57" s="36" t="s">
+      <c r="D57" s="39"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="41"/>
+      <c r="J57" s="41"/>
+      <c r="K57" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L57" s="36"/>
+      <c r="L57" s="34"/>
       <c r="M57" s="15">
         <v>0.78</v>
       </c>
@@ -3960,21 +4880,21 @@
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="41"/>
-      <c r="E58" s="34" t="s">
+      <c r="D58" s="39"/>
+      <c r="E58" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F58" s="34"/>
-      <c r="G58" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="H58" s="35"/>
-      <c r="I58" s="35"/>
-      <c r="J58" s="35"/>
-      <c r="K58" s="36" t="s">
+      <c r="F58" s="40"/>
+      <c r="G58" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="H58" s="41"/>
+      <c r="I58" s="41"/>
+      <c r="J58" s="41"/>
+      <c r="K58" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L58" s="36"/>
+      <c r="L58" s="34"/>
       <c r="M58" s="23">
         <v>0.73</v>
       </c>
@@ -4017,17 +4937,17 @@
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
-      <c r="D59" s="41"/>
-      <c r="E59" s="34"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="35"/>
-      <c r="I59" s="35"/>
-      <c r="J59" s="35"/>
-      <c r="K59" s="37" t="s">
+      <c r="D59" s="39"/>
+      <c r="E59" s="40"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="41"/>
+      <c r="H59" s="41"/>
+      <c r="I59" s="41"/>
+      <c r="J59" s="41"/>
+      <c r="K59" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L59" s="38"/>
+      <c r="L59" s="36"/>
       <c r="M59" s="16">
         <v>0.75</v>
       </c>
@@ -4070,17 +4990,17 @@
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
-      <c r="D60" s="41"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="35"/>
-      <c r="J60" s="35"/>
-      <c r="K60" s="36" t="s">
+      <c r="D60" s="39"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="40"/>
+      <c r="G60" s="41"/>
+      <c r="H60" s="41"/>
+      <c r="I60" s="41"/>
+      <c r="J60" s="41"/>
+      <c r="K60" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L60" s="36"/>
+      <c r="L60" s="34"/>
       <c r="M60" s="15">
         <v>0.82</v>
       </c>
@@ -4123,17 +5043,17 @@
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="41"/>
-      <c r="E61" s="34"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="35"/>
-      <c r="J61" s="35"/>
-      <c r="K61" s="39" t="s">
+      <c r="D61" s="39"/>
+      <c r="E61" s="40"/>
+      <c r="F61" s="40"/>
+      <c r="G61" s="41"/>
+      <c r="H61" s="41"/>
+      <c r="I61" s="41"/>
+      <c r="J61" s="41"/>
+      <c r="K61" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L61" s="39"/>
+      <c r="L61" s="37"/>
       <c r="M61" s="16">
         <v>0.64</v>
       </c>
@@ -4176,17 +5096,17 @@
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="41"/>
-      <c r="E62" s="34"/>
-      <c r="F62" s="34"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="35"/>
-      <c r="J62" s="35"/>
-      <c r="K62" s="36" t="s">
+      <c r="D62" s="39"/>
+      <c r="E62" s="40"/>
+      <c r="F62" s="40"/>
+      <c r="G62" s="41"/>
+      <c r="H62" s="41"/>
+      <c r="I62" s="41"/>
+      <c r="J62" s="41"/>
+      <c r="K62" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L62" s="36"/>
+      <c r="L62" s="34"/>
       <c r="M62" s="15">
         <v>0.78</v>
       </c>
@@ -4229,21 +5149,21 @@
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="34" t="s">
+      <c r="D63" s="39"/>
+      <c r="E63" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="F63" s="34"/>
-      <c r="G63" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="H63" s="35"/>
-      <c r="I63" s="35"/>
-      <c r="J63" s="35"/>
-      <c r="K63" s="36" t="s">
+      <c r="F63" s="40"/>
+      <c r="G63" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="H63" s="41"/>
+      <c r="I63" s="41"/>
+      <c r="J63" s="41"/>
+      <c r="K63" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L63" s="36"/>
+      <c r="L63" s="34"/>
       <c r="M63" s="15" t="s">
         <v>76</v>
       </c>
@@ -4286,17 +5206,17 @@
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="41"/>
-      <c r="E64" s="34"/>
-      <c r="F64" s="34"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="35"/>
-      <c r="J64" s="35"/>
-      <c r="K64" s="37" t="s">
+      <c r="D64" s="39"/>
+      <c r="E64" s="40"/>
+      <c r="F64" s="40"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="41"/>
+      <c r="I64" s="41"/>
+      <c r="J64" s="41"/>
+      <c r="K64" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L64" s="38"/>
+      <c r="L64" s="36"/>
       <c r="M64" s="16" t="s">
         <v>53</v>
       </c>
@@ -4339,17 +5259,17 @@
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="41"/>
-      <c r="E65" s="34"/>
-      <c r="F65" s="34"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="35"/>
-      <c r="I65" s="35"/>
-      <c r="J65" s="35"/>
-      <c r="K65" s="36" t="s">
+      <c r="D65" s="39"/>
+      <c r="E65" s="40"/>
+      <c r="F65" s="40"/>
+      <c r="G65" s="41"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="41"/>
+      <c r="J65" s="41"/>
+      <c r="K65" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L65" s="36"/>
+      <c r="L65" s="34"/>
       <c r="M65" s="15" t="s">
         <v>76</v>
       </c>
@@ -4392,17 +5312,17 @@
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="41"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="34"/>
-      <c r="G66" s="35"/>
-      <c r="H66" s="35"/>
-      <c r="I66" s="35"/>
-      <c r="J66" s="35"/>
-      <c r="K66" s="39" t="s">
+      <c r="D66" s="39"/>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
+      <c r="G66" s="41"/>
+      <c r="H66" s="41"/>
+      <c r="I66" s="41"/>
+      <c r="J66" s="41"/>
+      <c r="K66" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L66" s="39"/>
+      <c r="L66" s="37"/>
       <c r="M66" s="16" t="s">
         <v>79</v>
       </c>
@@ -4445,17 +5365,17 @@
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="41"/>
-      <c r="E67" s="34"/>
-      <c r="F67" s="34"/>
-      <c r="G67" s="35"/>
-      <c r="H67" s="35"/>
-      <c r="I67" s="35"/>
-      <c r="J67" s="35"/>
-      <c r="K67" s="36" t="s">
+      <c r="D67" s="39"/>
+      <c r="E67" s="40"/>
+      <c r="F67" s="40"/>
+      <c r="G67" s="41"/>
+      <c r="H67" s="41"/>
+      <c r="I67" s="41"/>
+      <c r="J67" s="41"/>
+      <c r="K67" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L67" s="36"/>
+      <c r="L67" s="34"/>
       <c r="M67" s="15" t="s">
         <v>59</v>
       </c>
@@ -4498,23 +5418,23 @@
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
-      <c r="D68" s="40" t="s">
+      <c r="D68" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="E68" s="34" t="s">
+      <c r="E68" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="F68" s="34"/>
-      <c r="G68" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="H68" s="35"/>
-      <c r="I68" s="35"/>
-      <c r="J68" s="35"/>
-      <c r="K68" s="36" t="s">
+      <c r="F68" s="40"/>
+      <c r="G68" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="H68" s="41"/>
+      <c r="I68" s="41"/>
+      <c r="J68" s="41"/>
+      <c r="K68" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L68" s="36"/>
+      <c r="L68" s="34"/>
       <c r="M68" s="28">
         <v>0.83</v>
       </c>
@@ -4557,17 +5477,17 @@
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="34"/>
-      <c r="G69" s="35"/>
-      <c r="H69" s="35"/>
-      <c r="I69" s="35"/>
-      <c r="J69" s="35"/>
-      <c r="K69" s="37" t="s">
+      <c r="D69" s="39"/>
+      <c r="E69" s="40"/>
+      <c r="F69" s="40"/>
+      <c r="G69" s="41"/>
+      <c r="H69" s="41"/>
+      <c r="I69" s="41"/>
+      <c r="J69" s="41"/>
+      <c r="K69" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L69" s="38"/>
+      <c r="L69" s="36"/>
       <c r="M69" s="25">
         <v>0.83</v>
       </c>
@@ -4610,17 +5530,17 @@
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
-      <c r="D70" s="41"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="34"/>
-      <c r="G70" s="35"/>
-      <c r="H70" s="35"/>
-      <c r="I70" s="35"/>
-      <c r="J70" s="35"/>
-      <c r="K70" s="36" t="s">
+      <c r="D70" s="39"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="41"/>
+      <c r="H70" s="41"/>
+      <c r="I70" s="41"/>
+      <c r="J70" s="41"/>
+      <c r="K70" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L70" s="36"/>
+      <c r="L70" s="34"/>
       <c r="M70" s="24">
         <v>0.84</v>
       </c>
@@ -4663,17 +5583,17 @@
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
-      <c r="D71" s="41"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="35"/>
-      <c r="H71" s="35"/>
-      <c r="I71" s="35"/>
-      <c r="J71" s="35"/>
-      <c r="K71" s="39" t="s">
+      <c r="D71" s="39"/>
+      <c r="E71" s="40"/>
+      <c r="F71" s="40"/>
+      <c r="G71" s="41"/>
+      <c r="H71" s="41"/>
+      <c r="I71" s="41"/>
+      <c r="J71" s="41"/>
+      <c r="K71" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L71" s="39"/>
+      <c r="L71" s="37"/>
       <c r="M71" s="25">
         <v>0.74</v>
       </c>
@@ -4716,17 +5636,17 @@
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
-      <c r="D72" s="41"/>
-      <c r="E72" s="34"/>
-      <c r="F72" s="34"/>
-      <c r="G72" s="35"/>
-      <c r="H72" s="35"/>
-      <c r="I72" s="35"/>
-      <c r="J72" s="35"/>
-      <c r="K72" s="36" t="s">
+      <c r="D72" s="39"/>
+      <c r="E72" s="40"/>
+      <c r="F72" s="40"/>
+      <c r="G72" s="41"/>
+      <c r="H72" s="41"/>
+      <c r="I72" s="41"/>
+      <c r="J72" s="41"/>
+      <c r="K72" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L72" s="36"/>
+      <c r="L72" s="34"/>
       <c r="M72" s="24">
         <v>0.83</v>
       </c>
@@ -4769,21 +5689,21 @@
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
-      <c r="D73" s="41"/>
-      <c r="E73" s="34" t="s">
+      <c r="D73" s="39"/>
+      <c r="E73" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="F73" s="34"/>
-      <c r="G73" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="H73" s="35"/>
-      <c r="I73" s="35"/>
-      <c r="J73" s="35"/>
-      <c r="K73" s="36" t="s">
+      <c r="F73" s="40"/>
+      <c r="G73" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="H73" s="41"/>
+      <c r="I73" s="41"/>
+      <c r="J73" s="41"/>
+      <c r="K73" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L73" s="36"/>
+      <c r="L73" s="34"/>
       <c r="M73" s="23">
         <v>0.87</v>
       </c>
@@ -4826,17 +5746,17 @@
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
-      <c r="D74" s="41"/>
-      <c r="E74" s="34"/>
-      <c r="F74" s="34"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="35"/>
-      <c r="I74" s="35"/>
-      <c r="J74" s="35"/>
-      <c r="K74" s="37" t="s">
+      <c r="D74" s="39"/>
+      <c r="E74" s="40"/>
+      <c r="F74" s="40"/>
+      <c r="G74" s="41"/>
+      <c r="H74" s="41"/>
+      <c r="I74" s="41"/>
+      <c r="J74" s="41"/>
+      <c r="K74" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L74" s="38"/>
+      <c r="L74" s="36"/>
       <c r="M74" s="16">
         <v>0.85</v>
       </c>
@@ -4879,17 +5799,17 @@
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
-      <c r="D75" s="41"/>
-      <c r="E75" s="34"/>
-      <c r="F75" s="34"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
-      <c r="J75" s="35"/>
-      <c r="K75" s="36" t="s">
+      <c r="D75" s="39"/>
+      <c r="E75" s="40"/>
+      <c r="F75" s="40"/>
+      <c r="G75" s="41"/>
+      <c r="H75" s="41"/>
+      <c r="I75" s="41"/>
+      <c r="J75" s="41"/>
+      <c r="K75" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L75" s="36"/>
+      <c r="L75" s="34"/>
       <c r="M75" s="15">
         <v>0.89</v>
       </c>
@@ -4932,17 +5852,17 @@
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
-      <c r="D76" s="41"/>
-      <c r="E76" s="34"/>
-      <c r="F76" s="34"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
-      <c r="J76" s="35"/>
-      <c r="K76" s="39" t="s">
+      <c r="D76" s="39"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="41"/>
+      <c r="H76" s="41"/>
+      <c r="I76" s="41"/>
+      <c r="J76" s="41"/>
+      <c r="K76" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L76" s="39"/>
+      <c r="L76" s="37"/>
       <c r="M76" s="16">
         <v>0.76</v>
       </c>
@@ -4985,17 +5905,17 @@
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
-      <c r="D77" s="41"/>
-      <c r="E77" s="34"/>
-      <c r="F77" s="34"/>
-      <c r="G77" s="35"/>
-      <c r="H77" s="35"/>
-      <c r="I77" s="35"/>
-      <c r="J77" s="35"/>
-      <c r="K77" s="36" t="s">
+      <c r="D77" s="39"/>
+      <c r="E77" s="40"/>
+      <c r="F77" s="40"/>
+      <c r="G77" s="41"/>
+      <c r="H77" s="41"/>
+      <c r="I77" s="41"/>
+      <c r="J77" s="41"/>
+      <c r="K77" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L77" s="36"/>
+      <c r="L77" s="34"/>
       <c r="M77" s="15">
         <v>0.87</v>
       </c>
@@ -5038,21 +5958,21 @@
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
-      <c r="D78" s="41"/>
-      <c r="E78" s="34" t="s">
+      <c r="D78" s="39"/>
+      <c r="E78" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="F78" s="34"/>
-      <c r="G78" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="H78" s="35"/>
-      <c r="I78" s="35"/>
-      <c r="J78" s="35"/>
-      <c r="K78" s="36" t="s">
+      <c r="F78" s="40"/>
+      <c r="G78" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="H78" s="41"/>
+      <c r="I78" s="41"/>
+      <c r="J78" s="41"/>
+      <c r="K78" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L78" s="36"/>
+      <c r="L78" s="34"/>
       <c r="M78" s="15">
         <v>0.87</v>
       </c>
@@ -5095,17 +6015,17 @@
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
-      <c r="D79" s="41"/>
-      <c r="E79" s="34"/>
-      <c r="F79" s="34"/>
-      <c r="G79" s="35"/>
-      <c r="H79" s="35"/>
-      <c r="I79" s="35"/>
-      <c r="J79" s="35"/>
-      <c r="K79" s="37" t="s">
+      <c r="D79" s="39"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="41"/>
+      <c r="I79" s="41"/>
+      <c r="J79" s="41"/>
+      <c r="K79" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L79" s="38"/>
+      <c r="L79" s="36"/>
       <c r="M79" s="16">
         <v>0.85</v>
       </c>
@@ -5148,17 +6068,17 @@
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
-      <c r="D80" s="41"/>
-      <c r="E80" s="34"/>
-      <c r="F80" s="34"/>
-      <c r="G80" s="35"/>
-      <c r="H80" s="35"/>
-      <c r="I80" s="35"/>
-      <c r="J80" s="35"/>
-      <c r="K80" s="36" t="s">
+      <c r="D80" s="39"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="41"/>
+      <c r="I80" s="41"/>
+      <c r="J80" s="41"/>
+      <c r="K80" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L80" s="36"/>
+      <c r="L80" s="34"/>
       <c r="M80" s="15">
         <v>0.89</v>
       </c>
@@ -5201,17 +6121,17 @@
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
-      <c r="D81" s="41"/>
-      <c r="E81" s="34"/>
-      <c r="F81" s="34"/>
-      <c r="G81" s="35"/>
-      <c r="H81" s="35"/>
-      <c r="I81" s="35"/>
-      <c r="J81" s="35"/>
-      <c r="K81" s="39" t="s">
+      <c r="D81" s="39"/>
+      <c r="E81" s="40"/>
+      <c r="F81" s="40"/>
+      <c r="G81" s="41"/>
+      <c r="H81" s="41"/>
+      <c r="I81" s="41"/>
+      <c r="J81" s="41"/>
+      <c r="K81" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L81" s="39"/>
+      <c r="L81" s="37"/>
       <c r="M81" s="16">
         <v>0.76</v>
       </c>
@@ -5254,17 +6174,17 @@
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
-      <c r="D82" s="41"/>
-      <c r="E82" s="34"/>
-      <c r="F82" s="34"/>
-      <c r="G82" s="35"/>
-      <c r="H82" s="35"/>
-      <c r="I82" s="35"/>
-      <c r="J82" s="35"/>
-      <c r="K82" s="36" t="s">
+      <c r="D82" s="39"/>
+      <c r="E82" s="40"/>
+      <c r="F82" s="40"/>
+      <c r="G82" s="41"/>
+      <c r="H82" s="41"/>
+      <c r="I82" s="41"/>
+      <c r="J82" s="41"/>
+      <c r="K82" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L82" s="36"/>
+      <c r="L82" s="34"/>
       <c r="M82" s="15">
         <v>0.87</v>
       </c>
@@ -5307,21 +6227,21 @@
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
-      <c r="D83" s="41"/>
-      <c r="E83" s="34" t="s">
+      <c r="D83" s="39"/>
+      <c r="E83" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="F83" s="34"/>
-      <c r="G83" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="35"/>
-      <c r="I83" s="35"/>
-      <c r="J83" s="35"/>
-      <c r="K83" s="36" t="s">
+      <c r="F83" s="40"/>
+      <c r="G83" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="H83" s="41"/>
+      <c r="I83" s="41"/>
+      <c r="J83" s="41"/>
+      <c r="K83" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="L83" s="36"/>
+      <c r="L83" s="34"/>
       <c r="M83" s="30">
         <v>0.96</v>
       </c>
@@ -5364,17 +6284,17 @@
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
-      <c r="D84" s="41"/>
-      <c r="E84" s="34"/>
-      <c r="F84" s="34"/>
-      <c r="G84" s="35"/>
-      <c r="H84" s="35"/>
-      <c r="I84" s="35"/>
-      <c r="J84" s="35"/>
-      <c r="K84" s="37" t="s">
+      <c r="D84" s="39"/>
+      <c r="E84" s="40"/>
+      <c r="F84" s="40"/>
+      <c r="G84" s="41"/>
+      <c r="H84" s="41"/>
+      <c r="I84" s="41"/>
+      <c r="J84" s="41"/>
+      <c r="K84" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="L84" s="38"/>
+      <c r="L84" s="36"/>
       <c r="M84" s="25">
         <v>0.85</v>
       </c>
@@ -5417,17 +6337,17 @@
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
-      <c r="D85" s="41"/>
-      <c r="E85" s="34"/>
-      <c r="F85" s="34"/>
-      <c r="G85" s="35"/>
-      <c r="H85" s="35"/>
-      <c r="I85" s="35"/>
-      <c r="J85" s="35"/>
-      <c r="K85" s="36" t="s">
+      <c r="D85" s="39"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="40"/>
+      <c r="G85" s="41"/>
+      <c r="H85" s="41"/>
+      <c r="I85" s="41"/>
+      <c r="J85" s="41"/>
+      <c r="K85" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L85" s="36"/>
+      <c r="L85" s="34"/>
       <c r="M85" s="24">
         <v>0.84</v>
       </c>
@@ -5470,17 +6390,17 @@
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
-      <c r="D86" s="41"/>
-      <c r="E86" s="34"/>
-      <c r="F86" s="34"/>
-      <c r="G86" s="35"/>
-      <c r="H86" s="35"/>
-      <c r="I86" s="35"/>
-      <c r="J86" s="35"/>
-      <c r="K86" s="39" t="s">
+      <c r="D86" s="39"/>
+      <c r="E86" s="40"/>
+      <c r="F86" s="40"/>
+      <c r="G86" s="41"/>
+      <c r="H86" s="41"/>
+      <c r="I86" s="41"/>
+      <c r="J86" s="41"/>
+      <c r="K86" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="L86" s="39"/>
+      <c r="L86" s="37"/>
       <c r="M86" s="25">
         <v>0.71</v>
       </c>
@@ -5521,17 +6441,17 @@
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.35">
       <c r="C87" s="3"/>
-      <c r="D87" s="41"/>
-      <c r="E87" s="34"/>
-      <c r="F87" s="34"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="35"/>
-      <c r="J87" s="35"/>
-      <c r="K87" s="36" t="s">
+      <c r="D87" s="39"/>
+      <c r="E87" s="40"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="41"/>
+      <c r="H87" s="41"/>
+      <c r="I87" s="41"/>
+      <c r="J87" s="41"/>
+      <c r="K87" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="L87" s="36"/>
+      <c r="L87" s="34"/>
       <c r="M87" s="24" t="s">
         <v>37</v>
       </c>
@@ -6678,13 +7598,1685 @@
       <c r="AB128" s="5"/>
       <c r="AC128" s="5"/>
     </row>
+    <row r="173" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="G173" t="s">
+        <v>18</v>
+      </c>
+      <c r="H173" t="s">
+        <v>103</v>
+      </c>
+      <c r="I173" t="s">
+        <v>104</v>
+      </c>
+      <c r="J173" t="s">
+        <v>105</v>
+      </c>
+      <c r="K173" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="L173" s="40"/>
+      <c r="M173" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="N173" s="41"/>
+      <c r="O173" s="41"/>
+      <c r="P173" s="41"/>
+      <c r="Q173" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R173" s="34"/>
+      <c r="S173" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="T173" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="174" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="F174" t="s">
+        <v>18</v>
+      </c>
+      <c r="G174" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H174" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="I174" t="s">
+        <v>37</v>
+      </c>
+      <c r="J174" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="K174" s="40"/>
+      <c r="L174" s="40"/>
+      <c r="M174" s="41"/>
+      <c r="N174" s="41"/>
+      <c r="O174" s="41"/>
+      <c r="P174" s="41"/>
+      <c r="Q174" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R174" s="36"/>
+      <c r="S174" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="T174" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="175" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="F175" t="s">
+        <v>103</v>
+      </c>
+      <c r="G175" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="K175" s="40"/>
+      <c r="L175" s="40"/>
+      <c r="M175" s="41"/>
+      <c r="N175" s="41"/>
+      <c r="O175" s="41"/>
+      <c r="P175" s="41"/>
+      <c r="Q175" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R175" s="34"/>
+      <c r="S175" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="T175" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="176" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="F176" t="s">
+        <v>104</v>
+      </c>
+      <c r="G176" t="s">
+        <v>37</v>
+      </c>
+      <c r="K176" s="40"/>
+      <c r="L176" s="40"/>
+      <c r="M176" s="41"/>
+      <c r="N176" s="41"/>
+      <c r="O176" s="41"/>
+      <c r="P176" s="41"/>
+      <c r="Q176" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R176" s="37"/>
+      <c r="S176" s="16">
+        <v>0.73</v>
+      </c>
+      <c r="T176" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="177" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="F177" t="s">
+        <v>105</v>
+      </c>
+      <c r="G177" s="17">
+        <v>0.8</v>
+      </c>
+      <c r="K177" s="40"/>
+      <c r="L177" s="40"/>
+      <c r="M177" s="41"/>
+      <c r="N177" s="41"/>
+      <c r="O177" s="41"/>
+      <c r="P177" s="41"/>
+      <c r="Q177" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R177" s="34"/>
+      <c r="S177" s="15">
+        <v>0.84</v>
+      </c>
+      <c r="T177" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="178" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="K178" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="L178" s="40"/>
+      <c r="M178" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="N178" s="41"/>
+      <c r="O178" s="41"/>
+      <c r="P178" s="41"/>
+      <c r="Q178" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R178" s="34"/>
+      <c r="S178" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="T178" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="179" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="F179" t="s">
+        <v>106</v>
+      </c>
+      <c r="G179" s="17">
+        <v>0.81</v>
+      </c>
+      <c r="K179" s="40"/>
+      <c r="L179" s="40"/>
+      <c r="M179" s="41"/>
+      <c r="N179" s="41"/>
+      <c r="O179" s="41"/>
+      <c r="P179" s="41"/>
+      <c r="Q179" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R179" s="36"/>
+      <c r="S179" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="T179" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="180" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="F180" t="s">
+        <v>107</v>
+      </c>
+      <c r="G180" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="K180" s="40"/>
+      <c r="L180" s="40"/>
+      <c r="M180" s="41"/>
+      <c r="N180" s="41"/>
+      <c r="O180" s="41"/>
+      <c r="P180" s="41"/>
+      <c r="Q180" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R180" s="34"/>
+      <c r="S180" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="T180" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="181" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="K181" s="40"/>
+      <c r="L181" s="40"/>
+      <c r="M181" s="41"/>
+      <c r="N181" s="41"/>
+      <c r="O181" s="41"/>
+      <c r="P181" s="41"/>
+      <c r="Q181" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R181" s="37"/>
+      <c r="S181" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="T181" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="182" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="K182" s="40"/>
+      <c r="L182" s="40"/>
+      <c r="M182" s="41"/>
+      <c r="N182" s="41"/>
+      <c r="O182" s="41"/>
+      <c r="P182" s="41"/>
+      <c r="Q182" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R182" s="34"/>
+      <c r="S182" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="T182" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="183" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="K183" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="L183" s="40"/>
+      <c r="M183" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="N183" s="41"/>
+      <c r="O183" s="41"/>
+      <c r="P183" s="41"/>
+      <c r="Q183" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R183" s="34"/>
+      <c r="S183" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="T183" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="184" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="K184" s="40"/>
+      <c r="L184" s="40"/>
+      <c r="M184" s="41"/>
+      <c r="N184" s="41"/>
+      <c r="O184" s="41"/>
+      <c r="P184" s="41"/>
+      <c r="Q184" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R184" s="36"/>
+      <c r="S184" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="T184" s="29" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="185" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="K185" s="40"/>
+      <c r="L185" s="40"/>
+      <c r="M185" s="41"/>
+      <c r="N185" s="41"/>
+      <c r="O185" s="41"/>
+      <c r="P185" s="41"/>
+      <c r="Q185" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R185" s="34"/>
+      <c r="S185" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="T185" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="186" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="K186" s="40"/>
+      <c r="L186" s="40"/>
+      <c r="M186" s="41"/>
+      <c r="N186" s="41"/>
+      <c r="O186" s="41"/>
+      <c r="P186" s="41"/>
+      <c r="Q186" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R186" s="37"/>
+      <c r="S186" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="T186" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="187" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="K187" s="40"/>
+      <c r="L187" s="40"/>
+      <c r="M187" s="41"/>
+      <c r="N187" s="41"/>
+      <c r="O187" s="41"/>
+      <c r="P187" s="41"/>
+      <c r="Q187" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R187" s="34"/>
+      <c r="S187" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="T187" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="188" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="K188" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L188" s="40"/>
+      <c r="M188" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="N188" s="41"/>
+      <c r="O188" s="41"/>
+      <c r="P188" s="41"/>
+      <c r="Q188" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R188" s="34"/>
+      <c r="S188" s="18">
+        <v>0.99</v>
+      </c>
+      <c r="T188" s="18">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="189" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="K189" s="40"/>
+      <c r="L189" s="40"/>
+      <c r="M189" s="41"/>
+      <c r="N189" s="41"/>
+      <c r="O189" s="41"/>
+      <c r="P189" s="41"/>
+      <c r="Q189" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R189" s="36"/>
+      <c r="S189" s="16">
+        <v>0.84</v>
+      </c>
+      <c r="T189" s="16">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="190" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="K190" s="40"/>
+      <c r="L190" s="40"/>
+      <c r="M190" s="41"/>
+      <c r="N190" s="41"/>
+      <c r="O190" s="41"/>
+      <c r="P190" s="41"/>
+      <c r="Q190" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R190" s="34"/>
+      <c r="S190" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="T190" s="17">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="191" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="K191" s="40"/>
+      <c r="L191" s="40"/>
+      <c r="M191" s="41"/>
+      <c r="N191" s="41"/>
+      <c r="O191" s="41"/>
+      <c r="P191" s="41"/>
+      <c r="Q191" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R191" s="37"/>
+      <c r="S191" s="16">
+        <v>0.69</v>
+      </c>
+      <c r="T191" s="16">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="192" spans="6:20" x14ac:dyDescent="0.35">
+      <c r="K192" s="40"/>
+      <c r="L192" s="40"/>
+      <c r="M192" s="41"/>
+      <c r="N192" s="41"/>
+      <c r="O192" s="41"/>
+      <c r="P192" s="41"/>
+      <c r="Q192" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R192" s="34"/>
+      <c r="S192" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="T192" s="15">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="193" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K193" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="L193" s="40"/>
+      <c r="M193" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="N193" s="41"/>
+      <c r="O193" s="41"/>
+      <c r="P193" s="41"/>
+      <c r="Q193" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R193" s="34"/>
+      <c r="S193" s="23">
+        <v>0.83</v>
+      </c>
+      <c r="T193" s="23">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="194" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K194" s="40"/>
+      <c r="L194" s="40"/>
+      <c r="M194" s="41"/>
+      <c r="N194" s="41"/>
+      <c r="O194" s="41"/>
+      <c r="P194" s="41"/>
+      <c r="Q194" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R194" s="36"/>
+      <c r="S194" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="T194" s="16">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="195" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K195" s="40"/>
+      <c r="L195" s="40"/>
+      <c r="M195" s="41"/>
+      <c r="N195" s="41"/>
+      <c r="O195" s="41"/>
+      <c r="P195" s="41"/>
+      <c r="Q195" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R195" s="34"/>
+      <c r="S195" s="15">
+        <v>0.85</v>
+      </c>
+      <c r="T195" s="15">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="196" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K196" s="40"/>
+      <c r="L196" s="40"/>
+      <c r="M196" s="41"/>
+      <c r="N196" s="41"/>
+      <c r="O196" s="41"/>
+      <c r="P196" s="41"/>
+      <c r="Q196" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R196" s="37"/>
+      <c r="S196" s="16">
+        <v>0.73</v>
+      </c>
+      <c r="T196" s="16">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="197" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K197" s="40"/>
+      <c r="L197" s="40"/>
+      <c r="M197" s="41"/>
+      <c r="N197" s="41"/>
+      <c r="O197" s="41"/>
+      <c r="P197" s="41"/>
+      <c r="Q197" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R197" s="34"/>
+      <c r="S197" s="15">
+        <v>0.84</v>
+      </c>
+      <c r="T197" s="17">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="198" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K198" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="L198" s="40"/>
+      <c r="M198" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="N198" s="41"/>
+      <c r="O198" s="41"/>
+      <c r="P198" s="41"/>
+      <c r="Q198" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R198" s="34"/>
+      <c r="S198" s="15">
+        <v>0.84</v>
+      </c>
+      <c r="T198" s="15">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="199" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K199" s="40"/>
+      <c r="L199" s="40"/>
+      <c r="M199" s="41"/>
+      <c r="N199" s="41"/>
+      <c r="O199" s="41"/>
+      <c r="P199" s="41"/>
+      <c r="Q199" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R199" s="36"/>
+      <c r="S199" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="T199" s="19">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="200" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K200" s="40"/>
+      <c r="L200" s="40"/>
+      <c r="M200" s="41"/>
+      <c r="N200" s="41"/>
+      <c r="O200" s="41"/>
+      <c r="P200" s="41"/>
+      <c r="Q200" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R200" s="34"/>
+      <c r="S200" s="15">
+        <v>0.88</v>
+      </c>
+      <c r="T200" s="15">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="201" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K201" s="40"/>
+      <c r="L201" s="40"/>
+      <c r="M201" s="41"/>
+      <c r="N201" s="41"/>
+      <c r="O201" s="41"/>
+      <c r="P201" s="41"/>
+      <c r="Q201" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R201" s="37"/>
+      <c r="S201" s="16">
+        <v>0.78</v>
+      </c>
+      <c r="T201" s="16">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="202" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K202" s="40"/>
+      <c r="L202" s="40"/>
+      <c r="M202" s="41"/>
+      <c r="N202" s="41"/>
+      <c r="O202" s="41"/>
+      <c r="P202" s="41"/>
+      <c r="Q202" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R202" s="34"/>
+      <c r="S202" s="15">
+        <v>0.86</v>
+      </c>
+      <c r="T202" s="15">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="203" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K203" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="L203" s="40"/>
+      <c r="M203" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="N203" s="41"/>
+      <c r="O203" s="41"/>
+      <c r="P203" s="41"/>
+      <c r="Q203" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R203" s="34"/>
+      <c r="S203" s="15"/>
+      <c r="T203" s="15"/>
+    </row>
+    <row r="204" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K204" s="40"/>
+      <c r="L204" s="40"/>
+      <c r="M204" s="41"/>
+      <c r="N204" s="41"/>
+      <c r="O204" s="41"/>
+      <c r="P204" s="41"/>
+      <c r="Q204" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R204" s="36"/>
+      <c r="S204" s="16">
+        <v>0.83</v>
+      </c>
+      <c r="T204" s="16">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="205" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K205" s="40"/>
+      <c r="L205" s="40"/>
+      <c r="M205" s="41"/>
+      <c r="N205" s="41"/>
+      <c r="O205" s="41"/>
+      <c r="P205" s="41"/>
+      <c r="Q205" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R205" s="34"/>
+      <c r="S205" s="15">
+        <v>0.84</v>
+      </c>
+      <c r="T205" s="15">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="206" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K206" s="40"/>
+      <c r="L206" s="40"/>
+      <c r="M206" s="41"/>
+      <c r="N206" s="41"/>
+      <c r="O206" s="41"/>
+      <c r="P206" s="41"/>
+      <c r="Q206" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R206" s="37"/>
+      <c r="S206" s="16">
+        <v>0.67</v>
+      </c>
+      <c r="T206" s="16">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="207" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K207" s="40"/>
+      <c r="L207" s="40"/>
+      <c r="M207" s="41"/>
+      <c r="N207" s="41"/>
+      <c r="O207" s="41"/>
+      <c r="P207" s="41"/>
+      <c r="Q207" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R207" s="34"/>
+      <c r="S207" s="15">
+        <v>0.85</v>
+      </c>
+      <c r="T207" s="15">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="208" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K208" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L208" s="40"/>
+      <c r="M208" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="N208" s="41"/>
+      <c r="O208" s="41"/>
+      <c r="P208" s="41"/>
+      <c r="Q208" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R208" s="34"/>
+      <c r="S208" s="16">
+        <v>0.83</v>
+      </c>
+      <c r="T208" s="16">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="209" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K209" s="40"/>
+      <c r="L209" s="40"/>
+      <c r="M209" s="41"/>
+      <c r="N209" s="41"/>
+      <c r="O209" s="41"/>
+      <c r="P209" s="41"/>
+      <c r="Q209" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R209" s="36"/>
+      <c r="S209" s="18">
+        <v>0.75</v>
+      </c>
+      <c r="T209" s="18">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="210" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K210" s="40"/>
+      <c r="L210" s="40"/>
+      <c r="M210" s="41"/>
+      <c r="N210" s="41"/>
+      <c r="O210" s="41"/>
+      <c r="P210" s="41"/>
+      <c r="Q210" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R210" s="34"/>
+      <c r="S210" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="T210" s="31" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="211" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K211" s="40"/>
+      <c r="L211" s="40"/>
+      <c r="M211" s="41"/>
+      <c r="N211" s="41"/>
+      <c r="O211" s="41"/>
+      <c r="P211" s="41"/>
+      <c r="Q211" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R211" s="37"/>
+      <c r="S211" s="32">
+        <v>0.85</v>
+      </c>
+      <c r="T211" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="212" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K212" s="40"/>
+      <c r="L212" s="40"/>
+      <c r="M212" s="41"/>
+      <c r="N212" s="41"/>
+      <c r="O212" s="41"/>
+      <c r="P212" s="41"/>
+      <c r="Q212" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R212" s="34"/>
+      <c r="S212" s="15">
+        <v>0.86</v>
+      </c>
+      <c r="T212" s="15">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="213" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K213" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="L213" s="40"/>
+      <c r="M213" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="N213" s="41"/>
+      <c r="O213" s="41"/>
+      <c r="P213" s="41"/>
+      <c r="Q213" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R213" s="34"/>
+      <c r="S213" s="33"/>
+      <c r="T213" s="33"/>
+    </row>
+    <row r="214" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K214" s="40"/>
+      <c r="L214" s="40"/>
+      <c r="M214" s="41"/>
+      <c r="N214" s="41"/>
+      <c r="O214" s="41"/>
+      <c r="P214" s="41"/>
+      <c r="Q214" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R214" s="36"/>
+      <c r="S214" s="21"/>
+      <c r="T214" s="21"/>
+    </row>
+    <row r="215" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K215" s="40"/>
+      <c r="L215" s="40"/>
+      <c r="M215" s="41"/>
+      <c r="N215" s="41"/>
+      <c r="O215" s="41"/>
+      <c r="P215" s="41"/>
+      <c r="Q215" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R215" s="34"/>
+      <c r="S215" s="20"/>
+      <c r="T215" s="22"/>
+    </row>
+    <row r="216" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K216" s="40"/>
+      <c r="L216" s="40"/>
+      <c r="M216" s="41"/>
+      <c r="N216" s="41"/>
+      <c r="O216" s="41"/>
+      <c r="P216" s="41"/>
+      <c r="Q216" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R216" s="37"/>
+      <c r="S216" s="21"/>
+      <c r="T216" s="21"/>
+    </row>
+    <row r="217" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K217" s="40"/>
+      <c r="L217" s="40"/>
+      <c r="M217" s="41"/>
+      <c r="N217" s="41"/>
+      <c r="O217" s="41"/>
+      <c r="P217" s="41"/>
+      <c r="Q217" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R217" s="34"/>
+      <c r="S217" s="20"/>
+      <c r="T217" s="20"/>
+    </row>
+    <row r="218" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K218" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="L218" s="40"/>
+      <c r="M218" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="N218" s="41"/>
+      <c r="O218" s="41"/>
+      <c r="P218" s="41"/>
+      <c r="Q218" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R218" s="34"/>
+      <c r="S218" s="24">
+        <v>0.73</v>
+      </c>
+      <c r="T218" s="24">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="219" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K219" s="40"/>
+      <c r="L219" s="40"/>
+      <c r="M219" s="41"/>
+      <c r="N219" s="41"/>
+      <c r="O219" s="41"/>
+      <c r="P219" s="41"/>
+      <c r="Q219" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R219" s="36"/>
+      <c r="S219" s="25">
+        <v>0.76</v>
+      </c>
+      <c r="T219" s="26">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="220" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K220" s="40"/>
+      <c r="L220" s="40"/>
+      <c r="M220" s="41"/>
+      <c r="N220" s="41"/>
+      <c r="O220" s="41"/>
+      <c r="P220" s="41"/>
+      <c r="Q220" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R220" s="34"/>
+      <c r="S220" s="24">
+        <v>0.82</v>
+      </c>
+      <c r="T220" s="24">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="221" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K221" s="40"/>
+      <c r="L221" s="40"/>
+      <c r="M221" s="41"/>
+      <c r="N221" s="41"/>
+      <c r="O221" s="41"/>
+      <c r="P221" s="41"/>
+      <c r="Q221" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R221" s="37"/>
+      <c r="S221" s="16">
+        <v>0.64</v>
+      </c>
+      <c r="T221" s="16">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="222" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K222" s="40"/>
+      <c r="L222" s="40"/>
+      <c r="M222" s="41"/>
+      <c r="N222" s="41"/>
+      <c r="O222" s="41"/>
+      <c r="P222" s="41"/>
+      <c r="Q222" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R222" s="34"/>
+      <c r="S222" s="15">
+        <v>0.78</v>
+      </c>
+      <c r="T222" s="17">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="223" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K223" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="L223" s="40"/>
+      <c r="M223" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="N223" s="41"/>
+      <c r="O223" s="41"/>
+      <c r="P223" s="41"/>
+      <c r="Q223" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R223" s="34"/>
+      <c r="S223" s="23">
+        <v>0.73</v>
+      </c>
+      <c r="T223" s="23">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="224" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K224" s="40"/>
+      <c r="L224" s="40"/>
+      <c r="M224" s="41"/>
+      <c r="N224" s="41"/>
+      <c r="O224" s="41"/>
+      <c r="P224" s="41"/>
+      <c r="Q224" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R224" s="36"/>
+      <c r="S224" s="16">
+        <v>0.75</v>
+      </c>
+      <c r="T224" s="16">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="225" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K225" s="40"/>
+      <c r="L225" s="40"/>
+      <c r="M225" s="41"/>
+      <c r="N225" s="41"/>
+      <c r="O225" s="41"/>
+      <c r="P225" s="41"/>
+      <c r="Q225" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R225" s="34"/>
+      <c r="S225" s="15">
+        <v>0.82</v>
+      </c>
+      <c r="T225" s="15">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="226" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K226" s="40"/>
+      <c r="L226" s="40"/>
+      <c r="M226" s="41"/>
+      <c r="N226" s="41"/>
+      <c r="O226" s="41"/>
+      <c r="P226" s="41"/>
+      <c r="Q226" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R226" s="37"/>
+      <c r="S226" s="16">
+        <v>0.64</v>
+      </c>
+      <c r="T226" s="16">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="227" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K227" s="40"/>
+      <c r="L227" s="40"/>
+      <c r="M227" s="41"/>
+      <c r="N227" s="41"/>
+      <c r="O227" s="41"/>
+      <c r="P227" s="41"/>
+      <c r="Q227" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R227" s="34"/>
+      <c r="S227" s="15">
+        <v>0.78</v>
+      </c>
+      <c r="T227" s="15">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="228" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K228" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L228" s="40"/>
+      <c r="M228" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="N228" s="41"/>
+      <c r="O228" s="41"/>
+      <c r="P228" s="41"/>
+      <c r="Q228" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R228" s="34"/>
+      <c r="S228" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="T228" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="229" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K229" s="40"/>
+      <c r="L229" s="40"/>
+      <c r="M229" s="41"/>
+      <c r="N229" s="41"/>
+      <c r="O229" s="41"/>
+      <c r="P229" s="41"/>
+      <c r="Q229" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R229" s="36"/>
+      <c r="S229" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="T229" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="230" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K230" s="40"/>
+      <c r="L230" s="40"/>
+      <c r="M230" s="41"/>
+      <c r="N230" s="41"/>
+      <c r="O230" s="41"/>
+      <c r="P230" s="41"/>
+      <c r="Q230" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R230" s="34"/>
+      <c r="S230" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="T230" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="231" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K231" s="40"/>
+      <c r="L231" s="40"/>
+      <c r="M231" s="41"/>
+      <c r="N231" s="41"/>
+      <c r="O231" s="41"/>
+      <c r="P231" s="41"/>
+      <c r="Q231" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R231" s="37"/>
+      <c r="S231" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="T231" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="232" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K232" s="40"/>
+      <c r="L232" s="40"/>
+      <c r="M232" s="41"/>
+      <c r="N232" s="41"/>
+      <c r="O232" s="41"/>
+      <c r="P232" s="41"/>
+      <c r="Q232" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R232" s="34"/>
+      <c r="S232" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="T232" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="233" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K233" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="L233" s="40"/>
+      <c r="M233" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="N233" s="41"/>
+      <c r="O233" s="41"/>
+      <c r="P233" s="41"/>
+      <c r="Q233" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R233" s="34"/>
+      <c r="S233" s="28">
+        <v>0.83</v>
+      </c>
+      <c r="T233" s="28">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="234" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K234" s="40"/>
+      <c r="L234" s="40"/>
+      <c r="M234" s="41"/>
+      <c r="N234" s="41"/>
+      <c r="O234" s="41"/>
+      <c r="P234" s="41"/>
+      <c r="Q234" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R234" s="36"/>
+      <c r="S234" s="25">
+        <v>0.83</v>
+      </c>
+      <c r="T234" s="25">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="235" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K235" s="40"/>
+      <c r="L235" s="40"/>
+      <c r="M235" s="41"/>
+      <c r="N235" s="41"/>
+      <c r="O235" s="41"/>
+      <c r="P235" s="41"/>
+      <c r="Q235" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R235" s="34"/>
+      <c r="S235" s="24">
+        <v>0.84</v>
+      </c>
+      <c r="T235" s="24">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="236" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K236" s="40"/>
+      <c r="L236" s="40"/>
+      <c r="M236" s="41"/>
+      <c r="N236" s="41"/>
+      <c r="O236" s="41"/>
+      <c r="P236" s="41"/>
+      <c r="Q236" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R236" s="37"/>
+      <c r="S236" s="25">
+        <v>0.74</v>
+      </c>
+      <c r="T236" s="25">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="237" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K237" s="40"/>
+      <c r="L237" s="40"/>
+      <c r="M237" s="41"/>
+      <c r="N237" s="41"/>
+      <c r="O237" s="41"/>
+      <c r="P237" s="41"/>
+      <c r="Q237" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R237" s="34"/>
+      <c r="S237" s="24">
+        <v>0.83</v>
+      </c>
+      <c r="T237" s="27">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="238" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K238" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="L238" s="40"/>
+      <c r="M238" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="N238" s="41"/>
+      <c r="O238" s="41"/>
+      <c r="P238" s="41"/>
+      <c r="Q238" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R238" s="34"/>
+      <c r="S238" s="23">
+        <v>0.87</v>
+      </c>
+      <c r="T238" s="23">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="239" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K239" s="40"/>
+      <c r="L239" s="40"/>
+      <c r="M239" s="41"/>
+      <c r="N239" s="41"/>
+      <c r="O239" s="41"/>
+      <c r="P239" s="41"/>
+      <c r="Q239" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R239" s="36"/>
+      <c r="S239" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="T239" s="16">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="240" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K240" s="40"/>
+      <c r="L240" s="40"/>
+      <c r="M240" s="41"/>
+      <c r="N240" s="41"/>
+      <c r="O240" s="41"/>
+      <c r="P240" s="41"/>
+      <c r="Q240" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R240" s="34"/>
+      <c r="S240" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="T240" s="15">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="241" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K241" s="40"/>
+      <c r="L241" s="40"/>
+      <c r="M241" s="41"/>
+      <c r="N241" s="41"/>
+      <c r="O241" s="41"/>
+      <c r="P241" s="41"/>
+      <c r="Q241" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R241" s="37"/>
+      <c r="S241" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="T241" s="16">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="242" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K242" s="40"/>
+      <c r="L242" s="40"/>
+      <c r="M242" s="41"/>
+      <c r="N242" s="41"/>
+      <c r="O242" s="41"/>
+      <c r="P242" s="41"/>
+      <c r="Q242" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R242" s="34"/>
+      <c r="S242" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="T242" s="17">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="243" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K243" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="L243" s="40"/>
+      <c r="M243" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="N243" s="41"/>
+      <c r="O243" s="41"/>
+      <c r="P243" s="41"/>
+      <c r="Q243" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R243" s="34"/>
+      <c r="S243" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="T243" s="15">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="244" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K244" s="40"/>
+      <c r="L244" s="40"/>
+      <c r="M244" s="41"/>
+      <c r="N244" s="41"/>
+      <c r="O244" s="41"/>
+      <c r="P244" s="41"/>
+      <c r="Q244" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R244" s="36"/>
+      <c r="S244" s="16">
+        <v>0.85</v>
+      </c>
+      <c r="T244" s="16">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="245" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K245" s="40"/>
+      <c r="L245" s="40"/>
+      <c r="M245" s="41"/>
+      <c r="N245" s="41"/>
+      <c r="O245" s="41"/>
+      <c r="P245" s="41"/>
+      <c r="Q245" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R245" s="34"/>
+      <c r="S245" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="T245" s="15">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="246" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K246" s="40"/>
+      <c r="L246" s="40"/>
+      <c r="M246" s="41"/>
+      <c r="N246" s="41"/>
+      <c r="O246" s="41"/>
+      <c r="P246" s="41"/>
+      <c r="Q246" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R246" s="37"/>
+      <c r="S246" s="16">
+        <v>0.76</v>
+      </c>
+      <c r="T246" s="16">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="247" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K247" s="40"/>
+      <c r="L247" s="40"/>
+      <c r="M247" s="41"/>
+      <c r="N247" s="41"/>
+      <c r="O247" s="41"/>
+      <c r="P247" s="41"/>
+      <c r="Q247" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R247" s="34"/>
+      <c r="S247" s="15">
+        <v>0.87</v>
+      </c>
+      <c r="T247" s="15">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="248" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K248" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L248" s="40"/>
+      <c r="M248" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="N248" s="41"/>
+      <c r="O248" s="41"/>
+      <c r="P248" s="41"/>
+      <c r="Q248" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="R248" s="34"/>
+      <c r="S248" s="30">
+        <v>0.96</v>
+      </c>
+      <c r="T248" s="30">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="249" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K249" s="40"/>
+      <c r="L249" s="40"/>
+      <c r="M249" s="41"/>
+      <c r="N249" s="41"/>
+      <c r="O249" s="41"/>
+      <c r="P249" s="41"/>
+      <c r="Q249" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R249" s="36"/>
+      <c r="S249" s="25">
+        <v>0.85</v>
+      </c>
+      <c r="T249" s="26">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="250" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K250" s="40"/>
+      <c r="L250" s="40"/>
+      <c r="M250" s="41"/>
+      <c r="N250" s="41"/>
+      <c r="O250" s="41"/>
+      <c r="P250" s="41"/>
+      <c r="Q250" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="R250" s="34"/>
+      <c r="S250" s="24">
+        <v>0.84</v>
+      </c>
+      <c r="T250" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="251" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K251" s="40"/>
+      <c r="L251" s="40"/>
+      <c r="M251" s="41"/>
+      <c r="N251" s="41"/>
+      <c r="O251" s="41"/>
+      <c r="P251" s="41"/>
+      <c r="Q251" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R251" s="37"/>
+      <c r="S251" s="25">
+        <v>0.71</v>
+      </c>
+      <c r="T251" s="25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="252" spans="11:20" x14ac:dyDescent="0.35">
+      <c r="K252" s="40"/>
+      <c r="L252" s="40"/>
+      <c r="M252" s="41"/>
+      <c r="N252" s="41"/>
+      <c r="O252" s="41"/>
+      <c r="P252" s="41"/>
+      <c r="Q252" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="R252" s="34"/>
+      <c r="S252" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="T252" s="27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="302" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="I302" t="s">
+        <v>18</v>
+      </c>
+      <c r="J302" t="s">
+        <v>103</v>
+      </c>
+      <c r="K302" t="s">
+        <v>104</v>
+      </c>
+      <c r="L302" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="303" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="I303" s="17">
+        <v>0.84</v>
+      </c>
+      <c r="J303" s="17">
+        <v>0.83</v>
+      </c>
+      <c r="K303">
+        <v>0.84</v>
+      </c>
+      <c r="L303" s="17">
+        <v>0.8</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="130">
-    <mergeCell ref="G23:J27"/>
-    <mergeCell ref="G8:J12"/>
-    <mergeCell ref="E8:F12"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K9:L9"/>
+  <mergeCells count="242">
+    <mergeCell ref="K243:L247"/>
+    <mergeCell ref="M243:P247"/>
+    <mergeCell ref="Q243:R243"/>
+    <mergeCell ref="Q244:R244"/>
+    <mergeCell ref="Q245:R245"/>
+    <mergeCell ref="Q246:R246"/>
+    <mergeCell ref="Q247:R247"/>
+    <mergeCell ref="K248:L252"/>
+    <mergeCell ref="M248:P252"/>
+    <mergeCell ref="Q248:R248"/>
+    <mergeCell ref="Q249:R249"/>
+    <mergeCell ref="Q250:R250"/>
+    <mergeCell ref="Q251:R251"/>
+    <mergeCell ref="Q252:R252"/>
+    <mergeCell ref="K233:L237"/>
+    <mergeCell ref="M233:P237"/>
+    <mergeCell ref="Q233:R233"/>
+    <mergeCell ref="Q234:R234"/>
+    <mergeCell ref="Q235:R235"/>
+    <mergeCell ref="Q236:R236"/>
+    <mergeCell ref="Q237:R237"/>
+    <mergeCell ref="K238:L242"/>
+    <mergeCell ref="M238:P242"/>
+    <mergeCell ref="Q238:R238"/>
+    <mergeCell ref="Q239:R239"/>
+    <mergeCell ref="Q240:R240"/>
+    <mergeCell ref="Q241:R241"/>
+    <mergeCell ref="Q242:R242"/>
+    <mergeCell ref="K223:L227"/>
+    <mergeCell ref="M223:P227"/>
+    <mergeCell ref="Q223:R223"/>
+    <mergeCell ref="Q224:R224"/>
+    <mergeCell ref="Q225:R225"/>
+    <mergeCell ref="Q226:R226"/>
+    <mergeCell ref="Q227:R227"/>
+    <mergeCell ref="K228:L232"/>
+    <mergeCell ref="M228:P232"/>
+    <mergeCell ref="Q228:R228"/>
+    <mergeCell ref="Q229:R229"/>
+    <mergeCell ref="Q230:R230"/>
+    <mergeCell ref="Q231:R231"/>
+    <mergeCell ref="Q232:R232"/>
+    <mergeCell ref="K213:L217"/>
+    <mergeCell ref="M213:P217"/>
+    <mergeCell ref="Q213:R213"/>
+    <mergeCell ref="Q214:R214"/>
+    <mergeCell ref="Q215:R215"/>
+    <mergeCell ref="Q216:R216"/>
+    <mergeCell ref="Q217:R217"/>
+    <mergeCell ref="K218:L222"/>
+    <mergeCell ref="M218:P222"/>
+    <mergeCell ref="Q218:R218"/>
+    <mergeCell ref="Q219:R219"/>
+    <mergeCell ref="Q220:R220"/>
+    <mergeCell ref="Q221:R221"/>
+    <mergeCell ref="Q222:R222"/>
+    <mergeCell ref="K203:L207"/>
+    <mergeCell ref="M203:P207"/>
+    <mergeCell ref="Q203:R203"/>
+    <mergeCell ref="Q204:R204"/>
+    <mergeCell ref="Q205:R205"/>
+    <mergeCell ref="Q206:R206"/>
+    <mergeCell ref="Q207:R207"/>
+    <mergeCell ref="K208:L212"/>
+    <mergeCell ref="M208:P212"/>
+    <mergeCell ref="Q208:R208"/>
+    <mergeCell ref="Q209:R209"/>
+    <mergeCell ref="Q210:R210"/>
+    <mergeCell ref="Q211:R211"/>
+    <mergeCell ref="Q212:R212"/>
+    <mergeCell ref="K193:L197"/>
+    <mergeCell ref="M193:P197"/>
+    <mergeCell ref="Q193:R193"/>
+    <mergeCell ref="Q194:R194"/>
+    <mergeCell ref="Q195:R195"/>
+    <mergeCell ref="Q196:R196"/>
+    <mergeCell ref="Q197:R197"/>
+    <mergeCell ref="K198:L202"/>
+    <mergeCell ref="M198:P202"/>
+    <mergeCell ref="Q198:R198"/>
+    <mergeCell ref="Q199:R199"/>
+    <mergeCell ref="Q200:R200"/>
+    <mergeCell ref="Q201:R201"/>
+    <mergeCell ref="Q202:R202"/>
+    <mergeCell ref="K183:L187"/>
+    <mergeCell ref="M183:P187"/>
+    <mergeCell ref="Q183:R183"/>
+    <mergeCell ref="Q184:R184"/>
+    <mergeCell ref="Q185:R185"/>
+    <mergeCell ref="Q186:R186"/>
+    <mergeCell ref="Q187:R187"/>
+    <mergeCell ref="K188:L192"/>
+    <mergeCell ref="M188:P192"/>
+    <mergeCell ref="Q188:R188"/>
+    <mergeCell ref="Q189:R189"/>
+    <mergeCell ref="Q190:R190"/>
+    <mergeCell ref="Q191:R191"/>
+    <mergeCell ref="Q192:R192"/>
+    <mergeCell ref="K173:L177"/>
+    <mergeCell ref="M173:P177"/>
+    <mergeCell ref="Q173:R173"/>
+    <mergeCell ref="Q174:R174"/>
+    <mergeCell ref="Q175:R175"/>
+    <mergeCell ref="Q176:R176"/>
+    <mergeCell ref="Q177:R177"/>
+    <mergeCell ref="K178:L182"/>
+    <mergeCell ref="M178:P182"/>
+    <mergeCell ref="Q178:R178"/>
+    <mergeCell ref="Q179:R179"/>
+    <mergeCell ref="Q180:R180"/>
+    <mergeCell ref="Q181:R181"/>
+    <mergeCell ref="Q182:R182"/>
     <mergeCell ref="K10:L10"/>
     <mergeCell ref="K11:L11"/>
     <mergeCell ref="D2:T2"/>
@@ -6723,6 +9315,11 @@
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="K21:L21"/>
     <mergeCell ref="K22:L22"/>
+    <mergeCell ref="G23:J27"/>
+    <mergeCell ref="G8:J12"/>
+    <mergeCell ref="E8:F12"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K9:L9"/>
     <mergeCell ref="D28:D47"/>
     <mergeCell ref="E28:F32"/>
     <mergeCell ref="G28:J32"/>
@@ -6747,11 +9344,6 @@
     <mergeCell ref="K46:L46"/>
     <mergeCell ref="K47:L47"/>
     <mergeCell ref="G38:J42"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="K42:L42"/>
     <mergeCell ref="D48:D67"/>
     <mergeCell ref="E48:F52"/>
     <mergeCell ref="G48:J52"/>
@@ -6771,16 +9363,31 @@
     <mergeCell ref="E63:F67"/>
     <mergeCell ref="G63:J67"/>
     <mergeCell ref="K63:L63"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="K66:L66"/>
-    <mergeCell ref="K67:L67"/>
     <mergeCell ref="G58:J62"/>
     <mergeCell ref="K58:L58"/>
     <mergeCell ref="K59:L59"/>
     <mergeCell ref="K60:L60"/>
     <mergeCell ref="K61:L61"/>
     <mergeCell ref="K62:L62"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="K84:L84"/>
+    <mergeCell ref="K85:L85"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="G78:J82"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="K66:L66"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="K82:L82"/>
     <mergeCell ref="D68:D87"/>
     <mergeCell ref="E68:F72"/>
     <mergeCell ref="G68:J72"/>
@@ -6800,18 +9407,9 @@
     <mergeCell ref="E83:F87"/>
     <mergeCell ref="G83:J87"/>
     <mergeCell ref="K83:L83"/>
-    <mergeCell ref="K84:L84"/>
-    <mergeCell ref="K85:L85"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="G78:J82"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="K79:L79"/>
-    <mergeCell ref="K80:L80"/>
-    <mergeCell ref="K81:L81"/>
-    <mergeCell ref="K82:L82"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Expereiments/MessageFiltering.xlsx
+++ b/Expereiments/MessageFiltering.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ورقة1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="155">
   <si>
     <t>#</t>
   </si>
@@ -1201,89 +1202,6 @@
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1301,6 +1219,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1358,6 +1282,83 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1418,6 +1419,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2461,6 +2463,415 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ar-SA"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AB$156:$AB$157</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>F1 Score</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Train</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$AA$158:$AA$162</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>mBert +KNN</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FastText + SVM</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>AraBert +NN</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>TF-IDF +KNN</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Distilli mBert +SVM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AB$158:$AB$162</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7F4C-446C-8E2D-61685E0C3C0C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AC$156:$AC$157</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>F1 Score</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Test</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$AA$158:$AA$162</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>mBert +KNN</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FastText + SVM</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>AraBert +NN</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>TF-IDF +KNN</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Distilli mBert +SVM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AC$158:$AC$162</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.74</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7F4C-446C-8E2D-61685E0C3C0C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="437288200"/>
+        <c:axId val="366803208"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="437288200"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="366803208"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="366803208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="437288200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -2476,6 +2887,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2802,6 +3214,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2883,6 +3296,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3209,6 +3623,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3290,6 +3705,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3338,7 +3754,7 @@
                   <c:v>F1 Score</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Test</c:v>
+                  <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3383,19 +3799,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.8</c:v>
+                  <c:v>0.83</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.79</c:v>
+                  <c:v>0.86</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.79</c:v>
+                  <c:v>0.85</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.78</c:v>
+                  <c:v>0.82</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.74</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4466,6 +4882,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4756,6 +5173,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5724,6 +6142,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -7051,6 +7509,509 @@
 </file>
 
 <file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -11909,6 +12870,36 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>345722</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>71261</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>175</xdr:row>
+      <xdr:rowOff>48683</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="مخطط 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -12226,25 +13217,25 @@
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="108" t="s">
+      <c r="D2" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109"/>
-      <c r="K2" s="109"/>
-      <c r="L2" s="109"/>
-      <c r="M2" s="109"/>
-      <c r="N2" s="109"/>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="109"/>
-      <c r="R2" s="109"/>
-      <c r="S2" s="109"/>
-      <c r="T2" s="109"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="82"/>
+      <c r="T2" s="82"/>
       <c r="U2" s="3"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
@@ -12263,25 +13254,25 @@
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="115" t="s">
+      <c r="D3" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="115"/>
-      <c r="L3" s="115"/>
-      <c r="M3" s="115"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="Q3" s="115"/>
-      <c r="R3" s="115"/>
-      <c r="S3" s="115"/>
-      <c r="T3" s="115"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
       <c r="U3" s="3"/>
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
@@ -12300,23 +13291,23 @@
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116"/>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116"/>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
       <c r="U4" s="3"/>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
@@ -12338,30 +13329,30 @@
       <c r="D5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="110" t="s">
+      <c r="E5" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="110"/>
-      <c r="G5" s="111" t="s">
+      <c r="F5" s="83"/>
+      <c r="G5" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="112"/>
-      <c r="I5" s="112"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="117" t="s">
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="86"/>
+      <c r="K5" s="90" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="118"/>
-      <c r="M5" s="111" t="s">
+      <c r="L5" s="91"/>
+      <c r="M5" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="N5" s="112"/>
-      <c r="O5" s="112"/>
-      <c r="P5" s="112"/>
-      <c r="Q5" s="112"/>
-      <c r="R5" s="112"/>
-      <c r="S5" s="112"/>
-      <c r="T5" s="113"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="86"/>
       <c r="U5" s="3"/>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
@@ -12380,31 +13371,31 @@
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="114"/>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="120"/>
-      <c r="I6" s="120"/>
-      <c r="J6" s="121"/>
-      <c r="K6" s="103"/>
-      <c r="L6" s="103"/>
-      <c r="M6" s="125" t="s">
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="94"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="N6" s="126"/>
-      <c r="O6" s="125" t="s">
+      <c r="N6" s="99"/>
+      <c r="O6" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="126"/>
-      <c r="Q6" s="125" t="s">
+      <c r="P6" s="99"/>
+      <c r="Q6" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="R6" s="126"/>
-      <c r="S6" s="125" t="s">
+      <c r="R6" s="99"/>
+      <c r="S6" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="T6" s="126"/>
+      <c r="T6" s="99"/>
       <c r="U6" s="3"/>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
@@ -12423,15 +13414,15 @@
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="114"/>
-      <c r="F7" s="114"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="123"/>
-      <c r="I7" s="123"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="103"/>
-      <c r="L7" s="103"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
       <c r="M7" s="1" t="s">
         <v>5</v>
       </c>
@@ -12474,23 +13465,23 @@
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="100" t="s">
+      <c r="D8" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="102" t="s">
+      <c r="E8" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="102"/>
-      <c r="G8" s="103" t="s">
+      <c r="F8" s="73"/>
+      <c r="G8" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="103"/>
-      <c r="I8" s="103"/>
-      <c r="J8" s="103"/>
-      <c r="K8" s="104" t="s">
+      <c r="H8" s="74"/>
+      <c r="I8" s="74"/>
+      <c r="J8" s="74"/>
+      <c r="K8" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="104"/>
+      <c r="L8" s="75"/>
       <c r="M8" s="15" t="s">
         <v>27</v>
       </c>
@@ -12533,17 +13524,17 @@
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="103"/>
-      <c r="J9" s="103"/>
-      <c r="K9" s="105" t="s">
+      <c r="D9" s="80"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="74"/>
+      <c r="I9" s="74"/>
+      <c r="J9" s="74"/>
+      <c r="K9" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L9" s="106"/>
+      <c r="L9" s="77"/>
       <c r="M9" s="16" t="s">
         <v>32</v>
       </c>
@@ -12586,17 +13577,17 @@
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="102"/>
-      <c r="F10" s="102"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="103"/>
-      <c r="I10" s="103"/>
-      <c r="J10" s="103"/>
-      <c r="K10" s="104" t="s">
+      <c r="D10" s="80"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="74"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L10" s="104"/>
+      <c r="L10" s="75"/>
       <c r="M10" s="15" t="s">
         <v>34</v>
       </c>
@@ -12639,17 +13630,17 @@
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="103"/>
-      <c r="J11" s="103"/>
-      <c r="K11" s="107" t="s">
+      <c r="D11" s="80"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="74"/>
+      <c r="K11" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="107"/>
+      <c r="L11" s="78"/>
       <c r="M11" s="16">
         <v>0.73</v>
       </c>
@@ -12692,17 +13683,17 @@
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="103"/>
-      <c r="H12" s="103"/>
-      <c r="I12" s="103"/>
-      <c r="J12" s="103"/>
-      <c r="K12" s="104" t="s">
+      <c r="D12" s="80"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="104"/>
+      <c r="L12" s="75"/>
       <c r="M12" s="15">
         <v>0.84</v>
       </c>
@@ -12745,21 +13736,21 @@
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="102" t="s">
+      <c r="D13" s="80"/>
+      <c r="E13" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="102"/>
-      <c r="G13" s="103" t="s">
+      <c r="F13" s="73"/>
+      <c r="G13" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="H13" s="103"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="103"/>
-      <c r="K13" s="104" t="s">
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="74"/>
+      <c r="K13" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L13" s="104"/>
+      <c r="L13" s="75"/>
       <c r="M13" s="15" t="s">
         <v>46</v>
       </c>
@@ -12802,17 +13793,17 @@
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="102"/>
-      <c r="F14" s="102"/>
-      <c r="G14" s="103"/>
-      <c r="H14" s="103"/>
-      <c r="I14" s="103"/>
-      <c r="J14" s="103"/>
-      <c r="K14" s="105" t="s">
+      <c r="D14" s="80"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L14" s="106"/>
+      <c r="L14" s="77"/>
       <c r="M14" s="16" t="s">
         <v>50</v>
       </c>
@@ -12855,17 +13846,17 @@
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="102"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="103"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="103"/>
-      <c r="J15" s="103"/>
-      <c r="K15" s="104" t="s">
+      <c r="D15" s="80"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="74"/>
+      <c r="K15" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L15" s="104"/>
+      <c r="L15" s="75"/>
       <c r="M15" s="18" t="s">
         <v>55</v>
       </c>
@@ -12908,17 +13899,17 @@
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="102"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="103"/>
-      <c r="H16" s="103"/>
-      <c r="I16" s="103"/>
-      <c r="J16" s="103"/>
-      <c r="K16" s="107" t="s">
+      <c r="D16" s="80"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="74"/>
+      <c r="K16" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L16" s="107"/>
+      <c r="L16" s="78"/>
       <c r="M16" s="16" t="s">
         <v>59</v>
       </c>
@@ -12961,17 +13952,17 @@
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="101"/>
-      <c r="E17" s="102"/>
-      <c r="F17" s="102"/>
-      <c r="G17" s="103"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="103"/>
-      <c r="J17" s="103"/>
-      <c r="K17" s="104" t="s">
+      <c r="D17" s="80"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="74"/>
+      <c r="I17" s="74"/>
+      <c r="J17" s="74"/>
+      <c r="K17" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L17" s="104"/>
+      <c r="L17" s="75"/>
       <c r="M17" s="15" t="s">
         <v>58</v>
       </c>
@@ -13014,21 +14005,21 @@
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="101"/>
-      <c r="E18" s="102" t="s">
+      <c r="D18" s="80"/>
+      <c r="E18" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="102"/>
-      <c r="G18" s="103" t="s">
+      <c r="F18" s="73"/>
+      <c r="G18" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="103"/>
-      <c r="I18" s="103"/>
-      <c r="J18" s="103"/>
-      <c r="K18" s="104" t="s">
+      <c r="H18" s="74"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="74"/>
+      <c r="K18" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L18" s="104"/>
+      <c r="L18" s="75"/>
       <c r="M18" s="18" t="s">
         <v>69</v>
       </c>
@@ -13071,17 +14062,17 @@
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="101"/>
-      <c r="E19" s="102"/>
-      <c r="F19" s="102"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="103"/>
-      <c r="J19" s="103"/>
-      <c r="K19" s="105" t="s">
+      <c r="D19" s="80"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="74"/>
+      <c r="K19" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L19" s="106"/>
+      <c r="L19" s="77"/>
       <c r="M19" s="16" t="s">
         <v>46</v>
       </c>
@@ -13124,17 +14115,17 @@
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="101"/>
-      <c r="E20" s="102"/>
-      <c r="F20" s="102"/>
-      <c r="G20" s="103"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="103"/>
-      <c r="J20" s="103"/>
-      <c r="K20" s="104" t="s">
+      <c r="D20" s="80"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="74"/>
+      <c r="K20" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L20" s="104"/>
+      <c r="L20" s="75"/>
       <c r="M20" s="15" t="s">
         <v>50</v>
       </c>
@@ -13177,17 +14168,17 @@
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
-      <c r="D21" s="101"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="102"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="103"/>
-      <c r="J21" s="103"/>
-      <c r="K21" s="107" t="s">
+      <c r="D21" s="80"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="74"/>
+      <c r="K21" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L21" s="107"/>
+      <c r="L21" s="78"/>
       <c r="M21" s="16" t="s">
         <v>73</v>
       </c>
@@ -13230,17 +14221,17 @@
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="101"/>
-      <c r="E22" s="102"/>
-      <c r="F22" s="102"/>
-      <c r="G22" s="103"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="103"/>
-      <c r="J22" s="103"/>
-      <c r="K22" s="104" t="s">
+      <c r="D22" s="80"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="74"/>
+      <c r="K22" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L22" s="104"/>
+      <c r="L22" s="75"/>
       <c r="M22" s="15" t="s">
         <v>27</v>
       </c>
@@ -13283,21 +14274,21 @@
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
-      <c r="D23" s="101"/>
-      <c r="E23" s="102" t="s">
+      <c r="D23" s="80"/>
+      <c r="E23" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="102"/>
-      <c r="G23" s="103" t="s">
+      <c r="F23" s="73"/>
+      <c r="G23" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="H23" s="103"/>
-      <c r="I23" s="103"/>
-      <c r="J23" s="103"/>
-      <c r="K23" s="104" t="s">
+      <c r="H23" s="74"/>
+      <c r="I23" s="74"/>
+      <c r="J23" s="74"/>
+      <c r="K23" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L23" s="104"/>
+      <c r="L23" s="75"/>
       <c r="M23" s="18">
         <v>0.99</v>
       </c>
@@ -13340,17 +14331,17 @@
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
-      <c r="D24" s="101"/>
-      <c r="E24" s="102"/>
-      <c r="F24" s="102"/>
-      <c r="G24" s="103"/>
-      <c r="H24" s="103"/>
-      <c r="I24" s="103"/>
-      <c r="J24" s="103"/>
-      <c r="K24" s="105" t="s">
+      <c r="D24" s="80"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="74"/>
+      <c r="K24" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L24" s="106"/>
+      <c r="L24" s="77"/>
       <c r="M24" s="16">
         <v>0.84</v>
       </c>
@@ -13393,17 +14384,17 @@
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="102"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="103"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="103"/>
-      <c r="J25" s="103"/>
-      <c r="K25" s="104" t="s">
+      <c r="D25" s="80"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="74"/>
+      <c r="K25" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L25" s="104"/>
+      <c r="L25" s="75"/>
       <c r="M25" s="15">
         <v>0.87</v>
       </c>
@@ -13446,17 +14437,17 @@
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="102"/>
-      <c r="F26" s="102"/>
-      <c r="G26" s="103"/>
-      <c r="H26" s="103"/>
-      <c r="I26" s="103"/>
-      <c r="J26" s="103"/>
-      <c r="K26" s="107" t="s">
+      <c r="D26" s="80"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="74"/>
+      <c r="K26" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L26" s="107"/>
+      <c r="L26" s="78"/>
       <c r="M26" s="16">
         <v>0.69</v>
       </c>
@@ -13499,17 +14490,17 @@
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
-      <c r="D27" s="101"/>
-      <c r="E27" s="102"/>
-      <c r="F27" s="102"/>
-      <c r="G27" s="103"/>
-      <c r="H27" s="103"/>
-      <c r="I27" s="103"/>
-      <c r="J27" s="103"/>
-      <c r="K27" s="104" t="s">
+      <c r="D27" s="80"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="74"/>
+      <c r="K27" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L27" s="104"/>
+      <c r="L27" s="75"/>
       <c r="M27" s="15">
         <v>0.89</v>
       </c>
@@ -13552,23 +14543,23 @@
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="100" t="s">
+      <c r="D28" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="102" t="s">
+      <c r="E28" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="F28" s="102"/>
-      <c r="G28" s="103" t="s">
+      <c r="F28" s="73"/>
+      <c r="G28" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="103"/>
-      <c r="I28" s="103"/>
-      <c r="J28" s="103"/>
-      <c r="K28" s="104" t="s">
+      <c r="H28" s="74"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="74"/>
+      <c r="K28" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L28" s="104"/>
+      <c r="L28" s="75"/>
       <c r="M28" s="23">
         <v>0.83</v>
       </c>
@@ -13611,17 +14602,17 @@
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="101"/>
-      <c r="E29" s="102"/>
-      <c r="F29" s="102"/>
-      <c r="G29" s="103"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="103"/>
-      <c r="J29" s="103"/>
-      <c r="K29" s="105" t="s">
+      <c r="D29" s="80"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="74"/>
+      <c r="K29" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L29" s="106"/>
+      <c r="L29" s="77"/>
       <c r="M29" s="16">
         <v>0.85</v>
       </c>
@@ -13664,17 +14655,17 @@
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="101"/>
-      <c r="E30" s="102"/>
-      <c r="F30" s="102"/>
-      <c r="G30" s="103"/>
-      <c r="H30" s="103"/>
-      <c r="I30" s="103"/>
-      <c r="J30" s="103"/>
-      <c r="K30" s="104" t="s">
+      <c r="D30" s="80"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="74"/>
+      <c r="K30" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L30" s="104"/>
+      <c r="L30" s="75"/>
       <c r="M30" s="15">
         <v>0.85</v>
       </c>
@@ -13717,17 +14708,17 @@
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
-      <c r="D31" s="101"/>
-      <c r="E31" s="102"/>
-      <c r="F31" s="102"/>
-      <c r="G31" s="103"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="103"/>
-      <c r="J31" s="103"/>
-      <c r="K31" s="107" t="s">
+      <c r="D31" s="80"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="107"/>
+      <c r="L31" s="78"/>
       <c r="M31" s="16">
         <v>0.73</v>
       </c>
@@ -13770,17 +14761,17 @@
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="101"/>
-      <c r="E32" s="102"/>
-      <c r="F32" s="102"/>
-      <c r="G32" s="103"/>
-      <c r="H32" s="103"/>
-      <c r="I32" s="103"/>
-      <c r="J32" s="103"/>
-      <c r="K32" s="104" t="s">
+      <c r="D32" s="80"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="74"/>
+      <c r="H32" s="74"/>
+      <c r="I32" s="74"/>
+      <c r="J32" s="74"/>
+      <c r="K32" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L32" s="104"/>
+      <c r="L32" s="75"/>
       <c r="M32" s="15">
         <v>0.84</v>
       </c>
@@ -13823,21 +14814,21 @@
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
-      <c r="D33" s="101"/>
-      <c r="E33" s="102" t="s">
+      <c r="D33" s="80"/>
+      <c r="E33" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="102"/>
-      <c r="G33" s="103" t="s">
+      <c r="F33" s="73"/>
+      <c r="G33" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="H33" s="103"/>
-      <c r="I33" s="103"/>
-      <c r="J33" s="103"/>
-      <c r="K33" s="104" t="s">
+      <c r="H33" s="74"/>
+      <c r="I33" s="74"/>
+      <c r="J33" s="74"/>
+      <c r="K33" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L33" s="104"/>
+      <c r="L33" s="75"/>
       <c r="M33" s="15">
         <v>0.84</v>
       </c>
@@ -13880,17 +14871,17 @@
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="101"/>
-      <c r="E34" s="102"/>
-      <c r="F34" s="102"/>
-      <c r="G34" s="103"/>
-      <c r="H34" s="103"/>
-      <c r="I34" s="103"/>
-      <c r="J34" s="103"/>
-      <c r="K34" s="105" t="s">
+      <c r="D34" s="80"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="74"/>
+      <c r="I34" s="74"/>
+      <c r="J34" s="74"/>
+      <c r="K34" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L34" s="106"/>
+      <c r="L34" s="77"/>
       <c r="M34" s="16">
         <v>0.85</v>
       </c>
@@ -13933,17 +14924,17 @@
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="101"/>
-      <c r="E35" s="102"/>
-      <c r="F35" s="102"/>
-      <c r="G35" s="103"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="103"/>
-      <c r="J35" s="103"/>
-      <c r="K35" s="104" t="s">
+      <c r="D35" s="80"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="74"/>
+      <c r="I35" s="74"/>
+      <c r="J35" s="74"/>
+      <c r="K35" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L35" s="104"/>
+      <c r="L35" s="75"/>
       <c r="M35" s="15">
         <v>0.88</v>
       </c>
@@ -13986,17 +14977,17 @@
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="101"/>
-      <c r="E36" s="102"/>
-      <c r="F36" s="102"/>
-      <c r="G36" s="103"/>
-      <c r="H36" s="103"/>
-      <c r="I36" s="103"/>
-      <c r="J36" s="103"/>
-      <c r="K36" s="107" t="s">
+      <c r="D36" s="80"/>
+      <c r="E36" s="73"/>
+      <c r="F36" s="73"/>
+      <c r="G36" s="74"/>
+      <c r="H36" s="74"/>
+      <c r="I36" s="74"/>
+      <c r="J36" s="74"/>
+      <c r="K36" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L36" s="107"/>
+      <c r="L36" s="78"/>
       <c r="M36" s="16">
         <v>0.78</v>
       </c>
@@ -14039,17 +15030,17 @@
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="101"/>
-      <c r="E37" s="102"/>
-      <c r="F37" s="102"/>
-      <c r="G37" s="103"/>
-      <c r="H37" s="103"/>
-      <c r="I37" s="103"/>
-      <c r="J37" s="103"/>
-      <c r="K37" s="104" t="s">
+      <c r="D37" s="80"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="73"/>
+      <c r="G37" s="74"/>
+      <c r="H37" s="74"/>
+      <c r="I37" s="74"/>
+      <c r="J37" s="74"/>
+      <c r="K37" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L37" s="104"/>
+      <c r="L37" s="75"/>
       <c r="M37" s="15">
         <v>0.86</v>
       </c>
@@ -14092,21 +15083,21 @@
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="101"/>
-      <c r="E38" s="102" t="s">
+      <c r="D38" s="80"/>
+      <c r="E38" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="F38" s="102"/>
-      <c r="G38" s="103" t="s">
+      <c r="F38" s="73"/>
+      <c r="G38" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="H38" s="103"/>
-      <c r="I38" s="103"/>
-      <c r="J38" s="103"/>
-      <c r="K38" s="104" t="s">
+      <c r="H38" s="74"/>
+      <c r="I38" s="74"/>
+      <c r="J38" s="74"/>
+      <c r="K38" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L38" s="104"/>
+      <c r="L38" s="75"/>
       <c r="M38" s="15"/>
       <c r="N38" s="15"/>
       <c r="O38" s="15"/>
@@ -14133,17 +15124,17 @@
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="101"/>
-      <c r="E39" s="102"/>
-      <c r="F39" s="102"/>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="103"/>
-      <c r="J39" s="103"/>
-      <c r="K39" s="105" t="s">
+      <c r="D39" s="80"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="74"/>
+      <c r="H39" s="74"/>
+      <c r="I39" s="74"/>
+      <c r="J39" s="74"/>
+      <c r="K39" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L39" s="106"/>
+      <c r="L39" s="77"/>
       <c r="M39" s="16">
         <v>0.83</v>
       </c>
@@ -14186,17 +15177,17 @@
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="101"/>
-      <c r="E40" s="102"/>
-      <c r="F40" s="102"/>
-      <c r="G40" s="103"/>
-      <c r="H40" s="103"/>
-      <c r="I40" s="103"/>
-      <c r="J40" s="103"/>
-      <c r="K40" s="104" t="s">
+      <c r="D40" s="80"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="73"/>
+      <c r="G40" s="74"/>
+      <c r="H40" s="74"/>
+      <c r="I40" s="74"/>
+      <c r="J40" s="74"/>
+      <c r="K40" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L40" s="104"/>
+      <c r="L40" s="75"/>
       <c r="M40" s="15">
         <v>0.84</v>
       </c>
@@ -14239,17 +15230,17 @@
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="101"/>
-      <c r="E41" s="102"/>
-      <c r="F41" s="102"/>
-      <c r="G41" s="103"/>
-      <c r="H41" s="103"/>
-      <c r="I41" s="103"/>
-      <c r="J41" s="103"/>
-      <c r="K41" s="107" t="s">
+      <c r="D41" s="80"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="74"/>
+      <c r="H41" s="74"/>
+      <c r="I41" s="74"/>
+      <c r="J41" s="74"/>
+      <c r="K41" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L41" s="107"/>
+      <c r="L41" s="78"/>
       <c r="M41" s="16">
         <v>0.67</v>
       </c>
@@ -14292,17 +15283,17 @@
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
-      <c r="D42" s="101"/>
-      <c r="E42" s="102"/>
-      <c r="F42" s="102"/>
-      <c r="G42" s="103"/>
-      <c r="H42" s="103"/>
-      <c r="I42" s="103"/>
-      <c r="J42" s="103"/>
-      <c r="K42" s="104" t="s">
+      <c r="D42" s="80"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="74"/>
+      <c r="J42" s="74"/>
+      <c r="K42" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L42" s="104"/>
+      <c r="L42" s="75"/>
       <c r="M42" s="15">
         <v>0.85</v>
       </c>
@@ -14345,21 +15336,21 @@
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
-      <c r="D43" s="101"/>
-      <c r="E43" s="102" t="s">
+      <c r="D43" s="80"/>
+      <c r="E43" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="F43" s="102"/>
-      <c r="G43" s="103" t="s">
+      <c r="F43" s="73"/>
+      <c r="G43" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="H43" s="103"/>
-      <c r="I43" s="103"/>
-      <c r="J43" s="103"/>
-      <c r="K43" s="104" t="s">
+      <c r="H43" s="74"/>
+      <c r="I43" s="74"/>
+      <c r="J43" s="74"/>
+      <c r="K43" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L43" s="104"/>
+      <c r="L43" s="75"/>
       <c r="M43" s="16">
         <v>0.83</v>
       </c>
@@ -14402,17 +15393,17 @@
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
-      <c r="D44" s="101"/>
-      <c r="E44" s="102"/>
-      <c r="F44" s="102"/>
-      <c r="G44" s="103"/>
-      <c r="H44" s="103"/>
-      <c r="I44" s="103"/>
-      <c r="J44" s="103"/>
-      <c r="K44" s="105" t="s">
+      <c r="D44" s="80"/>
+      <c r="E44" s="73"/>
+      <c r="F44" s="73"/>
+      <c r="G44" s="74"/>
+      <c r="H44" s="74"/>
+      <c r="I44" s="74"/>
+      <c r="J44" s="74"/>
+      <c r="K44" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L44" s="106"/>
+      <c r="L44" s="77"/>
       <c r="M44" s="18">
         <v>0.75</v>
       </c>
@@ -14455,17 +15446,17 @@
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
-      <c r="D45" s="101"/>
-      <c r="E45" s="102"/>
-      <c r="F45" s="102"/>
-      <c r="G45" s="103"/>
-      <c r="H45" s="103"/>
-      <c r="I45" s="103"/>
-      <c r="J45" s="103"/>
-      <c r="K45" s="104" t="s">
+      <c r="D45" s="80"/>
+      <c r="E45" s="73"/>
+      <c r="F45" s="73"/>
+      <c r="G45" s="74"/>
+      <c r="H45" s="74"/>
+      <c r="I45" s="74"/>
+      <c r="J45" s="74"/>
+      <c r="K45" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L45" s="104"/>
+      <c r="L45" s="75"/>
       <c r="M45" s="31" t="s">
         <v>88</v>
       </c>
@@ -14508,17 +15499,17 @@
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
-      <c r="D46" s="101"/>
-      <c r="E46" s="102"/>
-      <c r="F46" s="102"/>
-      <c r="G46" s="103"/>
-      <c r="H46" s="103"/>
-      <c r="I46" s="103"/>
-      <c r="J46" s="103"/>
-      <c r="K46" s="107" t="s">
+      <c r="D46" s="80"/>
+      <c r="E46" s="73"/>
+      <c r="F46" s="73"/>
+      <c r="G46" s="74"/>
+      <c r="H46" s="74"/>
+      <c r="I46" s="74"/>
+      <c r="J46" s="74"/>
+      <c r="K46" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L46" s="107"/>
+      <c r="L46" s="78"/>
       <c r="M46" s="32">
         <v>0.85</v>
       </c>
@@ -14561,17 +15552,17 @@
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
-      <c r="D47" s="101"/>
-      <c r="E47" s="102"/>
-      <c r="F47" s="102"/>
-      <c r="G47" s="103"/>
-      <c r="H47" s="103"/>
-      <c r="I47" s="103"/>
-      <c r="J47" s="103"/>
-      <c r="K47" s="104" t="s">
+      <c r="D47" s="80"/>
+      <c r="E47" s="73"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="74"/>
+      <c r="H47" s="74"/>
+      <c r="I47" s="74"/>
+      <c r="J47" s="74"/>
+      <c r="K47" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L47" s="104"/>
+      <c r="L47" s="75"/>
       <c r="M47" s="15">
         <v>0.86</v>
       </c>
@@ -14614,23 +15605,23 @@
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
-      <c r="D48" s="100" t="s">
+      <c r="D48" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="E48" s="102" t="s">
+      <c r="E48" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="F48" s="102"/>
-      <c r="G48" s="103" t="s">
+      <c r="F48" s="73"/>
+      <c r="G48" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="H48" s="103"/>
-      <c r="I48" s="103"/>
-      <c r="J48" s="103"/>
-      <c r="K48" s="104" t="s">
+      <c r="H48" s="74"/>
+      <c r="I48" s="74"/>
+      <c r="J48" s="74"/>
+      <c r="K48" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L48" s="104"/>
+      <c r="L48" s="75"/>
       <c r="M48" s="33"/>
       <c r="N48" s="33"/>
       <c r="O48" s="33"/>
@@ -14657,17 +15648,17 @@
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
-      <c r="D49" s="101"/>
-      <c r="E49" s="102"/>
-      <c r="F49" s="102"/>
-      <c r="G49" s="103"/>
-      <c r="H49" s="103"/>
-      <c r="I49" s="103"/>
-      <c r="J49" s="103"/>
-      <c r="K49" s="105" t="s">
+      <c r="D49" s="80"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="73"/>
+      <c r="G49" s="74"/>
+      <c r="H49" s="74"/>
+      <c r="I49" s="74"/>
+      <c r="J49" s="74"/>
+      <c r="K49" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L49" s="106"/>
+      <c r="L49" s="77"/>
       <c r="M49" s="21"/>
       <c r="N49" s="21"/>
       <c r="O49" s="21"/>
@@ -14694,17 +15685,17 @@
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
-      <c r="D50" s="101"/>
-      <c r="E50" s="102"/>
-      <c r="F50" s="102"/>
-      <c r="G50" s="103"/>
-      <c r="H50" s="103"/>
-      <c r="I50" s="103"/>
-      <c r="J50" s="103"/>
-      <c r="K50" s="104" t="s">
+      <c r="D50" s="80"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="73"/>
+      <c r="G50" s="74"/>
+      <c r="H50" s="74"/>
+      <c r="I50" s="74"/>
+      <c r="J50" s="74"/>
+      <c r="K50" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L50" s="104"/>
+      <c r="L50" s="75"/>
       <c r="M50" s="20"/>
       <c r="N50" s="22"/>
       <c r="O50" s="20"/>
@@ -14731,17 +15722,17 @@
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
-      <c r="D51" s="101"/>
-      <c r="E51" s="102"/>
-      <c r="F51" s="102"/>
-      <c r="G51" s="103"/>
-      <c r="H51" s="103"/>
-      <c r="I51" s="103"/>
-      <c r="J51" s="103"/>
-      <c r="K51" s="107" t="s">
+      <c r="D51" s="80"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="73"/>
+      <c r="G51" s="74"/>
+      <c r="H51" s="74"/>
+      <c r="I51" s="74"/>
+      <c r="J51" s="74"/>
+      <c r="K51" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L51" s="107"/>
+      <c r="L51" s="78"/>
       <c r="M51" s="21"/>
       <c r="N51" s="21"/>
       <c r="O51" s="21"/>
@@ -14768,17 +15759,17 @@
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="101"/>
-      <c r="E52" s="102"/>
-      <c r="F52" s="102"/>
-      <c r="G52" s="103"/>
-      <c r="H52" s="103"/>
-      <c r="I52" s="103"/>
-      <c r="J52" s="103"/>
-      <c r="K52" s="104" t="s">
+      <c r="D52" s="80"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="73"/>
+      <c r="G52" s="74"/>
+      <c r="H52" s="74"/>
+      <c r="I52" s="74"/>
+      <c r="J52" s="74"/>
+      <c r="K52" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L52" s="104"/>
+      <c r="L52" s="75"/>
       <c r="M52" s="20"/>
       <c r="N52" s="20"/>
       <c r="O52" s="20"/>
@@ -14805,21 +15796,21 @@
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="101"/>
-      <c r="E53" s="102" t="s">
+      <c r="D53" s="80"/>
+      <c r="E53" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="F53" s="102"/>
-      <c r="G53" s="103" t="s">
+      <c r="F53" s="73"/>
+      <c r="G53" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="H53" s="103"/>
-      <c r="I53" s="103"/>
-      <c r="J53" s="103"/>
-      <c r="K53" s="104" t="s">
+      <c r="H53" s="74"/>
+      <c r="I53" s="74"/>
+      <c r="J53" s="74"/>
+      <c r="K53" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L53" s="104"/>
+      <c r="L53" s="75"/>
       <c r="M53" s="24">
         <v>0.73</v>
       </c>
@@ -14862,17 +15853,17 @@
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
-      <c r="D54" s="101"/>
-      <c r="E54" s="102"/>
-      <c r="F54" s="102"/>
-      <c r="G54" s="103"/>
-      <c r="H54" s="103"/>
-      <c r="I54" s="103"/>
-      <c r="J54" s="103"/>
-      <c r="K54" s="105" t="s">
+      <c r="D54" s="80"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="74"/>
+      <c r="I54" s="74"/>
+      <c r="J54" s="74"/>
+      <c r="K54" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L54" s="106"/>
+      <c r="L54" s="77"/>
       <c r="M54" s="25">
         <v>0.76</v>
       </c>
@@ -14915,17 +15906,17 @@
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
-      <c r="D55" s="101"/>
-      <c r="E55" s="102"/>
-      <c r="F55" s="102"/>
-      <c r="G55" s="103"/>
-      <c r="H55" s="103"/>
-      <c r="I55" s="103"/>
-      <c r="J55" s="103"/>
-      <c r="K55" s="104" t="s">
+      <c r="D55" s="80"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="73"/>
+      <c r="G55" s="74"/>
+      <c r="H55" s="74"/>
+      <c r="I55" s="74"/>
+      <c r="J55" s="74"/>
+      <c r="K55" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L55" s="104"/>
+      <c r="L55" s="75"/>
       <c r="M55" s="24">
         <v>0.82</v>
       </c>
@@ -14968,17 +15959,17 @@
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
-      <c r="D56" s="101"/>
-      <c r="E56" s="102"/>
-      <c r="F56" s="102"/>
-      <c r="G56" s="103"/>
-      <c r="H56" s="103"/>
-      <c r="I56" s="103"/>
-      <c r="J56" s="103"/>
-      <c r="K56" s="107" t="s">
+      <c r="D56" s="80"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="73"/>
+      <c r="G56" s="74"/>
+      <c r="H56" s="74"/>
+      <c r="I56" s="74"/>
+      <c r="J56" s="74"/>
+      <c r="K56" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L56" s="107"/>
+      <c r="L56" s="78"/>
       <c r="M56" s="16">
         <v>0.64</v>
       </c>
@@ -15021,17 +16012,17 @@
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
-      <c r="D57" s="101"/>
-      <c r="E57" s="102"/>
-      <c r="F57" s="102"/>
-      <c r="G57" s="103"/>
-      <c r="H57" s="103"/>
-      <c r="I57" s="103"/>
-      <c r="J57" s="103"/>
-      <c r="K57" s="104" t="s">
+      <c r="D57" s="80"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="73"/>
+      <c r="G57" s="74"/>
+      <c r="H57" s="74"/>
+      <c r="I57" s="74"/>
+      <c r="J57" s="74"/>
+      <c r="K57" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L57" s="104"/>
+      <c r="L57" s="75"/>
       <c r="M57" s="15">
         <v>0.78</v>
       </c>
@@ -15074,21 +16065,21 @@
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="101"/>
-      <c r="E58" s="102" t="s">
+      <c r="D58" s="80"/>
+      <c r="E58" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="F58" s="102"/>
-      <c r="G58" s="103" t="s">
+      <c r="F58" s="73"/>
+      <c r="G58" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="H58" s="103"/>
-      <c r="I58" s="103"/>
-      <c r="J58" s="103"/>
-      <c r="K58" s="104" t="s">
+      <c r="H58" s="74"/>
+      <c r="I58" s="74"/>
+      <c r="J58" s="74"/>
+      <c r="K58" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L58" s="104"/>
+      <c r="L58" s="75"/>
       <c r="M58" s="23">
         <v>0.73</v>
       </c>
@@ -15131,17 +16122,17 @@
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
-      <c r="D59" s="101"/>
-      <c r="E59" s="102"/>
-      <c r="F59" s="102"/>
-      <c r="G59" s="103"/>
-      <c r="H59" s="103"/>
-      <c r="I59" s="103"/>
-      <c r="J59" s="103"/>
-      <c r="K59" s="105" t="s">
+      <c r="D59" s="80"/>
+      <c r="E59" s="73"/>
+      <c r="F59" s="73"/>
+      <c r="G59" s="74"/>
+      <c r="H59" s="74"/>
+      <c r="I59" s="74"/>
+      <c r="J59" s="74"/>
+      <c r="K59" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L59" s="106"/>
+      <c r="L59" s="77"/>
       <c r="M59" s="16">
         <v>0.75</v>
       </c>
@@ -15184,17 +16175,17 @@
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
-      <c r="D60" s="101"/>
-      <c r="E60" s="102"/>
-      <c r="F60" s="102"/>
-      <c r="G60" s="103"/>
-      <c r="H60" s="103"/>
-      <c r="I60" s="103"/>
-      <c r="J60" s="103"/>
-      <c r="K60" s="104" t="s">
+      <c r="D60" s="80"/>
+      <c r="E60" s="73"/>
+      <c r="F60" s="73"/>
+      <c r="G60" s="74"/>
+      <c r="H60" s="74"/>
+      <c r="I60" s="74"/>
+      <c r="J60" s="74"/>
+      <c r="K60" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L60" s="104"/>
+      <c r="L60" s="75"/>
       <c r="M60" s="15">
         <v>0.82</v>
       </c>
@@ -15237,17 +16228,17 @@
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="101"/>
-      <c r="E61" s="102"/>
-      <c r="F61" s="102"/>
-      <c r="G61" s="103"/>
-      <c r="H61" s="103"/>
-      <c r="I61" s="103"/>
-      <c r="J61" s="103"/>
-      <c r="K61" s="107" t="s">
+      <c r="D61" s="80"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="74"/>
+      <c r="H61" s="74"/>
+      <c r="I61" s="74"/>
+      <c r="J61" s="74"/>
+      <c r="K61" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L61" s="107"/>
+      <c r="L61" s="78"/>
       <c r="M61" s="16">
         <v>0.64</v>
       </c>
@@ -15290,17 +16281,17 @@
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="101"/>
-      <c r="E62" s="102"/>
-      <c r="F62" s="102"/>
-      <c r="G62" s="103"/>
-      <c r="H62" s="103"/>
-      <c r="I62" s="103"/>
-      <c r="J62" s="103"/>
-      <c r="K62" s="104" t="s">
+      <c r="D62" s="80"/>
+      <c r="E62" s="73"/>
+      <c r="F62" s="73"/>
+      <c r="G62" s="74"/>
+      <c r="H62" s="74"/>
+      <c r="I62" s="74"/>
+      <c r="J62" s="74"/>
+      <c r="K62" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L62" s="104"/>
+      <c r="L62" s="75"/>
       <c r="M62" s="15">
         <v>0.78</v>
       </c>
@@ -15343,21 +16334,21 @@
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
-      <c r="D63" s="101"/>
-      <c r="E63" s="102" t="s">
+      <c r="D63" s="80"/>
+      <c r="E63" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="F63" s="102"/>
-      <c r="G63" s="103" t="s">
+      <c r="F63" s="73"/>
+      <c r="G63" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="H63" s="103"/>
-      <c r="I63" s="103"/>
-      <c r="J63" s="103"/>
-      <c r="K63" s="104" t="s">
+      <c r="H63" s="74"/>
+      <c r="I63" s="74"/>
+      <c r="J63" s="74"/>
+      <c r="K63" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L63" s="104"/>
+      <c r="L63" s="75"/>
       <c r="M63" s="15" t="s">
         <v>76</v>
       </c>
@@ -15400,17 +16391,17 @@
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="101"/>
-      <c r="E64" s="102"/>
-      <c r="F64" s="102"/>
-      <c r="G64" s="103"/>
-      <c r="H64" s="103"/>
-      <c r="I64" s="103"/>
-      <c r="J64" s="103"/>
-      <c r="K64" s="105" t="s">
+      <c r="D64" s="80"/>
+      <c r="E64" s="73"/>
+      <c r="F64" s="73"/>
+      <c r="G64" s="74"/>
+      <c r="H64" s="74"/>
+      <c r="I64" s="74"/>
+      <c r="J64" s="74"/>
+      <c r="K64" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L64" s="106"/>
+      <c r="L64" s="77"/>
       <c r="M64" s="16" t="s">
         <v>53</v>
       </c>
@@ -15453,17 +16444,17 @@
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="101"/>
-      <c r="E65" s="102"/>
-      <c r="F65" s="102"/>
-      <c r="G65" s="103"/>
-      <c r="H65" s="103"/>
-      <c r="I65" s="103"/>
-      <c r="J65" s="103"/>
-      <c r="K65" s="104" t="s">
+      <c r="D65" s="80"/>
+      <c r="E65" s="73"/>
+      <c r="F65" s="73"/>
+      <c r="G65" s="74"/>
+      <c r="H65" s="74"/>
+      <c r="I65" s="74"/>
+      <c r="J65" s="74"/>
+      <c r="K65" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L65" s="104"/>
+      <c r="L65" s="75"/>
       <c r="M65" s="15" t="s">
         <v>76</v>
       </c>
@@ -15506,17 +16497,17 @@
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="101"/>
-      <c r="E66" s="102"/>
-      <c r="F66" s="102"/>
-      <c r="G66" s="103"/>
-      <c r="H66" s="103"/>
-      <c r="I66" s="103"/>
-      <c r="J66" s="103"/>
-      <c r="K66" s="107" t="s">
+      <c r="D66" s="80"/>
+      <c r="E66" s="73"/>
+      <c r="F66" s="73"/>
+      <c r="G66" s="74"/>
+      <c r="H66" s="74"/>
+      <c r="I66" s="74"/>
+      <c r="J66" s="74"/>
+      <c r="K66" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L66" s="107"/>
+      <c r="L66" s="78"/>
       <c r="M66" s="16" t="s">
         <v>79</v>
       </c>
@@ -15559,17 +16550,17 @@
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="101"/>
-      <c r="E67" s="102"/>
-      <c r="F67" s="102"/>
-      <c r="G67" s="103"/>
-      <c r="H67" s="103"/>
-      <c r="I67" s="103"/>
-      <c r="J67" s="103"/>
-      <c r="K67" s="104" t="s">
+      <c r="D67" s="80"/>
+      <c r="E67" s="73"/>
+      <c r="F67" s="73"/>
+      <c r="G67" s="74"/>
+      <c r="H67" s="74"/>
+      <c r="I67" s="74"/>
+      <c r="J67" s="74"/>
+      <c r="K67" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L67" s="104"/>
+      <c r="L67" s="75"/>
       <c r="M67" s="15" t="s">
         <v>59</v>
       </c>
@@ -15612,23 +16603,23 @@
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
-      <c r="D68" s="100" t="s">
+      <c r="D68" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="E68" s="102" t="s">
+      <c r="E68" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="F68" s="102"/>
-      <c r="G68" s="103" t="s">
+      <c r="F68" s="73"/>
+      <c r="G68" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="H68" s="103"/>
-      <c r="I68" s="103"/>
-      <c r="J68" s="103"/>
-      <c r="K68" s="104" t="s">
+      <c r="H68" s="74"/>
+      <c r="I68" s="74"/>
+      <c r="J68" s="74"/>
+      <c r="K68" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L68" s="104"/>
+      <c r="L68" s="75"/>
       <c r="M68" s="28">
         <v>0.83</v>
       </c>
@@ -15671,17 +16662,17 @@
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="101"/>
-      <c r="E69" s="102"/>
-      <c r="F69" s="102"/>
-      <c r="G69" s="103"/>
-      <c r="H69" s="103"/>
-      <c r="I69" s="103"/>
-      <c r="J69" s="103"/>
-      <c r="K69" s="105" t="s">
+      <c r="D69" s="80"/>
+      <c r="E69" s="73"/>
+      <c r="F69" s="73"/>
+      <c r="G69" s="74"/>
+      <c r="H69" s="74"/>
+      <c r="I69" s="74"/>
+      <c r="J69" s="74"/>
+      <c r="K69" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L69" s="106"/>
+      <c r="L69" s="77"/>
       <c r="M69" s="25">
         <v>0.83</v>
       </c>
@@ -15724,17 +16715,17 @@
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
-      <c r="D70" s="101"/>
-      <c r="E70" s="102"/>
-      <c r="F70" s="102"/>
-      <c r="G70" s="103"/>
-      <c r="H70" s="103"/>
-      <c r="I70" s="103"/>
-      <c r="J70" s="103"/>
-      <c r="K70" s="104" t="s">
+      <c r="D70" s="80"/>
+      <c r="E70" s="73"/>
+      <c r="F70" s="73"/>
+      <c r="G70" s="74"/>
+      <c r="H70" s="74"/>
+      <c r="I70" s="74"/>
+      <c r="J70" s="74"/>
+      <c r="K70" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L70" s="104"/>
+      <c r="L70" s="75"/>
       <c r="M70" s="24">
         <v>0.84</v>
       </c>
@@ -15777,17 +16768,17 @@
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
-      <c r="D71" s="101"/>
-      <c r="E71" s="102"/>
-      <c r="F71" s="102"/>
-      <c r="G71" s="103"/>
-      <c r="H71" s="103"/>
-      <c r="I71" s="103"/>
-      <c r="J71" s="103"/>
-      <c r="K71" s="107" t="s">
+      <c r="D71" s="80"/>
+      <c r="E71" s="73"/>
+      <c r="F71" s="73"/>
+      <c r="G71" s="74"/>
+      <c r="H71" s="74"/>
+      <c r="I71" s="74"/>
+      <c r="J71" s="74"/>
+      <c r="K71" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L71" s="107"/>
+      <c r="L71" s="78"/>
       <c r="M71" s="25">
         <v>0.74</v>
       </c>
@@ -15830,17 +16821,17 @@
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
-      <c r="D72" s="101"/>
-      <c r="E72" s="102"/>
-      <c r="F72" s="102"/>
-      <c r="G72" s="103"/>
-      <c r="H72" s="103"/>
-      <c r="I72" s="103"/>
-      <c r="J72" s="103"/>
-      <c r="K72" s="104" t="s">
+      <c r="D72" s="80"/>
+      <c r="E72" s="73"/>
+      <c r="F72" s="73"/>
+      <c r="G72" s="74"/>
+      <c r="H72" s="74"/>
+      <c r="I72" s="74"/>
+      <c r="J72" s="74"/>
+      <c r="K72" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L72" s="104"/>
+      <c r="L72" s="75"/>
       <c r="M72" s="24">
         <v>0.83</v>
       </c>
@@ -15883,21 +16874,21 @@
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
-      <c r="D73" s="101"/>
-      <c r="E73" s="102" t="s">
+      <c r="D73" s="80"/>
+      <c r="E73" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="F73" s="102"/>
-      <c r="G73" s="103" t="s">
+      <c r="F73" s="73"/>
+      <c r="G73" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="H73" s="103"/>
-      <c r="I73" s="103"/>
-      <c r="J73" s="103"/>
-      <c r="K73" s="104" t="s">
+      <c r="H73" s="74"/>
+      <c r="I73" s="74"/>
+      <c r="J73" s="74"/>
+      <c r="K73" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L73" s="104"/>
+      <c r="L73" s="75"/>
       <c r="M73" s="23">
         <v>0.87</v>
       </c>
@@ -15940,17 +16931,17 @@
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
-      <c r="D74" s="101"/>
-      <c r="E74" s="102"/>
-      <c r="F74" s="102"/>
-      <c r="G74" s="103"/>
-      <c r="H74" s="103"/>
-      <c r="I74" s="103"/>
-      <c r="J74" s="103"/>
-      <c r="K74" s="105" t="s">
+      <c r="D74" s="80"/>
+      <c r="E74" s="73"/>
+      <c r="F74" s="73"/>
+      <c r="G74" s="74"/>
+      <c r="H74" s="74"/>
+      <c r="I74" s="74"/>
+      <c r="J74" s="74"/>
+      <c r="K74" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L74" s="106"/>
+      <c r="L74" s="77"/>
       <c r="M74" s="16">
         <v>0.85</v>
       </c>
@@ -15993,17 +16984,17 @@
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
-      <c r="D75" s="101"/>
-      <c r="E75" s="102"/>
-      <c r="F75" s="102"/>
-      <c r="G75" s="103"/>
-      <c r="H75" s="103"/>
-      <c r="I75" s="103"/>
-      <c r="J75" s="103"/>
-      <c r="K75" s="104" t="s">
+      <c r="D75" s="80"/>
+      <c r="E75" s="73"/>
+      <c r="F75" s="73"/>
+      <c r="G75" s="74"/>
+      <c r="H75" s="74"/>
+      <c r="I75" s="74"/>
+      <c r="J75" s="74"/>
+      <c r="K75" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L75" s="104"/>
+      <c r="L75" s="75"/>
       <c r="M75" s="15">
         <v>0.89</v>
       </c>
@@ -16046,17 +17037,17 @@
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
-      <c r="D76" s="101"/>
-      <c r="E76" s="102"/>
-      <c r="F76" s="102"/>
-      <c r="G76" s="103"/>
-      <c r="H76" s="103"/>
-      <c r="I76" s="103"/>
-      <c r="J76" s="103"/>
-      <c r="K76" s="107" t="s">
+      <c r="D76" s="80"/>
+      <c r="E76" s="73"/>
+      <c r="F76" s="73"/>
+      <c r="G76" s="74"/>
+      <c r="H76" s="74"/>
+      <c r="I76" s="74"/>
+      <c r="J76" s="74"/>
+      <c r="K76" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L76" s="107"/>
+      <c r="L76" s="78"/>
       <c r="M76" s="16">
         <v>0.76</v>
       </c>
@@ -16099,17 +17090,17 @@
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
-      <c r="D77" s="101"/>
-      <c r="E77" s="102"/>
-      <c r="F77" s="102"/>
-      <c r="G77" s="103"/>
-      <c r="H77" s="103"/>
-      <c r="I77" s="103"/>
-      <c r="J77" s="103"/>
-      <c r="K77" s="104" t="s">
+      <c r="D77" s="80"/>
+      <c r="E77" s="73"/>
+      <c r="F77" s="73"/>
+      <c r="G77" s="74"/>
+      <c r="H77" s="74"/>
+      <c r="I77" s="74"/>
+      <c r="J77" s="74"/>
+      <c r="K77" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L77" s="104"/>
+      <c r="L77" s="75"/>
       <c r="M77" s="15">
         <v>0.87</v>
       </c>
@@ -16152,21 +17143,21 @@
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
-      <c r="D78" s="101"/>
-      <c r="E78" s="102" t="s">
+      <c r="D78" s="80"/>
+      <c r="E78" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="F78" s="102"/>
-      <c r="G78" s="103" t="s">
+      <c r="F78" s="73"/>
+      <c r="G78" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="H78" s="103"/>
-      <c r="I78" s="103"/>
-      <c r="J78" s="103"/>
-      <c r="K78" s="104" t="s">
+      <c r="H78" s="74"/>
+      <c r="I78" s="74"/>
+      <c r="J78" s="74"/>
+      <c r="K78" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L78" s="104"/>
+      <c r="L78" s="75"/>
       <c r="M78" s="15">
         <v>0.87</v>
       </c>
@@ -16209,17 +17200,17 @@
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
-      <c r="D79" s="101"/>
-      <c r="E79" s="102"/>
-      <c r="F79" s="102"/>
-      <c r="G79" s="103"/>
-      <c r="H79" s="103"/>
-      <c r="I79" s="103"/>
-      <c r="J79" s="103"/>
-      <c r="K79" s="105" t="s">
+      <c r="D79" s="80"/>
+      <c r="E79" s="73"/>
+      <c r="F79" s="73"/>
+      <c r="G79" s="74"/>
+      <c r="H79" s="74"/>
+      <c r="I79" s="74"/>
+      <c r="J79" s="74"/>
+      <c r="K79" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L79" s="106"/>
+      <c r="L79" s="77"/>
       <c r="M79" s="16">
         <v>0.85</v>
       </c>
@@ -16262,17 +17253,17 @@
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
-      <c r="D80" s="101"/>
-      <c r="E80" s="102"/>
-      <c r="F80" s="102"/>
-      <c r="G80" s="103"/>
-      <c r="H80" s="103"/>
-      <c r="I80" s="103"/>
-      <c r="J80" s="103"/>
-      <c r="K80" s="104" t="s">
+      <c r="D80" s="80"/>
+      <c r="E80" s="73"/>
+      <c r="F80" s="73"/>
+      <c r="G80" s="74"/>
+      <c r="H80" s="74"/>
+      <c r="I80" s="74"/>
+      <c r="J80" s="74"/>
+      <c r="K80" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L80" s="104"/>
+      <c r="L80" s="75"/>
       <c r="M80" s="15">
         <v>0.89</v>
       </c>
@@ -16315,17 +17306,17 @@
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
-      <c r="D81" s="101"/>
-      <c r="E81" s="102"/>
-      <c r="F81" s="102"/>
-      <c r="G81" s="103"/>
-      <c r="H81" s="103"/>
-      <c r="I81" s="103"/>
-      <c r="J81" s="103"/>
-      <c r="K81" s="107" t="s">
+      <c r="D81" s="80"/>
+      <c r="E81" s="73"/>
+      <c r="F81" s="73"/>
+      <c r="G81" s="74"/>
+      <c r="H81" s="74"/>
+      <c r="I81" s="74"/>
+      <c r="J81" s="74"/>
+      <c r="K81" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L81" s="107"/>
+      <c r="L81" s="78"/>
       <c r="M81" s="16">
         <v>0.76</v>
       </c>
@@ -16368,17 +17359,17 @@
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
-      <c r="D82" s="101"/>
-      <c r="E82" s="102"/>
-      <c r="F82" s="102"/>
-      <c r="G82" s="103"/>
-      <c r="H82" s="103"/>
-      <c r="I82" s="103"/>
-      <c r="J82" s="103"/>
-      <c r="K82" s="104" t="s">
+      <c r="D82" s="80"/>
+      <c r="E82" s="73"/>
+      <c r="F82" s="73"/>
+      <c r="G82" s="74"/>
+      <c r="H82" s="74"/>
+      <c r="I82" s="74"/>
+      <c r="J82" s="74"/>
+      <c r="K82" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L82" s="104"/>
+      <c r="L82" s="75"/>
       <c r="M82" s="15">
         <v>0.87</v>
       </c>
@@ -16421,21 +17412,21 @@
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
-      <c r="D83" s="101"/>
-      <c r="E83" s="102" t="s">
+      <c r="D83" s="80"/>
+      <c r="E83" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="F83" s="102"/>
-      <c r="G83" s="103" t="s">
+      <c r="F83" s="73"/>
+      <c r="G83" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="H83" s="103"/>
-      <c r="I83" s="103"/>
-      <c r="J83" s="103"/>
-      <c r="K83" s="104" t="s">
+      <c r="H83" s="74"/>
+      <c r="I83" s="74"/>
+      <c r="J83" s="74"/>
+      <c r="K83" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="L83" s="104"/>
+      <c r="L83" s="75"/>
       <c r="M83" s="30">
         <v>0.96</v>
       </c>
@@ -16478,17 +17469,17 @@
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
-      <c r="D84" s="101"/>
-      <c r="E84" s="102"/>
-      <c r="F84" s="102"/>
-      <c r="G84" s="103"/>
-      <c r="H84" s="103"/>
-      <c r="I84" s="103"/>
-      <c r="J84" s="103"/>
-      <c r="K84" s="105" t="s">
+      <c r="D84" s="80"/>
+      <c r="E84" s="73"/>
+      <c r="F84" s="73"/>
+      <c r="G84" s="74"/>
+      <c r="H84" s="74"/>
+      <c r="I84" s="74"/>
+      <c r="J84" s="74"/>
+      <c r="K84" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="L84" s="106"/>
+      <c r="L84" s="77"/>
       <c r="M84" s="25">
         <v>0.85</v>
       </c>
@@ -16531,17 +17522,17 @@
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
-      <c r="D85" s="101"/>
-      <c r="E85" s="102"/>
-      <c r="F85" s="102"/>
-      <c r="G85" s="103"/>
-      <c r="H85" s="103"/>
-      <c r="I85" s="103"/>
-      <c r="J85" s="103"/>
-      <c r="K85" s="104" t="s">
+      <c r="D85" s="80"/>
+      <c r="E85" s="73"/>
+      <c r="F85" s="73"/>
+      <c r="G85" s="74"/>
+      <c r="H85" s="74"/>
+      <c r="I85" s="74"/>
+      <c r="J85" s="74"/>
+      <c r="K85" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="L85" s="104"/>
+      <c r="L85" s="75"/>
       <c r="M85" s="24">
         <v>0.84</v>
       </c>
@@ -16584,17 +17575,17 @@
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
-      <c r="D86" s="101"/>
-      <c r="E86" s="102"/>
-      <c r="F86" s="102"/>
-      <c r="G86" s="103"/>
-      <c r="H86" s="103"/>
-      <c r="I86" s="103"/>
-      <c r="J86" s="103"/>
-      <c r="K86" s="107" t="s">
+      <c r="D86" s="80"/>
+      <c r="E86" s="73"/>
+      <c r="F86" s="73"/>
+      <c r="G86" s="74"/>
+      <c r="H86" s="74"/>
+      <c r="I86" s="74"/>
+      <c r="J86" s="74"/>
+      <c r="K86" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="L86" s="107"/>
+      <c r="L86" s="78"/>
       <c r="M86" s="25">
         <v>0.71</v>
       </c>
@@ -16635,17 +17626,17 @@
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.35">
       <c r="C87" s="3"/>
-      <c r="D87" s="101"/>
-      <c r="E87" s="102"/>
-      <c r="F87" s="102"/>
-      <c r="G87" s="103"/>
-      <c r="H87" s="103"/>
-      <c r="I87" s="103"/>
-      <c r="J87" s="103"/>
-      <c r="K87" s="104" t="s">
+      <c r="D87" s="80"/>
+      <c r="E87" s="73"/>
+      <c r="F87" s="73"/>
+      <c r="G87" s="74"/>
+      <c r="H87" s="74"/>
+      <c r="I87" s="74"/>
+      <c r="J87" s="74"/>
+      <c r="K87" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="L87" s="104"/>
+      <c r="L87" s="75"/>
       <c r="M87" s="24" t="s">
         <v>37</v>
       </c>
@@ -17803,42 +18794,42 @@
       <c r="AI132" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="AJ132" s="88" t="s">
+      <c r="AJ132" s="100" t="s">
         <v>109</v>
       </c>
-      <c r="AK132" s="89"/>
-      <c r="AL132" s="89"/>
-      <c r="AM132" s="89"/>
-      <c r="AN132" s="89"/>
-      <c r="AO132" s="89"/>
-      <c r="AP132" s="89"/>
-      <c r="AQ132" s="90"/>
+      <c r="AK132" s="101"/>
+      <c r="AL132" s="101"/>
+      <c r="AM132" s="101"/>
+      <c r="AN132" s="101"/>
+      <c r="AO132" s="101"/>
+      <c r="AP132" s="101"/>
+      <c r="AQ132" s="102"/>
     </row>
     <row r="133" spans="23:43" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AG133" s="96"/>
-      <c r="AH133" s="96"/>
-      <c r="AI133" s="98"/>
-      <c r="AJ133" s="85" t="s">
+      <c r="AG133" s="103"/>
+      <c r="AH133" s="103"/>
+      <c r="AI133" s="105"/>
+      <c r="AJ133" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="AK133" s="86"/>
-      <c r="AL133" s="87" t="s">
+      <c r="AK133" s="108"/>
+      <c r="AL133" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="AM133" s="86"/>
-      <c r="AN133" s="87" t="s">
+      <c r="AM133" s="108"/>
+      <c r="AN133" s="109" t="s">
         <v>111</v>
       </c>
-      <c r="AO133" s="86"/>
-      <c r="AP133" s="87" t="s">
+      <c r="AO133" s="108"/>
+      <c r="AP133" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AQ133" s="86"/>
+      <c r="AQ133" s="108"/>
     </row>
     <row r="134" spans="23:43" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AG134" s="97"/>
-      <c r="AH134" s="97"/>
-      <c r="AI134" s="99"/>
+      <c r="AG134" s="104"/>
+      <c r="AH134" s="104"/>
+      <c r="AI134" s="106"/>
       <c r="AJ134" s="37" t="s">
         <v>5</v>
       </c>
@@ -17865,10 +18856,10 @@
       </c>
     </row>
     <row r="135" spans="23:43" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AG135" s="73" t="s">
+      <c r="AG135" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="AH135" s="76" t="s">
+      <c r="AH135" s="113" t="s">
         <v>112</v>
       </c>
       <c r="AI135" s="39" t="s">
@@ -17900,8 +18891,8 @@
       </c>
     </row>
     <row r="136" spans="23:43" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AG136" s="74"/>
-      <c r="AH136" s="77"/>
+      <c r="AG136" s="111"/>
+      <c r="AH136" s="114"/>
       <c r="AI136" s="40" t="s">
         <v>13</v>
       </c>
@@ -17934,8 +18925,8 @@
       <c r="AA137" t="s">
         <v>120</v>
       </c>
-      <c r="AG137" s="74"/>
-      <c r="AH137" s="77"/>
+      <c r="AG137" s="111"/>
+      <c r="AH137" s="114"/>
       <c r="AI137" s="39" t="s">
         <v>12</v>
       </c>
@@ -17965,8 +18956,8 @@
       </c>
     </row>
     <row r="138" spans="23:43" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AG138" s="74"/>
-      <c r="AH138" s="77"/>
+      <c r="AG138" s="111"/>
+      <c r="AH138" s="114"/>
       <c r="AI138" s="41" t="s">
         <v>113</v>
       </c>
@@ -17996,24 +18987,24 @@
       </c>
     </row>
     <row r="139" spans="23:43" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="X139" s="85" t="s">
+      <c r="X139" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="Y139" s="86"/>
-      <c r="Z139" s="87" t="s">
+      <c r="Y139" s="108"/>
+      <c r="Z139" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="AA139" s="86"/>
-      <c r="AB139" s="87" t="s">
+      <c r="AA139" s="108"/>
+      <c r="AB139" s="109" t="s">
         <v>111</v>
       </c>
-      <c r="AC139" s="86"/>
-      <c r="AD139" s="87" t="s">
+      <c r="AC139" s="108"/>
+      <c r="AD139" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AE139" s="86"/>
-      <c r="AG139" s="74"/>
-      <c r="AH139" s="78"/>
+      <c r="AE139" s="108"/>
+      <c r="AG139" s="111"/>
+      <c r="AH139" s="115"/>
       <c r="AI139" s="39" t="s">
         <v>11</v>
       </c>
@@ -18070,8 +19061,8 @@
       <c r="AF140" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="AG140" s="74"/>
-      <c r="AH140" s="76" t="s">
+      <c r="AG140" s="111"/>
+      <c r="AH140" s="113" t="s">
         <v>103</v>
       </c>
       <c r="AI140" s="39" t="s">
@@ -18134,8 +19125,8 @@
         <f>AD141-AE141</f>
         <v>6.9999999999999951E-2</v>
       </c>
-      <c r="AG141" s="74"/>
-      <c r="AH141" s="77"/>
+      <c r="AG141" s="111"/>
+      <c r="AH141" s="114"/>
       <c r="AI141" s="40" t="s">
         <v>13</v>
       </c>
@@ -18196,8 +19187,8 @@
         <f t="shared" ref="AF142:AF145" si="0">AD142-AE142</f>
         <v>5.9999999999999942E-2</v>
       </c>
-      <c r="AG142" s="74"/>
-      <c r="AH142" s="77"/>
+      <c r="AG142" s="111"/>
+      <c r="AH142" s="114"/>
       <c r="AI142" s="39" t="s">
         <v>12</v>
       </c>
@@ -18258,8 +19249,8 @@
         <f t="shared" si="0"/>
         <v>2.9999999999999916E-2</v>
       </c>
-      <c r="AG143" s="74"/>
-      <c r="AH143" s="77"/>
+      <c r="AG143" s="111"/>
+      <c r="AH143" s="114"/>
       <c r="AI143" s="41" t="s">
         <v>113</v>
       </c>
@@ -18320,8 +19311,8 @@
         <f t="shared" si="0"/>
         <v>3.9999999999999925E-2</v>
       </c>
-      <c r="AG144" s="74"/>
-      <c r="AH144" s="78"/>
+      <c r="AG144" s="111"/>
+      <c r="AH144" s="115"/>
       <c r="AI144" s="39" t="s">
         <v>11</v>
       </c>
@@ -18382,8 +19373,8 @@
         <f t="shared" si="0"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="AG145" s="74"/>
-      <c r="AH145" s="76" t="s">
+      <c r="AG145" s="111"/>
+      <c r="AH145" s="113" t="s">
         <v>104</v>
       </c>
       <c r="AI145" s="39" t="s">
@@ -18415,8 +19406,8 @@
       </c>
     </row>
     <row r="146" spans="23:43" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AG146" s="74"/>
-      <c r="AH146" s="77"/>
+      <c r="AG146" s="111"/>
+      <c r="AH146" s="114"/>
       <c r="AI146" s="40" t="s">
         <v>13</v>
       </c>
@@ -18446,8 +19437,8 @@
       </c>
     </row>
     <row r="147" spans="23:43" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AG147" s="74"/>
-      <c r="AH147" s="77"/>
+      <c r="AG147" s="111"/>
+      <c r="AH147" s="114"/>
       <c r="AI147" s="39" t="s">
         <v>12</v>
       </c>
@@ -18477,20 +19468,20 @@
       </c>
     </row>
     <row r="148" spans="23:43" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="X148" s="85" t="s">
+      <c r="X148" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="Y148" s="86"/>
-      <c r="Z148" s="87" t="s">
+      <c r="Y148" s="108"/>
+      <c r="Z148" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AA148" s="86"/>
-      <c r="AB148" s="87"/>
-      <c r="AC148" s="86"/>
-      <c r="AD148" s="87"/>
-      <c r="AE148" s="86"/>
-      <c r="AG148" s="74"/>
-      <c r="AH148" s="77"/>
+      <c r="AA148" s="108"/>
+      <c r="AB148" s="109"/>
+      <c r="AC148" s="108"/>
+      <c r="AD148" s="109"/>
+      <c r="AE148" s="108"/>
+      <c r="AG148" s="111"/>
+      <c r="AH148" s="114"/>
       <c r="AI148" s="41" t="s">
         <v>113</v>
       </c>
@@ -18536,8 +19527,8 @@
       <c r="AC149" s="37"/>
       <c r="AD149" s="37"/>
       <c r="AE149" s="37"/>
-      <c r="AG149" s="74"/>
-      <c r="AH149" s="78"/>
+      <c r="AG149" s="111"/>
+      <c r="AH149" s="115"/>
       <c r="AI149" s="39" t="s">
         <v>11</v>
       </c>
@@ -18586,8 +19577,8 @@
       <c r="AC150" s="39"/>
       <c r="AD150" s="39"/>
       <c r="AE150" s="42"/>
-      <c r="AG150" s="74"/>
-      <c r="AH150" s="76" t="s">
+      <c r="AG150" s="111"/>
+      <c r="AH150" s="113" t="s">
         <v>105</v>
       </c>
       <c r="AI150" s="39" t="s">
@@ -18638,8 +19629,8 @@
       <c r="AC151" s="39"/>
       <c r="AD151" s="39"/>
       <c r="AE151" s="42"/>
-      <c r="AG151" s="74"/>
-      <c r="AH151" s="77"/>
+      <c r="AG151" s="111"/>
+      <c r="AH151" s="114"/>
       <c r="AI151" s="40" t="s">
         <v>13</v>
       </c>
@@ -18688,8 +19679,8 @@
       <c r="AC152" s="41"/>
       <c r="AD152" s="41"/>
       <c r="AE152" s="45"/>
-      <c r="AG152" s="74"/>
-      <c r="AH152" s="77"/>
+      <c r="AG152" s="111"/>
+      <c r="AH152" s="114"/>
       <c r="AI152" s="39" t="s">
         <v>12</v>
       </c>
@@ -18738,8 +19729,8 @@
       <c r="AC153" s="41"/>
       <c r="AD153" s="41"/>
       <c r="AE153" s="46"/>
-      <c r="AG153" s="74"/>
-      <c r="AH153" s="77"/>
+      <c r="AG153" s="111"/>
+      <c r="AH153" s="114"/>
       <c r="AI153" s="41" t="s">
         <v>113</v>
       </c>
@@ -18788,8 +19779,8 @@
       <c r="AC154" s="47"/>
       <c r="AD154" s="47"/>
       <c r="AE154" s="48"/>
-      <c r="AG154" s="74"/>
-      <c r="AH154" s="78"/>
+      <c r="AG154" s="111"/>
+      <c r="AH154" s="115"/>
       <c r="AI154" s="39" t="s">
         <v>11</v>
       </c>
@@ -18819,8 +19810,8 @@
       </c>
     </row>
     <row r="155" spans="23:43" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AG155" s="74"/>
-      <c r="AH155" s="82" t="s">
+      <c r="AG155" s="111"/>
+      <c r="AH155" s="116" t="s">
         <v>114</v>
       </c>
       <c r="AI155" s="47" t="s">
@@ -18852,16 +19843,16 @@
       </c>
     </row>
     <row r="156" spans="23:43" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="X156" s="87" t="s">
+      <c r="X156" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="Y156" s="86"/>
+      <c r="Y156" s="108"/>
       <c r="AB156" s="51" t="s">
         <v>8</v>
       </c>
       <c r="AC156" s="52"/>
-      <c r="AG156" s="74"/>
-      <c r="AH156" s="83"/>
+      <c r="AG156" s="111"/>
+      <c r="AH156" s="117"/>
       <c r="AI156" s="39" t="s">
         <v>13</v>
       </c>
@@ -18898,13 +19889,13 @@
         <v>6</v>
       </c>
       <c r="AB157" s="37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC157" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="AG157" s="74"/>
-      <c r="AH157" s="83"/>
+      <c r="AG157" s="111"/>
+      <c r="AH157" s="117"/>
       <c r="AI157" s="47" t="s">
         <v>12</v>
       </c>
@@ -18946,17 +19937,17 @@
       <c r="AA158" t="s">
         <v>117</v>
       </c>
-      <c r="AB158" s="45">
+      <c r="AB158" s="41">
+        <v>0.83</v>
+      </c>
+      <c r="AC158" s="45">
         <v>0.8</v>
-      </c>
-      <c r="AC158" t="s">
-        <v>117</v>
       </c>
       <c r="AD158" s="45">
         <v>0.8</v>
       </c>
-      <c r="AG158" s="74"/>
-      <c r="AH158" s="83"/>
+      <c r="AG158" s="111"/>
+      <c r="AH158" s="117"/>
       <c r="AI158" s="39" t="s">
         <v>113</v>
       </c>
@@ -18998,14 +19989,14 @@
       <c r="AA159" t="s">
         <v>115</v>
       </c>
-      <c r="AB159" s="42">
-        <v>0.79</v>
+      <c r="AB159" s="39">
+        <v>0.86</v>
       </c>
       <c r="AC159" s="45">
         <v>0.8</v>
       </c>
-      <c r="AG159" s="75"/>
-      <c r="AH159" s="84"/>
+      <c r="AG159" s="112"/>
+      <c r="AH159" s="118"/>
       <c r="AI159" s="47" t="s">
         <v>11</v>
       </c>
@@ -19047,8 +20038,8 @@
       <c r="AA160" t="s">
         <v>116</v>
       </c>
-      <c r="AB160" s="42">
-        <v>0.79</v>
+      <c r="AB160" s="39">
+        <v>0.85</v>
       </c>
       <c r="AC160" s="42">
         <v>0.79</v>
@@ -19067,8 +20058,8 @@
       <c r="AA161" t="s">
         <v>118</v>
       </c>
-      <c r="AB161" s="46">
-        <v>0.78</v>
+      <c r="AB161" s="41">
+        <v>0.82</v>
       </c>
       <c r="AC161" s="46">
         <v>0.78</v>
@@ -19087,8 +20078,8 @@
       <c r="AA162" t="s">
         <v>121</v>
       </c>
-      <c r="AB162" s="48">
-        <v>0.74</v>
+      <c r="AB162" s="47">
+        <v>0.8</v>
       </c>
       <c r="AC162" s="48">
         <v>0.74</v>
@@ -19107,20 +20098,20 @@
       <c r="J173" t="s">
         <v>105</v>
       </c>
-      <c r="K173" s="102" t="s">
+      <c r="K173" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="L173" s="102"/>
-      <c r="M173" s="103" t="s">
+      <c r="L173" s="73"/>
+      <c r="M173" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="N173" s="103"/>
-      <c r="O173" s="103"/>
-      <c r="P173" s="103"/>
-      <c r="Q173" s="104" t="s">
+      <c r="N173" s="74"/>
+      <c r="O173" s="74"/>
+      <c r="P173" s="74"/>
+      <c r="Q173" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R173" s="104"/>
+      <c r="R173" s="75"/>
       <c r="S173" s="15" t="s">
         <v>27</v>
       </c>
@@ -19144,16 +20135,16 @@
       <c r="J174" s="17">
         <v>0.8</v>
       </c>
-      <c r="K174" s="102"/>
-      <c r="L174" s="102"/>
-      <c r="M174" s="103"/>
-      <c r="N174" s="103"/>
-      <c r="O174" s="103"/>
-      <c r="P174" s="103"/>
-      <c r="Q174" s="105" t="s">
+      <c r="K174" s="73"/>
+      <c r="L174" s="73"/>
+      <c r="M174" s="74"/>
+      <c r="N174" s="74"/>
+      <c r="O174" s="74"/>
+      <c r="P174" s="74"/>
+      <c r="Q174" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R174" s="106"/>
+      <c r="R174" s="77"/>
       <c r="S174" s="16" t="s">
         <v>32</v>
       </c>
@@ -19168,16 +20159,16 @@
       <c r="G175" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="K175" s="102"/>
-      <c r="L175" s="102"/>
-      <c r="M175" s="103"/>
-      <c r="N175" s="103"/>
-      <c r="O175" s="103"/>
-      <c r="P175" s="103"/>
-      <c r="Q175" s="104" t="s">
+      <c r="K175" s="73"/>
+      <c r="L175" s="73"/>
+      <c r="M175" s="74"/>
+      <c r="N175" s="74"/>
+      <c r="O175" s="74"/>
+      <c r="P175" s="74"/>
+      <c r="Q175" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R175" s="104"/>
+      <c r="R175" s="75"/>
       <c r="S175" s="15" t="s">
         <v>34</v>
       </c>
@@ -19192,16 +20183,16 @@
       <c r="G176" t="s">
         <v>37</v>
       </c>
-      <c r="K176" s="102"/>
-      <c r="L176" s="102"/>
-      <c r="M176" s="103"/>
-      <c r="N176" s="103"/>
-      <c r="O176" s="103"/>
-      <c r="P176" s="103"/>
-      <c r="Q176" s="107" t="s">
+      <c r="K176" s="73"/>
+      <c r="L176" s="73"/>
+      <c r="M176" s="74"/>
+      <c r="N176" s="74"/>
+      <c r="O176" s="74"/>
+      <c r="P176" s="74"/>
+      <c r="Q176" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R176" s="107"/>
+      <c r="R176" s="78"/>
       <c r="S176" s="16">
         <v>0.73</v>
       </c>
@@ -19216,16 +20207,16 @@
       <c r="G177" s="17">
         <v>0.8</v>
       </c>
-      <c r="K177" s="102"/>
-      <c r="L177" s="102"/>
-      <c r="M177" s="103"/>
-      <c r="N177" s="103"/>
-      <c r="O177" s="103"/>
-      <c r="P177" s="103"/>
-      <c r="Q177" s="104" t="s">
+      <c r="K177" s="73"/>
+      <c r="L177" s="73"/>
+      <c r="M177" s="74"/>
+      <c r="N177" s="74"/>
+      <c r="O177" s="74"/>
+      <c r="P177" s="74"/>
+      <c r="Q177" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R177" s="104"/>
+      <c r="R177" s="75"/>
       <c r="S177" s="15">
         <v>0.84</v>
       </c>
@@ -19234,20 +20225,20 @@
       </c>
     </row>
     <row r="178" spans="6:20" x14ac:dyDescent="0.35">
-      <c r="K178" s="102" t="s">
+      <c r="K178" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="L178" s="102"/>
-      <c r="M178" s="103" t="s">
+      <c r="L178" s="73"/>
+      <c r="M178" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="N178" s="103"/>
-      <c r="O178" s="103"/>
-      <c r="P178" s="103"/>
-      <c r="Q178" s="104" t="s">
+      <c r="N178" s="74"/>
+      <c r="O178" s="74"/>
+      <c r="P178" s="74"/>
+      <c r="Q178" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R178" s="104"/>
+      <c r="R178" s="75"/>
       <c r="S178" s="15" t="s">
         <v>46</v>
       </c>
@@ -19262,16 +20253,16 @@
       <c r="G179" s="17">
         <v>0.81</v>
       </c>
-      <c r="K179" s="102"/>
-      <c r="L179" s="102"/>
-      <c r="M179" s="103"/>
-      <c r="N179" s="103"/>
-      <c r="O179" s="103"/>
-      <c r="P179" s="103"/>
-      <c r="Q179" s="105" t="s">
+      <c r="K179" s="73"/>
+      <c r="L179" s="73"/>
+      <c r="M179" s="74"/>
+      <c r="N179" s="74"/>
+      <c r="O179" s="74"/>
+      <c r="P179" s="74"/>
+      <c r="Q179" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R179" s="106"/>
+      <c r="R179" s="77"/>
       <c r="S179" s="16" t="s">
         <v>50</v>
       </c>
@@ -19286,16 +20277,16 @@
       <c r="G180" s="15">
         <v>0.8</v>
       </c>
-      <c r="K180" s="102"/>
-      <c r="L180" s="102"/>
-      <c r="M180" s="103"/>
-      <c r="N180" s="103"/>
-      <c r="O180" s="103"/>
-      <c r="P180" s="103"/>
-      <c r="Q180" s="104" t="s">
+      <c r="K180" s="73"/>
+      <c r="L180" s="73"/>
+      <c r="M180" s="74"/>
+      <c r="N180" s="74"/>
+      <c r="O180" s="74"/>
+      <c r="P180" s="74"/>
+      <c r="Q180" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R180" s="104"/>
+      <c r="R180" s="75"/>
       <c r="S180" s="18" t="s">
         <v>55</v>
       </c>
@@ -19304,16 +20295,16 @@
       </c>
     </row>
     <row r="181" spans="6:20" x14ac:dyDescent="0.35">
-      <c r="K181" s="102"/>
-      <c r="L181" s="102"/>
-      <c r="M181" s="103"/>
-      <c r="N181" s="103"/>
-      <c r="O181" s="103"/>
-      <c r="P181" s="103"/>
-      <c r="Q181" s="107" t="s">
+      <c r="K181" s="73"/>
+      <c r="L181" s="73"/>
+      <c r="M181" s="74"/>
+      <c r="N181" s="74"/>
+      <c r="O181" s="74"/>
+      <c r="P181" s="74"/>
+      <c r="Q181" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R181" s="107"/>
+      <c r="R181" s="78"/>
       <c r="S181" s="16" t="s">
         <v>59</v>
       </c>
@@ -19322,16 +20313,16 @@
       </c>
     </row>
     <row r="182" spans="6:20" x14ac:dyDescent="0.35">
-      <c r="K182" s="102"/>
-      <c r="L182" s="102"/>
-      <c r="M182" s="103"/>
-      <c r="N182" s="103"/>
-      <c r="O182" s="103"/>
-      <c r="P182" s="103"/>
-      <c r="Q182" s="104" t="s">
+      <c r="K182" s="73"/>
+      <c r="L182" s="73"/>
+      <c r="M182" s="74"/>
+      <c r="N182" s="74"/>
+      <c r="O182" s="74"/>
+      <c r="P182" s="74"/>
+      <c r="Q182" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R182" s="104"/>
+      <c r="R182" s="75"/>
       <c r="S182" s="15" t="s">
         <v>58</v>
       </c>
@@ -19340,20 +20331,20 @@
       </c>
     </row>
     <row r="183" spans="6:20" x14ac:dyDescent="0.35">
-      <c r="K183" s="102" t="s">
+      <c r="K183" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="L183" s="102"/>
-      <c r="M183" s="103" t="s">
+      <c r="L183" s="73"/>
+      <c r="M183" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="N183" s="103"/>
-      <c r="O183" s="103"/>
-      <c r="P183" s="103"/>
-      <c r="Q183" s="104" t="s">
+      <c r="N183" s="74"/>
+      <c r="O183" s="74"/>
+      <c r="P183" s="74"/>
+      <c r="Q183" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R183" s="104"/>
+      <c r="R183" s="75"/>
       <c r="S183" s="18" t="s">
         <v>69</v>
       </c>
@@ -19362,16 +20353,16 @@
       </c>
     </row>
     <row r="184" spans="6:20" x14ac:dyDescent="0.35">
-      <c r="K184" s="102"/>
-      <c r="L184" s="102"/>
-      <c r="M184" s="103"/>
-      <c r="N184" s="103"/>
-      <c r="O184" s="103"/>
-      <c r="P184" s="103"/>
-      <c r="Q184" s="105" t="s">
+      <c r="K184" s="73"/>
+      <c r="L184" s="73"/>
+      <c r="M184" s="74"/>
+      <c r="N184" s="74"/>
+      <c r="O184" s="74"/>
+      <c r="P184" s="74"/>
+      <c r="Q184" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R184" s="106"/>
+      <c r="R184" s="77"/>
       <c r="S184" s="16" t="s">
         <v>46</v>
       </c>
@@ -19380,16 +20371,16 @@
       </c>
     </row>
     <row r="185" spans="6:20" x14ac:dyDescent="0.35">
-      <c r="K185" s="102"/>
-      <c r="L185" s="102"/>
-      <c r="M185" s="103"/>
-      <c r="N185" s="103"/>
-      <c r="O185" s="103"/>
-      <c r="P185" s="103"/>
-      <c r="Q185" s="104" t="s">
+      <c r="K185" s="73"/>
+      <c r="L185" s="73"/>
+      <c r="M185" s="74"/>
+      <c r="N185" s="74"/>
+      <c r="O185" s="74"/>
+      <c r="P185" s="74"/>
+      <c r="Q185" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R185" s="104"/>
+      <c r="R185" s="75"/>
       <c r="S185" s="15" t="s">
         <v>50</v>
       </c>
@@ -19398,16 +20389,16 @@
       </c>
     </row>
     <row r="186" spans="6:20" x14ac:dyDescent="0.35">
-      <c r="K186" s="102"/>
-      <c r="L186" s="102"/>
-      <c r="M186" s="103"/>
-      <c r="N186" s="103"/>
-      <c r="O186" s="103"/>
-      <c r="P186" s="103"/>
-      <c r="Q186" s="107" t="s">
+      <c r="K186" s="73"/>
+      <c r="L186" s="73"/>
+      <c r="M186" s="74"/>
+      <c r="N186" s="74"/>
+      <c r="O186" s="74"/>
+      <c r="P186" s="74"/>
+      <c r="Q186" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R186" s="107"/>
+      <c r="R186" s="78"/>
       <c r="S186" s="16" t="s">
         <v>73</v>
       </c>
@@ -19416,16 +20407,16 @@
       </c>
     </row>
     <row r="187" spans="6:20" x14ac:dyDescent="0.35">
-      <c r="K187" s="102"/>
-      <c r="L187" s="102"/>
-      <c r="M187" s="103"/>
-      <c r="N187" s="103"/>
-      <c r="O187" s="103"/>
-      <c r="P187" s="103"/>
-      <c r="Q187" s="104" t="s">
+      <c r="K187" s="73"/>
+      <c r="L187" s="73"/>
+      <c r="M187" s="74"/>
+      <c r="N187" s="74"/>
+      <c r="O187" s="74"/>
+      <c r="P187" s="74"/>
+      <c r="Q187" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R187" s="104"/>
+      <c r="R187" s="75"/>
       <c r="S187" s="15" t="s">
         <v>27</v>
       </c>
@@ -19434,20 +20425,20 @@
       </c>
     </row>
     <row r="188" spans="6:20" x14ac:dyDescent="0.35">
-      <c r="K188" s="102" t="s">
+      <c r="K188" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="L188" s="102"/>
-      <c r="M188" s="103" t="s">
+      <c r="L188" s="73"/>
+      <c r="M188" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="N188" s="103"/>
-      <c r="O188" s="103"/>
-      <c r="P188" s="103"/>
-      <c r="Q188" s="104" t="s">
+      <c r="N188" s="74"/>
+      <c r="O188" s="74"/>
+      <c r="P188" s="74"/>
+      <c r="Q188" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R188" s="104"/>
+      <c r="R188" s="75"/>
       <c r="S188" s="18">
         <v>0.99</v>
       </c>
@@ -19456,16 +20447,16 @@
       </c>
     </row>
     <row r="189" spans="6:20" x14ac:dyDescent="0.35">
-      <c r="K189" s="102"/>
-      <c r="L189" s="102"/>
-      <c r="M189" s="103"/>
-      <c r="N189" s="103"/>
-      <c r="O189" s="103"/>
-      <c r="P189" s="103"/>
-      <c r="Q189" s="105" t="s">
+      <c r="K189" s="73"/>
+      <c r="L189" s="73"/>
+      <c r="M189" s="74"/>
+      <c r="N189" s="74"/>
+      <c r="O189" s="74"/>
+      <c r="P189" s="74"/>
+      <c r="Q189" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R189" s="106"/>
+      <c r="R189" s="77"/>
       <c r="S189" s="16">
         <v>0.84</v>
       </c>
@@ -19474,16 +20465,16 @@
       </c>
     </row>
     <row r="190" spans="6:20" x14ac:dyDescent="0.35">
-      <c r="K190" s="102"/>
-      <c r="L190" s="102"/>
-      <c r="M190" s="103"/>
-      <c r="N190" s="103"/>
-      <c r="O190" s="103"/>
-      <c r="P190" s="103"/>
-      <c r="Q190" s="104" t="s">
+      <c r="K190" s="73"/>
+      <c r="L190" s="73"/>
+      <c r="M190" s="74"/>
+      <c r="N190" s="74"/>
+      <c r="O190" s="74"/>
+      <c r="P190" s="74"/>
+      <c r="Q190" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R190" s="104"/>
+      <c r="R190" s="75"/>
       <c r="S190" s="15">
         <v>0.87</v>
       </c>
@@ -19492,16 +20483,16 @@
       </c>
     </row>
     <row r="191" spans="6:20" x14ac:dyDescent="0.35">
-      <c r="K191" s="102"/>
-      <c r="L191" s="102"/>
-      <c r="M191" s="103"/>
-      <c r="N191" s="103"/>
-      <c r="O191" s="103"/>
-      <c r="P191" s="103"/>
-      <c r="Q191" s="107" t="s">
+      <c r="K191" s="73"/>
+      <c r="L191" s="73"/>
+      <c r="M191" s="74"/>
+      <c r="N191" s="74"/>
+      <c r="O191" s="74"/>
+      <c r="P191" s="74"/>
+      <c r="Q191" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R191" s="107"/>
+      <c r="R191" s="78"/>
       <c r="S191" s="16">
         <v>0.69</v>
       </c>
@@ -19510,16 +20501,16 @@
       </c>
     </row>
     <row r="192" spans="6:20" x14ac:dyDescent="0.35">
-      <c r="K192" s="102"/>
-      <c r="L192" s="102"/>
-      <c r="M192" s="103"/>
-      <c r="N192" s="103"/>
-      <c r="O192" s="103"/>
-      <c r="P192" s="103"/>
-      <c r="Q192" s="104" t="s">
+      <c r="K192" s="73"/>
+      <c r="L192" s="73"/>
+      <c r="M192" s="74"/>
+      <c r="N192" s="74"/>
+      <c r="O192" s="74"/>
+      <c r="P192" s="74"/>
+      <c r="Q192" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R192" s="104"/>
+      <c r="R192" s="75"/>
       <c r="S192" s="15">
         <v>0.89</v>
       </c>
@@ -19528,20 +20519,20 @@
       </c>
     </row>
     <row r="193" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K193" s="102" t="s">
+      <c r="K193" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="L193" s="102"/>
-      <c r="M193" s="103" t="s">
+      <c r="L193" s="73"/>
+      <c r="M193" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="N193" s="103"/>
-      <c r="O193" s="103"/>
-      <c r="P193" s="103"/>
-      <c r="Q193" s="104" t="s">
+      <c r="N193" s="74"/>
+      <c r="O193" s="74"/>
+      <c r="P193" s="74"/>
+      <c r="Q193" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R193" s="104"/>
+      <c r="R193" s="75"/>
       <c r="S193" s="23">
         <v>0.83</v>
       </c>
@@ -19550,16 +20541,16 @@
       </c>
     </row>
     <row r="194" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K194" s="102"/>
-      <c r="L194" s="102"/>
-      <c r="M194" s="103"/>
-      <c r="N194" s="103"/>
-      <c r="O194" s="103"/>
-      <c r="P194" s="103"/>
-      <c r="Q194" s="105" t="s">
+      <c r="K194" s="73"/>
+      <c r="L194" s="73"/>
+      <c r="M194" s="74"/>
+      <c r="N194" s="74"/>
+      <c r="O194" s="74"/>
+      <c r="P194" s="74"/>
+      <c r="Q194" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R194" s="106"/>
+      <c r="R194" s="77"/>
       <c r="S194" s="16">
         <v>0.85</v>
       </c>
@@ -19568,16 +20559,16 @@
       </c>
     </row>
     <row r="195" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K195" s="102"/>
-      <c r="L195" s="102"/>
-      <c r="M195" s="103"/>
-      <c r="N195" s="103"/>
-      <c r="O195" s="103"/>
-      <c r="P195" s="103"/>
-      <c r="Q195" s="104" t="s">
+      <c r="K195" s="73"/>
+      <c r="L195" s="73"/>
+      <c r="M195" s="74"/>
+      <c r="N195" s="74"/>
+      <c r="O195" s="74"/>
+      <c r="P195" s="74"/>
+      <c r="Q195" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R195" s="104"/>
+      <c r="R195" s="75"/>
       <c r="S195" s="15">
         <v>0.85</v>
       </c>
@@ -19586,16 +20577,16 @@
       </c>
     </row>
     <row r="196" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K196" s="102"/>
-      <c r="L196" s="102"/>
-      <c r="M196" s="103"/>
-      <c r="N196" s="103"/>
-      <c r="O196" s="103"/>
-      <c r="P196" s="103"/>
-      <c r="Q196" s="107" t="s">
+      <c r="K196" s="73"/>
+      <c r="L196" s="73"/>
+      <c r="M196" s="74"/>
+      <c r="N196" s="74"/>
+      <c r="O196" s="74"/>
+      <c r="P196" s="74"/>
+      <c r="Q196" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R196" s="107"/>
+      <c r="R196" s="78"/>
       <c r="S196" s="16">
         <v>0.73</v>
       </c>
@@ -19604,16 +20595,16 @@
       </c>
     </row>
     <row r="197" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K197" s="102"/>
-      <c r="L197" s="102"/>
-      <c r="M197" s="103"/>
-      <c r="N197" s="103"/>
-      <c r="O197" s="103"/>
-      <c r="P197" s="103"/>
-      <c r="Q197" s="104" t="s">
+      <c r="K197" s="73"/>
+      <c r="L197" s="73"/>
+      <c r="M197" s="74"/>
+      <c r="N197" s="74"/>
+      <c r="O197" s="74"/>
+      <c r="P197" s="74"/>
+      <c r="Q197" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R197" s="104"/>
+      <c r="R197" s="75"/>
       <c r="S197" s="15">
         <v>0.84</v>
       </c>
@@ -19622,20 +20613,20 @@
       </c>
     </row>
     <row r="198" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K198" s="102" t="s">
+      <c r="K198" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="L198" s="102"/>
-      <c r="M198" s="103" t="s">
+      <c r="L198" s="73"/>
+      <c r="M198" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="N198" s="103"/>
-      <c r="O198" s="103"/>
-      <c r="P198" s="103"/>
-      <c r="Q198" s="104" t="s">
+      <c r="N198" s="74"/>
+      <c r="O198" s="74"/>
+      <c r="P198" s="74"/>
+      <c r="Q198" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R198" s="104"/>
+      <c r="R198" s="75"/>
       <c r="S198" s="15">
         <v>0.84</v>
       </c>
@@ -19644,16 +20635,16 @@
       </c>
     </row>
     <row r="199" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K199" s="102"/>
-      <c r="L199" s="102"/>
-      <c r="M199" s="103"/>
-      <c r="N199" s="103"/>
-      <c r="O199" s="103"/>
-      <c r="P199" s="103"/>
-      <c r="Q199" s="105" t="s">
+      <c r="K199" s="73"/>
+      <c r="L199" s="73"/>
+      <c r="M199" s="74"/>
+      <c r="N199" s="74"/>
+      <c r="O199" s="74"/>
+      <c r="P199" s="74"/>
+      <c r="Q199" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R199" s="106"/>
+      <c r="R199" s="77"/>
       <c r="S199" s="16">
         <v>0.85</v>
       </c>
@@ -19662,16 +20653,16 @@
       </c>
     </row>
     <row r="200" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K200" s="102"/>
-      <c r="L200" s="102"/>
-      <c r="M200" s="103"/>
-      <c r="N200" s="103"/>
-      <c r="O200" s="103"/>
-      <c r="P200" s="103"/>
-      <c r="Q200" s="104" t="s">
+      <c r="K200" s="73"/>
+      <c r="L200" s="73"/>
+      <c r="M200" s="74"/>
+      <c r="N200" s="74"/>
+      <c r="O200" s="74"/>
+      <c r="P200" s="74"/>
+      <c r="Q200" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R200" s="104"/>
+      <c r="R200" s="75"/>
       <c r="S200" s="15">
         <v>0.88</v>
       </c>
@@ -19680,16 +20671,16 @@
       </c>
     </row>
     <row r="201" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K201" s="102"/>
-      <c r="L201" s="102"/>
-      <c r="M201" s="103"/>
-      <c r="N201" s="103"/>
-      <c r="O201" s="103"/>
-      <c r="P201" s="103"/>
-      <c r="Q201" s="107" t="s">
+      <c r="K201" s="73"/>
+      <c r="L201" s="73"/>
+      <c r="M201" s="74"/>
+      <c r="N201" s="74"/>
+      <c r="O201" s="74"/>
+      <c r="P201" s="74"/>
+      <c r="Q201" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R201" s="107"/>
+      <c r="R201" s="78"/>
       <c r="S201" s="16">
         <v>0.78</v>
       </c>
@@ -19698,16 +20689,16 @@
       </c>
     </row>
     <row r="202" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K202" s="102"/>
-      <c r="L202" s="102"/>
-      <c r="M202" s="103"/>
-      <c r="N202" s="103"/>
-      <c r="O202" s="103"/>
-      <c r="P202" s="103"/>
-      <c r="Q202" s="104" t="s">
+      <c r="K202" s="73"/>
+      <c r="L202" s="73"/>
+      <c r="M202" s="74"/>
+      <c r="N202" s="74"/>
+      <c r="O202" s="74"/>
+      <c r="P202" s="74"/>
+      <c r="Q202" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R202" s="104"/>
+      <c r="R202" s="75"/>
       <c r="S202" s="15">
         <v>0.86</v>
       </c>
@@ -19716,34 +20707,34 @@
       </c>
     </row>
     <row r="203" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K203" s="102" t="s">
+      <c r="K203" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="L203" s="102"/>
-      <c r="M203" s="103" t="s">
+      <c r="L203" s="73"/>
+      <c r="M203" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="N203" s="103"/>
-      <c r="O203" s="103"/>
-      <c r="P203" s="103"/>
-      <c r="Q203" s="104" t="s">
+      <c r="N203" s="74"/>
+      <c r="O203" s="74"/>
+      <c r="P203" s="74"/>
+      <c r="Q203" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R203" s="104"/>
+      <c r="R203" s="75"/>
       <c r="S203" s="15"/>
       <c r="T203" s="15"/>
     </row>
     <row r="204" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K204" s="102"/>
-      <c r="L204" s="102"/>
-      <c r="M204" s="103"/>
-      <c r="N204" s="103"/>
-      <c r="O204" s="103"/>
-      <c r="P204" s="103"/>
-      <c r="Q204" s="105" t="s">
+      <c r="K204" s="73"/>
+      <c r="L204" s="73"/>
+      <c r="M204" s="74"/>
+      <c r="N204" s="74"/>
+      <c r="O204" s="74"/>
+      <c r="P204" s="74"/>
+      <c r="Q204" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R204" s="106"/>
+      <c r="R204" s="77"/>
       <c r="S204" s="16">
         <v>0.83</v>
       </c>
@@ -19752,16 +20743,16 @@
       </c>
     </row>
     <row r="205" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K205" s="102"/>
-      <c r="L205" s="102"/>
-      <c r="M205" s="103"/>
-      <c r="N205" s="103"/>
-      <c r="O205" s="103"/>
-      <c r="P205" s="103"/>
-      <c r="Q205" s="104" t="s">
+      <c r="K205" s="73"/>
+      <c r="L205" s="73"/>
+      <c r="M205" s="74"/>
+      <c r="N205" s="74"/>
+      <c r="O205" s="74"/>
+      <c r="P205" s="74"/>
+      <c r="Q205" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R205" s="104"/>
+      <c r="R205" s="75"/>
       <c r="S205" s="15">
         <v>0.84</v>
       </c>
@@ -19770,16 +20761,16 @@
       </c>
     </row>
     <row r="206" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K206" s="102"/>
-      <c r="L206" s="102"/>
-      <c r="M206" s="103"/>
-      <c r="N206" s="103"/>
-      <c r="O206" s="103"/>
-      <c r="P206" s="103"/>
-      <c r="Q206" s="107" t="s">
+      <c r="K206" s="73"/>
+      <c r="L206" s="73"/>
+      <c r="M206" s="74"/>
+      <c r="N206" s="74"/>
+      <c r="O206" s="74"/>
+      <c r="P206" s="74"/>
+      <c r="Q206" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R206" s="107"/>
+      <c r="R206" s="78"/>
       <c r="S206" s="16">
         <v>0.67</v>
       </c>
@@ -19788,16 +20779,16 @@
       </c>
     </row>
     <row r="207" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K207" s="102"/>
-      <c r="L207" s="102"/>
-      <c r="M207" s="103"/>
-      <c r="N207" s="103"/>
-      <c r="O207" s="103"/>
-      <c r="P207" s="103"/>
-      <c r="Q207" s="104" t="s">
+      <c r="K207" s="73"/>
+      <c r="L207" s="73"/>
+      <c r="M207" s="74"/>
+      <c r="N207" s="74"/>
+      <c r="O207" s="74"/>
+      <c r="P207" s="74"/>
+      <c r="Q207" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R207" s="104"/>
+      <c r="R207" s="75"/>
       <c r="S207" s="15">
         <v>0.85</v>
       </c>
@@ -19806,20 +20797,20 @@
       </c>
     </row>
     <row r="208" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K208" s="102" t="s">
+      <c r="K208" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="L208" s="102"/>
-      <c r="M208" s="103" t="s">
+      <c r="L208" s="73"/>
+      <c r="M208" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="N208" s="103"/>
-      <c r="O208" s="103"/>
-      <c r="P208" s="103"/>
-      <c r="Q208" s="104" t="s">
+      <c r="N208" s="74"/>
+      <c r="O208" s="74"/>
+      <c r="P208" s="74"/>
+      <c r="Q208" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R208" s="104"/>
+      <c r="R208" s="75"/>
       <c r="S208" s="16">
         <v>0.83</v>
       </c>
@@ -19828,16 +20819,16 @@
       </c>
     </row>
     <row r="209" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K209" s="102"/>
-      <c r="L209" s="102"/>
-      <c r="M209" s="103"/>
-      <c r="N209" s="103"/>
-      <c r="O209" s="103"/>
-      <c r="P209" s="103"/>
-      <c r="Q209" s="105" t="s">
+      <c r="K209" s="73"/>
+      <c r="L209" s="73"/>
+      <c r="M209" s="74"/>
+      <c r="N209" s="74"/>
+      <c r="O209" s="74"/>
+      <c r="P209" s="74"/>
+      <c r="Q209" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R209" s="106"/>
+      <c r="R209" s="77"/>
       <c r="S209" s="18">
         <v>0.75</v>
       </c>
@@ -19846,16 +20837,16 @@
       </c>
     </row>
     <row r="210" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K210" s="102"/>
-      <c r="L210" s="102"/>
-      <c r="M210" s="103"/>
-      <c r="N210" s="103"/>
-      <c r="O210" s="103"/>
-      <c r="P210" s="103"/>
-      <c r="Q210" s="104" t="s">
+      <c r="K210" s="73"/>
+      <c r="L210" s="73"/>
+      <c r="M210" s="74"/>
+      <c r="N210" s="74"/>
+      <c r="O210" s="74"/>
+      <c r="P210" s="74"/>
+      <c r="Q210" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R210" s="104"/>
+      <c r="R210" s="75"/>
       <c r="S210" s="31" t="s">
         <v>88</v>
       </c>
@@ -19864,16 +20855,16 @@
       </c>
     </row>
     <row r="211" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K211" s="102"/>
-      <c r="L211" s="102"/>
-      <c r="M211" s="103"/>
-      <c r="N211" s="103"/>
-      <c r="O211" s="103"/>
-      <c r="P211" s="103"/>
-      <c r="Q211" s="107" t="s">
+      <c r="K211" s="73"/>
+      <c r="L211" s="73"/>
+      <c r="M211" s="74"/>
+      <c r="N211" s="74"/>
+      <c r="O211" s="74"/>
+      <c r="P211" s="74"/>
+      <c r="Q211" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R211" s="107"/>
+      <c r="R211" s="78"/>
       <c r="S211" s="32">
         <v>0.85</v>
       </c>
@@ -19882,16 +20873,16 @@
       </c>
     </row>
     <row r="212" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K212" s="102"/>
-      <c r="L212" s="102"/>
-      <c r="M212" s="103"/>
-      <c r="N212" s="103"/>
-      <c r="O212" s="103"/>
-      <c r="P212" s="103"/>
-      <c r="Q212" s="104" t="s">
+      <c r="K212" s="73"/>
+      <c r="L212" s="73"/>
+      <c r="M212" s="74"/>
+      <c r="N212" s="74"/>
+      <c r="O212" s="74"/>
+      <c r="P212" s="74"/>
+      <c r="Q212" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R212" s="104"/>
+      <c r="R212" s="75"/>
       <c r="S212" s="15">
         <v>0.86</v>
       </c>
@@ -19900,94 +20891,94 @@
       </c>
     </row>
     <row r="213" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K213" s="102" t="s">
+      <c r="K213" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="L213" s="102"/>
-      <c r="M213" s="103" t="s">
+      <c r="L213" s="73"/>
+      <c r="M213" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="N213" s="103"/>
-      <c r="O213" s="103"/>
-      <c r="P213" s="103"/>
-      <c r="Q213" s="104" t="s">
+      <c r="N213" s="74"/>
+      <c r="O213" s="74"/>
+      <c r="P213" s="74"/>
+      <c r="Q213" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R213" s="104"/>
+      <c r="R213" s="75"/>
       <c r="S213" s="33"/>
       <c r="T213" s="33"/>
     </row>
     <row r="214" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K214" s="102"/>
-      <c r="L214" s="102"/>
-      <c r="M214" s="103"/>
-      <c r="N214" s="103"/>
-      <c r="O214" s="103"/>
-      <c r="P214" s="103"/>
-      <c r="Q214" s="105" t="s">
+      <c r="K214" s="73"/>
+      <c r="L214" s="73"/>
+      <c r="M214" s="74"/>
+      <c r="N214" s="74"/>
+      <c r="O214" s="74"/>
+      <c r="P214" s="74"/>
+      <c r="Q214" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R214" s="106"/>
+      <c r="R214" s="77"/>
       <c r="S214" s="21"/>
       <c r="T214" s="21"/>
     </row>
     <row r="215" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K215" s="102"/>
-      <c r="L215" s="102"/>
-      <c r="M215" s="103"/>
-      <c r="N215" s="103"/>
-      <c r="O215" s="103"/>
-      <c r="P215" s="103"/>
-      <c r="Q215" s="104" t="s">
+      <c r="K215" s="73"/>
+      <c r="L215" s="73"/>
+      <c r="M215" s="74"/>
+      <c r="N215" s="74"/>
+      <c r="O215" s="74"/>
+      <c r="P215" s="74"/>
+      <c r="Q215" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R215" s="104"/>
+      <c r="R215" s="75"/>
       <c r="S215" s="20"/>
       <c r="T215" s="22"/>
     </row>
     <row r="216" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K216" s="102"/>
-      <c r="L216" s="102"/>
-      <c r="M216" s="103"/>
-      <c r="N216" s="103"/>
-      <c r="O216" s="103"/>
-      <c r="P216" s="103"/>
-      <c r="Q216" s="107" t="s">
+      <c r="K216" s="73"/>
+      <c r="L216" s="73"/>
+      <c r="M216" s="74"/>
+      <c r="N216" s="74"/>
+      <c r="O216" s="74"/>
+      <c r="P216" s="74"/>
+      <c r="Q216" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R216" s="107"/>
+      <c r="R216" s="78"/>
       <c r="S216" s="21"/>
       <c r="T216" s="21"/>
     </row>
     <row r="217" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K217" s="102"/>
-      <c r="L217" s="102"/>
-      <c r="M217" s="103"/>
-      <c r="N217" s="103"/>
-      <c r="O217" s="103"/>
-      <c r="P217" s="103"/>
-      <c r="Q217" s="104" t="s">
+      <c r="K217" s="73"/>
+      <c r="L217" s="73"/>
+      <c r="M217" s="74"/>
+      <c r="N217" s="74"/>
+      <c r="O217" s="74"/>
+      <c r="P217" s="74"/>
+      <c r="Q217" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R217" s="104"/>
+      <c r="R217" s="75"/>
       <c r="S217" s="20"/>
       <c r="T217" s="20"/>
     </row>
     <row r="218" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K218" s="102" t="s">
+      <c r="K218" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="L218" s="102"/>
-      <c r="M218" s="103" t="s">
+      <c r="L218" s="73"/>
+      <c r="M218" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="N218" s="103"/>
-      <c r="O218" s="103"/>
-      <c r="P218" s="103"/>
-      <c r="Q218" s="104" t="s">
+      <c r="N218" s="74"/>
+      <c r="O218" s="74"/>
+      <c r="P218" s="74"/>
+      <c r="Q218" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R218" s="104"/>
+      <c r="R218" s="75"/>
       <c r="S218" s="24">
         <v>0.73</v>
       </c>
@@ -19996,16 +20987,16 @@
       </c>
     </row>
     <row r="219" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K219" s="102"/>
-      <c r="L219" s="102"/>
-      <c r="M219" s="103"/>
-      <c r="N219" s="103"/>
-      <c r="O219" s="103"/>
-      <c r="P219" s="103"/>
-      <c r="Q219" s="105" t="s">
+      <c r="K219" s="73"/>
+      <c r="L219" s="73"/>
+      <c r="M219" s="74"/>
+      <c r="N219" s="74"/>
+      <c r="O219" s="74"/>
+      <c r="P219" s="74"/>
+      <c r="Q219" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R219" s="106"/>
+      <c r="R219" s="77"/>
       <c r="S219" s="25">
         <v>0.76</v>
       </c>
@@ -20014,16 +21005,16 @@
       </c>
     </row>
     <row r="220" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K220" s="102"/>
-      <c r="L220" s="102"/>
-      <c r="M220" s="103"/>
-      <c r="N220" s="103"/>
-      <c r="O220" s="103"/>
-      <c r="P220" s="103"/>
-      <c r="Q220" s="104" t="s">
+      <c r="K220" s="73"/>
+      <c r="L220" s="73"/>
+      <c r="M220" s="74"/>
+      <c r="N220" s="74"/>
+      <c r="O220" s="74"/>
+      <c r="P220" s="74"/>
+      <c r="Q220" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R220" s="104"/>
+      <c r="R220" s="75"/>
       <c r="S220" s="24">
         <v>0.82</v>
       </c>
@@ -20032,16 +21023,16 @@
       </c>
     </row>
     <row r="221" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K221" s="102"/>
-      <c r="L221" s="102"/>
-      <c r="M221" s="103"/>
-      <c r="N221" s="103"/>
-      <c r="O221" s="103"/>
-      <c r="P221" s="103"/>
-      <c r="Q221" s="107" t="s">
+      <c r="K221" s="73"/>
+      <c r="L221" s="73"/>
+      <c r="M221" s="74"/>
+      <c r="N221" s="74"/>
+      <c r="O221" s="74"/>
+      <c r="P221" s="74"/>
+      <c r="Q221" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R221" s="107"/>
+      <c r="R221" s="78"/>
       <c r="S221" s="16">
         <v>0.64</v>
       </c>
@@ -20050,16 +21041,16 @@
       </c>
     </row>
     <row r="222" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K222" s="102"/>
-      <c r="L222" s="102"/>
-      <c r="M222" s="103"/>
-      <c r="N222" s="103"/>
-      <c r="O222" s="103"/>
-      <c r="P222" s="103"/>
-      <c r="Q222" s="104" t="s">
+      <c r="K222" s="73"/>
+      <c r="L222" s="73"/>
+      <c r="M222" s="74"/>
+      <c r="N222" s="74"/>
+      <c r="O222" s="74"/>
+      <c r="P222" s="74"/>
+      <c r="Q222" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R222" s="104"/>
+      <c r="R222" s="75"/>
       <c r="S222" s="15">
         <v>0.78</v>
       </c>
@@ -20068,20 +21059,20 @@
       </c>
     </row>
     <row r="223" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K223" s="102" t="s">
+      <c r="K223" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="L223" s="102"/>
-      <c r="M223" s="103" t="s">
+      <c r="L223" s="73"/>
+      <c r="M223" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="N223" s="103"/>
-      <c r="O223" s="103"/>
-      <c r="P223" s="103"/>
-      <c r="Q223" s="104" t="s">
+      <c r="N223" s="74"/>
+      <c r="O223" s="74"/>
+      <c r="P223" s="74"/>
+      <c r="Q223" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R223" s="104"/>
+      <c r="R223" s="75"/>
       <c r="S223" s="23">
         <v>0.73</v>
       </c>
@@ -20090,16 +21081,16 @@
       </c>
     </row>
     <row r="224" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K224" s="102"/>
-      <c r="L224" s="102"/>
-      <c r="M224" s="103"/>
-      <c r="N224" s="103"/>
-      <c r="O224" s="103"/>
-      <c r="P224" s="103"/>
-      <c r="Q224" s="105" t="s">
+      <c r="K224" s="73"/>
+      <c r="L224" s="73"/>
+      <c r="M224" s="74"/>
+      <c r="N224" s="74"/>
+      <c r="O224" s="74"/>
+      <c r="P224" s="74"/>
+      <c r="Q224" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R224" s="106"/>
+      <c r="R224" s="77"/>
       <c r="S224" s="16">
         <v>0.75</v>
       </c>
@@ -20108,16 +21099,16 @@
       </c>
     </row>
     <row r="225" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K225" s="102"/>
-      <c r="L225" s="102"/>
-      <c r="M225" s="103"/>
-      <c r="N225" s="103"/>
-      <c r="O225" s="103"/>
-      <c r="P225" s="103"/>
-      <c r="Q225" s="104" t="s">
+      <c r="K225" s="73"/>
+      <c r="L225" s="73"/>
+      <c r="M225" s="74"/>
+      <c r="N225" s="74"/>
+      <c r="O225" s="74"/>
+      <c r="P225" s="74"/>
+      <c r="Q225" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R225" s="104"/>
+      <c r="R225" s="75"/>
       <c r="S225" s="15">
         <v>0.82</v>
       </c>
@@ -20126,16 +21117,16 @@
       </c>
     </row>
     <row r="226" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K226" s="102"/>
-      <c r="L226" s="102"/>
-      <c r="M226" s="103"/>
-      <c r="N226" s="103"/>
-      <c r="O226" s="103"/>
-      <c r="P226" s="103"/>
-      <c r="Q226" s="107" t="s">
+      <c r="K226" s="73"/>
+      <c r="L226" s="73"/>
+      <c r="M226" s="74"/>
+      <c r="N226" s="74"/>
+      <c r="O226" s="74"/>
+      <c r="P226" s="74"/>
+      <c r="Q226" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R226" s="107"/>
+      <c r="R226" s="78"/>
       <c r="S226" s="16">
         <v>0.64</v>
       </c>
@@ -20144,16 +21135,16 @@
       </c>
     </row>
     <row r="227" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K227" s="102"/>
-      <c r="L227" s="102"/>
-      <c r="M227" s="103"/>
-      <c r="N227" s="103"/>
-      <c r="O227" s="103"/>
-      <c r="P227" s="103"/>
-      <c r="Q227" s="104" t="s">
+      <c r="K227" s="73"/>
+      <c r="L227" s="73"/>
+      <c r="M227" s="74"/>
+      <c r="N227" s="74"/>
+      <c r="O227" s="74"/>
+      <c r="P227" s="74"/>
+      <c r="Q227" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R227" s="104"/>
+      <c r="R227" s="75"/>
       <c r="S227" s="15">
         <v>0.78</v>
       </c>
@@ -20162,20 +21153,20 @@
       </c>
     </row>
     <row r="228" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K228" s="102" t="s">
+      <c r="K228" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="L228" s="102"/>
-      <c r="M228" s="103" t="s">
+      <c r="L228" s="73"/>
+      <c r="M228" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="N228" s="103"/>
-      <c r="O228" s="103"/>
-      <c r="P228" s="103"/>
-      <c r="Q228" s="104" t="s">
+      <c r="N228" s="74"/>
+      <c r="O228" s="74"/>
+      <c r="P228" s="74"/>
+      <c r="Q228" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R228" s="104"/>
+      <c r="R228" s="75"/>
       <c r="S228" s="15" t="s">
         <v>76</v>
       </c>
@@ -20184,16 +21175,16 @@
       </c>
     </row>
     <row r="229" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K229" s="102"/>
-      <c r="L229" s="102"/>
-      <c r="M229" s="103"/>
-      <c r="N229" s="103"/>
-      <c r="O229" s="103"/>
-      <c r="P229" s="103"/>
-      <c r="Q229" s="105" t="s">
+      <c r="K229" s="73"/>
+      <c r="L229" s="73"/>
+      <c r="M229" s="74"/>
+      <c r="N229" s="74"/>
+      <c r="O229" s="74"/>
+      <c r="P229" s="74"/>
+      <c r="Q229" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R229" s="106"/>
+      <c r="R229" s="77"/>
       <c r="S229" s="16" t="s">
         <v>53</v>
       </c>
@@ -20202,16 +21193,16 @@
       </c>
     </row>
     <row r="230" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K230" s="102"/>
-      <c r="L230" s="102"/>
-      <c r="M230" s="103"/>
-      <c r="N230" s="103"/>
-      <c r="O230" s="103"/>
-      <c r="P230" s="103"/>
-      <c r="Q230" s="104" t="s">
+      <c r="K230" s="73"/>
+      <c r="L230" s="73"/>
+      <c r="M230" s="74"/>
+      <c r="N230" s="74"/>
+      <c r="O230" s="74"/>
+      <c r="P230" s="74"/>
+      <c r="Q230" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R230" s="104"/>
+      <c r="R230" s="75"/>
       <c r="S230" s="15" t="s">
         <v>76</v>
       </c>
@@ -20220,16 +21211,16 @@
       </c>
     </row>
     <row r="231" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K231" s="102"/>
-      <c r="L231" s="102"/>
-      <c r="M231" s="103"/>
-      <c r="N231" s="103"/>
-      <c r="O231" s="103"/>
-      <c r="P231" s="103"/>
-      <c r="Q231" s="107" t="s">
+      <c r="K231" s="73"/>
+      <c r="L231" s="73"/>
+      <c r="M231" s="74"/>
+      <c r="N231" s="74"/>
+      <c r="O231" s="74"/>
+      <c r="P231" s="74"/>
+      <c r="Q231" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R231" s="107"/>
+      <c r="R231" s="78"/>
       <c r="S231" s="16" t="s">
         <v>79</v>
       </c>
@@ -20238,16 +21229,16 @@
       </c>
     </row>
     <row r="232" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K232" s="102"/>
-      <c r="L232" s="102"/>
-      <c r="M232" s="103"/>
-      <c r="N232" s="103"/>
-      <c r="O232" s="103"/>
-      <c r="P232" s="103"/>
-      <c r="Q232" s="104" t="s">
+      <c r="K232" s="73"/>
+      <c r="L232" s="73"/>
+      <c r="M232" s="74"/>
+      <c r="N232" s="74"/>
+      <c r="O232" s="74"/>
+      <c r="P232" s="74"/>
+      <c r="Q232" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R232" s="104"/>
+      <c r="R232" s="75"/>
       <c r="S232" s="15" t="s">
         <v>59</v>
       </c>
@@ -20256,20 +21247,20 @@
       </c>
     </row>
     <row r="233" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K233" s="102" t="s">
+      <c r="K233" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="L233" s="102"/>
-      <c r="M233" s="103" t="s">
+      <c r="L233" s="73"/>
+      <c r="M233" s="74" t="s">
         <v>99</v>
       </c>
-      <c r="N233" s="103"/>
-      <c r="O233" s="103"/>
-      <c r="P233" s="103"/>
-      <c r="Q233" s="104" t="s">
+      <c r="N233" s="74"/>
+      <c r="O233" s="74"/>
+      <c r="P233" s="74"/>
+      <c r="Q233" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R233" s="104"/>
+      <c r="R233" s="75"/>
       <c r="S233" s="28">
         <v>0.83</v>
       </c>
@@ -20278,16 +21269,16 @@
       </c>
     </row>
     <row r="234" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K234" s="102"/>
-      <c r="L234" s="102"/>
-      <c r="M234" s="103"/>
-      <c r="N234" s="103"/>
-      <c r="O234" s="103"/>
-      <c r="P234" s="103"/>
-      <c r="Q234" s="105" t="s">
+      <c r="K234" s="73"/>
+      <c r="L234" s="73"/>
+      <c r="M234" s="74"/>
+      <c r="N234" s="74"/>
+      <c r="O234" s="74"/>
+      <c r="P234" s="74"/>
+      <c r="Q234" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R234" s="106"/>
+      <c r="R234" s="77"/>
       <c r="S234" s="25">
         <v>0.83</v>
       </c>
@@ -20296,16 +21287,16 @@
       </c>
     </row>
     <row r="235" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K235" s="102"/>
-      <c r="L235" s="102"/>
-      <c r="M235" s="103"/>
-      <c r="N235" s="103"/>
-      <c r="O235" s="103"/>
-      <c r="P235" s="103"/>
-      <c r="Q235" s="104" t="s">
+      <c r="K235" s="73"/>
+      <c r="L235" s="73"/>
+      <c r="M235" s="74"/>
+      <c r="N235" s="74"/>
+      <c r="O235" s="74"/>
+      <c r="P235" s="74"/>
+      <c r="Q235" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R235" s="104"/>
+      <c r="R235" s="75"/>
       <c r="S235" s="24">
         <v>0.84</v>
       </c>
@@ -20314,16 +21305,16 @@
       </c>
     </row>
     <row r="236" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K236" s="102"/>
-      <c r="L236" s="102"/>
-      <c r="M236" s="103"/>
-      <c r="N236" s="103"/>
-      <c r="O236" s="103"/>
-      <c r="P236" s="103"/>
-      <c r="Q236" s="107" t="s">
+      <c r="K236" s="73"/>
+      <c r="L236" s="73"/>
+      <c r="M236" s="74"/>
+      <c r="N236" s="74"/>
+      <c r="O236" s="74"/>
+      <c r="P236" s="74"/>
+      <c r="Q236" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R236" s="107"/>
+      <c r="R236" s="78"/>
       <c r="S236" s="25">
         <v>0.74</v>
       </c>
@@ -20332,16 +21323,16 @@
       </c>
     </row>
     <row r="237" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K237" s="102"/>
-      <c r="L237" s="102"/>
-      <c r="M237" s="103"/>
-      <c r="N237" s="103"/>
-      <c r="O237" s="103"/>
-      <c r="P237" s="103"/>
-      <c r="Q237" s="104" t="s">
+      <c r="K237" s="73"/>
+      <c r="L237" s="73"/>
+      <c r="M237" s="74"/>
+      <c r="N237" s="74"/>
+      <c r="O237" s="74"/>
+      <c r="P237" s="74"/>
+      <c r="Q237" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R237" s="104"/>
+      <c r="R237" s="75"/>
       <c r="S237" s="24">
         <v>0.83</v>
       </c>
@@ -20350,20 +21341,20 @@
       </c>
     </row>
     <row r="238" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K238" s="102" t="s">
+      <c r="K238" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="L238" s="102"/>
-      <c r="M238" s="103" t="s">
+      <c r="L238" s="73"/>
+      <c r="M238" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="N238" s="103"/>
-      <c r="O238" s="103"/>
-      <c r="P238" s="103"/>
-      <c r="Q238" s="104" t="s">
+      <c r="N238" s="74"/>
+      <c r="O238" s="74"/>
+      <c r="P238" s="74"/>
+      <c r="Q238" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R238" s="104"/>
+      <c r="R238" s="75"/>
       <c r="S238" s="23">
         <v>0.87</v>
       </c>
@@ -20372,16 +21363,16 @@
       </c>
     </row>
     <row r="239" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K239" s="102"/>
-      <c r="L239" s="102"/>
-      <c r="M239" s="103"/>
-      <c r="N239" s="103"/>
-      <c r="O239" s="103"/>
-      <c r="P239" s="103"/>
-      <c r="Q239" s="105" t="s">
+      <c r="K239" s="73"/>
+      <c r="L239" s="73"/>
+      <c r="M239" s="74"/>
+      <c r="N239" s="74"/>
+      <c r="O239" s="74"/>
+      <c r="P239" s="74"/>
+      <c r="Q239" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R239" s="106"/>
+      <c r="R239" s="77"/>
       <c r="S239" s="16">
         <v>0.85</v>
       </c>
@@ -20390,16 +21381,16 @@
       </c>
     </row>
     <row r="240" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K240" s="102"/>
-      <c r="L240" s="102"/>
-      <c r="M240" s="103"/>
-      <c r="N240" s="103"/>
-      <c r="O240" s="103"/>
-      <c r="P240" s="103"/>
-      <c r="Q240" s="104" t="s">
+      <c r="K240" s="73"/>
+      <c r="L240" s="73"/>
+      <c r="M240" s="74"/>
+      <c r="N240" s="74"/>
+      <c r="O240" s="74"/>
+      <c r="P240" s="74"/>
+      <c r="Q240" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R240" s="104"/>
+      <c r="R240" s="75"/>
       <c r="S240" s="15">
         <v>0.89</v>
       </c>
@@ -20408,16 +21399,16 @@
       </c>
     </row>
     <row r="241" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K241" s="102"/>
-      <c r="L241" s="102"/>
-      <c r="M241" s="103"/>
-      <c r="N241" s="103"/>
-      <c r="O241" s="103"/>
-      <c r="P241" s="103"/>
-      <c r="Q241" s="107" t="s">
+      <c r="K241" s="73"/>
+      <c r="L241" s="73"/>
+      <c r="M241" s="74"/>
+      <c r="N241" s="74"/>
+      <c r="O241" s="74"/>
+      <c r="P241" s="74"/>
+      <c r="Q241" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R241" s="107"/>
+      <c r="R241" s="78"/>
       <c r="S241" s="16">
         <v>0.76</v>
       </c>
@@ -20426,16 +21417,16 @@
       </c>
     </row>
     <row r="242" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K242" s="102"/>
-      <c r="L242" s="102"/>
-      <c r="M242" s="103"/>
-      <c r="N242" s="103"/>
-      <c r="O242" s="103"/>
-      <c r="P242" s="103"/>
-      <c r="Q242" s="104" t="s">
+      <c r="K242" s="73"/>
+      <c r="L242" s="73"/>
+      <c r="M242" s="74"/>
+      <c r="N242" s="74"/>
+      <c r="O242" s="74"/>
+      <c r="P242" s="74"/>
+      <c r="Q242" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R242" s="104"/>
+      <c r="R242" s="75"/>
       <c r="S242" s="15">
         <v>0.87</v>
       </c>
@@ -20444,20 +21435,20 @@
       </c>
     </row>
     <row r="243" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K243" s="102" t="s">
+      <c r="K243" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="L243" s="102"/>
-      <c r="M243" s="103" t="s">
+      <c r="L243" s="73"/>
+      <c r="M243" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="N243" s="103"/>
-      <c r="O243" s="103"/>
-      <c r="P243" s="103"/>
-      <c r="Q243" s="104" t="s">
+      <c r="N243" s="74"/>
+      <c r="O243" s="74"/>
+      <c r="P243" s="74"/>
+      <c r="Q243" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R243" s="104"/>
+      <c r="R243" s="75"/>
       <c r="S243" s="15">
         <v>0.87</v>
       </c>
@@ -20466,16 +21457,16 @@
       </c>
     </row>
     <row r="244" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K244" s="102"/>
-      <c r="L244" s="102"/>
-      <c r="M244" s="103"/>
-      <c r="N244" s="103"/>
-      <c r="O244" s="103"/>
-      <c r="P244" s="103"/>
-      <c r="Q244" s="105" t="s">
+      <c r="K244" s="73"/>
+      <c r="L244" s="73"/>
+      <c r="M244" s="74"/>
+      <c r="N244" s="74"/>
+      <c r="O244" s="74"/>
+      <c r="P244" s="74"/>
+      <c r="Q244" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R244" s="106"/>
+      <c r="R244" s="77"/>
       <c r="S244" s="16">
         <v>0.85</v>
       </c>
@@ -20484,16 +21475,16 @@
       </c>
     </row>
     <row r="245" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K245" s="102"/>
-      <c r="L245" s="102"/>
-      <c r="M245" s="103"/>
-      <c r="N245" s="103"/>
-      <c r="O245" s="103"/>
-      <c r="P245" s="103"/>
-      <c r="Q245" s="104" t="s">
+      <c r="K245" s="73"/>
+      <c r="L245" s="73"/>
+      <c r="M245" s="74"/>
+      <c r="N245" s="74"/>
+      <c r="O245" s="74"/>
+      <c r="P245" s="74"/>
+      <c r="Q245" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R245" s="104"/>
+      <c r="R245" s="75"/>
       <c r="S245" s="15">
         <v>0.89</v>
       </c>
@@ -20502,16 +21493,16 @@
       </c>
     </row>
     <row r="246" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K246" s="102"/>
-      <c r="L246" s="102"/>
-      <c r="M246" s="103"/>
-      <c r="N246" s="103"/>
-      <c r="O246" s="103"/>
-      <c r="P246" s="103"/>
-      <c r="Q246" s="107" t="s">
+      <c r="K246" s="73"/>
+      <c r="L246" s="73"/>
+      <c r="M246" s="74"/>
+      <c r="N246" s="74"/>
+      <c r="O246" s="74"/>
+      <c r="P246" s="74"/>
+      <c r="Q246" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R246" s="107"/>
+      <c r="R246" s="78"/>
       <c r="S246" s="16">
         <v>0.76</v>
       </c>
@@ -20520,16 +21511,16 @@
       </c>
     </row>
     <row r="247" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K247" s="102"/>
-      <c r="L247" s="102"/>
-      <c r="M247" s="103"/>
-      <c r="N247" s="103"/>
-      <c r="O247" s="103"/>
-      <c r="P247" s="103"/>
-      <c r="Q247" s="104" t="s">
+      <c r="K247" s="73"/>
+      <c r="L247" s="73"/>
+      <c r="M247" s="74"/>
+      <c r="N247" s="74"/>
+      <c r="O247" s="74"/>
+      <c r="P247" s="74"/>
+      <c r="Q247" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R247" s="104"/>
+      <c r="R247" s="75"/>
       <c r="S247" s="15">
         <v>0.87</v>
       </c>
@@ -20538,20 +21529,20 @@
       </c>
     </row>
     <row r="248" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K248" s="102" t="s">
+      <c r="K248" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="L248" s="102"/>
-      <c r="M248" s="103" t="s">
+      <c r="L248" s="73"/>
+      <c r="M248" s="74" t="s">
         <v>102</v>
       </c>
-      <c r="N248" s="103"/>
-      <c r="O248" s="103"/>
-      <c r="P248" s="103"/>
-      <c r="Q248" s="104" t="s">
+      <c r="N248" s="74"/>
+      <c r="O248" s="74"/>
+      <c r="P248" s="74"/>
+      <c r="Q248" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="R248" s="104"/>
+      <c r="R248" s="75"/>
       <c r="S248" s="30">
         <v>0.96</v>
       </c>
@@ -20560,16 +21551,16 @@
       </c>
     </row>
     <row r="249" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K249" s="102"/>
-      <c r="L249" s="102"/>
-      <c r="M249" s="103"/>
-      <c r="N249" s="103"/>
-      <c r="O249" s="103"/>
-      <c r="P249" s="103"/>
-      <c r="Q249" s="105" t="s">
+      <c r="K249" s="73"/>
+      <c r="L249" s="73"/>
+      <c r="M249" s="74"/>
+      <c r="N249" s="74"/>
+      <c r="O249" s="74"/>
+      <c r="P249" s="74"/>
+      <c r="Q249" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="R249" s="106"/>
+      <c r="R249" s="77"/>
       <c r="S249" s="25">
         <v>0.85</v>
       </c>
@@ -20578,16 +21569,16 @@
       </c>
     </row>
     <row r="250" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K250" s="102"/>
-      <c r="L250" s="102"/>
-      <c r="M250" s="103"/>
-      <c r="N250" s="103"/>
-      <c r="O250" s="103"/>
-      <c r="P250" s="103"/>
-      <c r="Q250" s="104" t="s">
+      <c r="K250" s="73"/>
+      <c r="L250" s="73"/>
+      <c r="M250" s="74"/>
+      <c r="N250" s="74"/>
+      <c r="O250" s="74"/>
+      <c r="P250" s="74"/>
+      <c r="Q250" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="R250" s="104"/>
+      <c r="R250" s="75"/>
       <c r="S250" s="24">
         <v>0.84</v>
       </c>
@@ -20596,16 +21587,16 @@
       </c>
     </row>
     <row r="251" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K251" s="102"/>
-      <c r="L251" s="102"/>
-      <c r="M251" s="103"/>
-      <c r="N251" s="103"/>
-      <c r="O251" s="103"/>
-      <c r="P251" s="103"/>
-      <c r="Q251" s="107" t="s">
+      <c r="K251" s="73"/>
+      <c r="L251" s="73"/>
+      <c r="M251" s="74"/>
+      <c r="N251" s="74"/>
+      <c r="O251" s="74"/>
+      <c r="P251" s="74"/>
+      <c r="Q251" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="R251" s="107"/>
+      <c r="R251" s="78"/>
       <c r="S251" s="25">
         <v>0.71</v>
       </c>
@@ -20614,16 +21605,16 @@
       </c>
     </row>
     <row r="252" spans="11:20" x14ac:dyDescent="0.35">
-      <c r="K252" s="102"/>
-      <c r="L252" s="102"/>
-      <c r="M252" s="103"/>
-      <c r="N252" s="103"/>
-      <c r="O252" s="103"/>
-      <c r="P252" s="103"/>
-      <c r="Q252" s="104" t="s">
+      <c r="K252" s="73"/>
+      <c r="L252" s="73"/>
+      <c r="M252" s="74"/>
+      <c r="N252" s="74"/>
+      <c r="O252" s="74"/>
+      <c r="P252" s="74"/>
+      <c r="Q252" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="R252" s="104"/>
+      <c r="R252" s="75"/>
       <c r="S252" s="24" t="s">
         <v>37</v>
       </c>
@@ -20633,22 +21624,22 @@
     </row>
     <row r="262" spans="28:36" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="263" spans="28:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AC263" s="85" t="s">
+      <c r="AC263" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="AD263" s="86"/>
-      <c r="AE263" s="87" t="s">
+      <c r="AD263" s="108"/>
+      <c r="AE263" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="AF263" s="86"/>
-      <c r="AG263" s="87" t="s">
+      <c r="AF263" s="108"/>
+      <c r="AG263" s="109" t="s">
         <v>111</v>
       </c>
-      <c r="AH263" s="86"/>
-      <c r="AI263" s="87" t="s">
+      <c r="AH263" s="108"/>
+      <c r="AI263" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AJ263" s="86"/>
+      <c r="AJ263" s="108"/>
     </row>
     <row r="264" spans="28:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="AC264" s="37" t="s">
@@ -20736,10 +21727,10 @@
     </row>
     <row r="269" spans="28:36" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="270" spans="28:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AF270" s="87" t="s">
+      <c r="AF270" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AG270" s="86"/>
+      <c r="AG270" s="108"/>
     </row>
     <row r="271" spans="28:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="AF271" s="37" t="s">
@@ -20782,53 +21773,53 @@
       <c r="AM275" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="AN275" s="88" t="s">
+      <c r="AN275" s="100" t="s">
         <v>109</v>
       </c>
-      <c r="AO275" s="89"/>
-      <c r="AP275" s="89"/>
-      <c r="AQ275" s="89"/>
-      <c r="AR275" s="89"/>
-      <c r="AS275" s="89"/>
-      <c r="AT275" s="89"/>
-      <c r="AU275" s="90"/>
+      <c r="AO275" s="101"/>
+      <c r="AP275" s="101"/>
+      <c r="AQ275" s="101"/>
+      <c r="AR275" s="101"/>
+      <c r="AS275" s="101"/>
+      <c r="AT275" s="101"/>
+      <c r="AU275" s="102"/>
     </row>
     <row r="276" spans="25:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AA276" s="85" t="s">
+      <c r="AA276" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="AB276" s="86"/>
-      <c r="AC276" s="87" t="s">
+      <c r="AB276" s="108"/>
+      <c r="AC276" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="AD276" s="86"/>
-      <c r="AE276" s="87" t="s">
+      <c r="AD276" s="108"/>
+      <c r="AE276" s="109" t="s">
         <v>111</v>
       </c>
-      <c r="AF276" s="86"/>
-      <c r="AG276" s="87" t="s">
+      <c r="AF276" s="108"/>
+      <c r="AG276" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AH276" s="86"/>
-      <c r="AK276" s="91"/>
-      <c r="AL276" s="91"/>
-      <c r="AM276" s="91"/>
-      <c r="AN276" s="85" t="s">
+      <c r="AH276" s="108"/>
+      <c r="AK276" s="119"/>
+      <c r="AL276" s="119"/>
+      <c r="AM276" s="119"/>
+      <c r="AN276" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="AO276" s="86"/>
-      <c r="AP276" s="87" t="s">
+      <c r="AO276" s="108"/>
+      <c r="AP276" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="AQ276" s="86"/>
-      <c r="AR276" s="87" t="s">
+      <c r="AQ276" s="108"/>
+      <c r="AR276" s="109" t="s">
         <v>111</v>
       </c>
-      <c r="AS276" s="86"/>
-      <c r="AT276" s="87" t="s">
+      <c r="AS276" s="108"/>
+      <c r="AT276" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AU276" s="86"/>
+      <c r="AU276" s="108"/>
     </row>
     <row r="277" spans="25:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="AA277" s="37" t="s">
@@ -20855,9 +21846,9 @@
       <c r="AH277" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="AK277" s="92"/>
-      <c r="AL277" s="92"/>
-      <c r="AM277" s="92"/>
+      <c r="AK277" s="120"/>
+      <c r="AL277" s="120"/>
+      <c r="AM277" s="120"/>
       <c r="AN277" s="37" t="s">
         <v>5</v>
       </c>
@@ -20911,10 +21902,10 @@
       <c r="AH278" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="AK278" s="73" t="s">
+      <c r="AK278" s="110" t="s">
         <v>66</v>
       </c>
-      <c r="AL278" s="76" t="s">
+      <c r="AL278" s="113" t="s">
         <v>122</v>
       </c>
       <c r="AM278" s="39" t="s">
@@ -20973,8 +21964,8 @@
       <c r="AH279" s="64">
         <v>0.73</v>
       </c>
-      <c r="AK279" s="74"/>
-      <c r="AL279" s="77"/>
+      <c r="AK279" s="111"/>
+      <c r="AL279" s="114"/>
       <c r="AM279" s="40" t="s">
         <v>13</v>
       </c>
@@ -21031,8 +22022,8 @@
       <c r="AH280" s="59">
         <v>0.63</v>
       </c>
-      <c r="AK280" s="74"/>
-      <c r="AL280" s="77"/>
+      <c r="AK280" s="111"/>
+      <c r="AL280" s="114"/>
       <c r="AM280" s="39" t="s">
         <v>12</v>
       </c>
@@ -21089,8 +22080,8 @@
       <c r="AH281" s="67">
         <v>0.63</v>
       </c>
-      <c r="AK281" s="74"/>
-      <c r="AL281" s="77"/>
+      <c r="AK281" s="111"/>
+      <c r="AL281" s="114"/>
       <c r="AM281" s="41" t="s">
         <v>113</v>
       </c>
@@ -21150,8 +22141,8 @@
       <c r="AH282" s="53">
         <v>0.42</v>
       </c>
-      <c r="AK282" s="74"/>
-      <c r="AL282" s="78"/>
+      <c r="AK282" s="111"/>
+      <c r="AL282" s="115"/>
       <c r="AM282" s="39" t="s">
         <v>11</v>
       </c>
@@ -21181,8 +22172,8 @@
       </c>
     </row>
     <row r="283" spans="25:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AK283" s="74"/>
-      <c r="AL283" s="76" t="s">
+      <c r="AK283" s="111"/>
+      <c r="AL283" s="113" t="s">
         <v>123</v>
       </c>
       <c r="AM283" s="39" t="s">
@@ -21214,8 +22205,8 @@
       </c>
     </row>
     <row r="284" spans="25:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AK284" s="74"/>
-      <c r="AL284" s="77"/>
+      <c r="AK284" s="111"/>
+      <c r="AL284" s="114"/>
       <c r="AM284" s="40" t="s">
         <v>13</v>
       </c>
@@ -21245,8 +22236,8 @@
       </c>
     </row>
     <row r="285" spans="25:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AK285" s="74"/>
-      <c r="AL285" s="77"/>
+      <c r="AK285" s="111"/>
+      <c r="AL285" s="114"/>
       <c r="AM285" s="39" t="s">
         <v>12</v>
       </c>
@@ -21276,8 +22267,8 @@
       </c>
     </row>
     <row r="286" spans="25:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AK286" s="74"/>
-      <c r="AL286" s="77"/>
+      <c r="AK286" s="111"/>
+      <c r="AL286" s="114"/>
       <c r="AM286" s="41" t="s">
         <v>113</v>
       </c>
@@ -21307,12 +22298,12 @@
       </c>
     </row>
     <row r="287" spans="25:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AE287" s="87" t="s">
+      <c r="AE287" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AF287" s="86"/>
-      <c r="AK287" s="74"/>
-      <c r="AL287" s="78"/>
+      <c r="AF287" s="108"/>
+      <c r="AK287" s="111"/>
+      <c r="AL287" s="115"/>
       <c r="AM287" s="39" t="s">
         <v>11</v>
       </c>
@@ -21348,8 +22339,8 @@
       <c r="AF288" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="AK288" s="74"/>
-      <c r="AL288" s="76" t="s">
+      <c r="AK288" s="111"/>
+      <c r="AL288" s="113" t="s">
         <v>124</v>
       </c>
       <c r="AM288" s="39" t="s">
@@ -21390,8 +22381,8 @@
       <c r="AF289" s="65">
         <v>0.74</v>
       </c>
-      <c r="AK289" s="74"/>
-      <c r="AL289" s="77"/>
+      <c r="AK289" s="111"/>
+      <c r="AL289" s="114"/>
       <c r="AM289" s="40" t="s">
         <v>13</v>
       </c>
@@ -21430,8 +22421,8 @@
       <c r="AF290" s="64">
         <v>0.73</v>
       </c>
-      <c r="AK290" s="74"/>
-      <c r="AL290" s="77"/>
+      <c r="AK290" s="111"/>
+      <c r="AL290" s="114"/>
       <c r="AM290" s="39" t="s">
         <v>12</v>
       </c>
@@ -21470,8 +22461,8 @@
       <c r="AF291" s="59">
         <v>0.63</v>
       </c>
-      <c r="AK291" s="74"/>
-      <c r="AL291" s="77"/>
+      <c r="AK291" s="111"/>
+      <c r="AL291" s="114"/>
       <c r="AM291" s="41" t="s">
         <v>113</v>
       </c>
@@ -21510,8 +22501,8 @@
       <c r="AF292" s="67">
         <v>0.63</v>
       </c>
-      <c r="AK292" s="74"/>
-      <c r="AL292" s="78"/>
+      <c r="AK292" s="111"/>
+      <c r="AL292" s="115"/>
       <c r="AM292" s="39" t="s">
         <v>11</v>
       </c>
@@ -21550,8 +22541,8 @@
       <c r="AF293" s="53">
         <v>0.42</v>
       </c>
-      <c r="AK293" s="74"/>
-      <c r="AL293" s="76" t="s">
+      <c r="AK293" s="111"/>
+      <c r="AL293" s="113" t="s">
         <v>125</v>
       </c>
       <c r="AM293" s="39" t="s">
@@ -21583,8 +22574,8 @@
       </c>
     </row>
     <row r="294" spans="9:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AK294" s="74"/>
-      <c r="AL294" s="77"/>
+      <c r="AK294" s="111"/>
+      <c r="AL294" s="114"/>
       <c r="AM294" s="40" t="s">
         <v>13</v>
       </c>
@@ -21614,8 +22605,8 @@
       </c>
     </row>
     <row r="295" spans="9:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AK295" s="74"/>
-      <c r="AL295" s="77"/>
+      <c r="AK295" s="111"/>
+      <c r="AL295" s="114"/>
       <c r="AM295" s="39" t="s">
         <v>12</v>
       </c>
@@ -21645,8 +22636,8 @@
       </c>
     </row>
     <row r="296" spans="9:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AK296" s="74"/>
-      <c r="AL296" s="77"/>
+      <c r="AK296" s="111"/>
+      <c r="AL296" s="114"/>
       <c r="AM296" s="41" t="s">
         <v>113</v>
       </c>
@@ -21676,8 +22667,8 @@
       </c>
     </row>
     <row r="297" spans="9:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AK297" s="74"/>
-      <c r="AL297" s="78"/>
+      <c r="AK297" s="111"/>
+      <c r="AL297" s="115"/>
       <c r="AM297" s="39" t="s">
         <v>11</v>
       </c>
@@ -21707,8 +22698,8 @@
       </c>
     </row>
     <row r="298" spans="9:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AK298" s="74"/>
-      <c r="AL298" s="93" t="s">
+      <c r="AK298" s="111"/>
+      <c r="AL298" s="121" t="s">
         <v>132</v>
       </c>
       <c r="AM298" s="47" t="s">
@@ -21740,8 +22731,8 @@
       </c>
     </row>
     <row r="299" spans="9:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AK299" s="74"/>
-      <c r="AL299" s="94"/>
+      <c r="AK299" s="111"/>
+      <c r="AL299" s="122"/>
       <c r="AM299" s="39" t="s">
         <v>13</v>
       </c>
@@ -21771,8 +22762,8 @@
       </c>
     </row>
     <row r="300" spans="9:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AK300" s="74"/>
-      <c r="AL300" s="94"/>
+      <c r="AK300" s="111"/>
+      <c r="AL300" s="122"/>
       <c r="AM300" s="47" t="s">
         <v>12</v>
       </c>
@@ -21802,8 +22793,8 @@
       </c>
     </row>
     <row r="301" spans="9:47" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AK301" s="74"/>
-      <c r="AL301" s="94"/>
+      <c r="AK301" s="111"/>
+      <c r="AL301" s="122"/>
       <c r="AM301" s="39" t="s">
         <v>113</v>
       </c>
@@ -21845,8 +22836,8 @@
       <c r="L302" t="s">
         <v>105</v>
       </c>
-      <c r="AK302" s="75"/>
-      <c r="AL302" s="95"/>
+      <c r="AK302" s="112"/>
+      <c r="AL302" s="123"/>
       <c r="AM302" s="47" t="s">
         <v>11</v>
       </c>
@@ -21900,58 +22891,58 @@
       <c r="AP341" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="AQ341" s="88" t="s">
+      <c r="AQ341" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="AR341" s="89"/>
-      <c r="AS341" s="89"/>
-      <c r="AT341" s="89"/>
-      <c r="AU341" s="89"/>
-      <c r="AV341" s="89"/>
-      <c r="AW341" s="89"/>
-      <c r="AX341" s="90"/>
+      <c r="AR341" s="101"/>
+      <c r="AS341" s="101"/>
+      <c r="AT341" s="101"/>
+      <c r="AU341" s="101"/>
+      <c r="AV341" s="101"/>
+      <c r="AW341" s="101"/>
+      <c r="AX341" s="102"/>
     </row>
     <row r="342" spans="28:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AN342" s="91"/>
-      <c r="AO342" s="91"/>
-      <c r="AP342" s="91"/>
-      <c r="AQ342" s="85" t="s">
+      <c r="AN342" s="119"/>
+      <c r="AO342" s="119"/>
+      <c r="AP342" s="119"/>
+      <c r="AQ342" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="AR342" s="86"/>
-      <c r="AS342" s="87" t="s">
+      <c r="AR342" s="108"/>
+      <c r="AS342" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="AT342" s="86"/>
-      <c r="AU342" s="87" t="s">
+      <c r="AT342" s="108"/>
+      <c r="AU342" s="109" t="s">
         <v>111</v>
       </c>
-      <c r="AV342" s="86"/>
-      <c r="AW342" s="87" t="s">
+      <c r="AV342" s="108"/>
+      <c r="AW342" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AX342" s="86"/>
+      <c r="AX342" s="108"/>
     </row>
     <row r="343" spans="28:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AC343" s="85" t="s">
+      <c r="AC343" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="AD343" s="86"/>
-      <c r="AE343" s="87" t="s">
+      <c r="AD343" s="108"/>
+      <c r="AE343" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="AF343" s="86"/>
-      <c r="AG343" s="87" t="s">
+      <c r="AF343" s="108"/>
+      <c r="AG343" s="109" t="s">
         <v>111</v>
       </c>
-      <c r="AH343" s="86"/>
-      <c r="AI343" s="87" t="s">
+      <c r="AH343" s="108"/>
+      <c r="AI343" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AJ343" s="86"/>
-      <c r="AN343" s="92"/>
-      <c r="AO343" s="92"/>
-      <c r="AP343" s="92"/>
+      <c r="AJ343" s="108"/>
+      <c r="AN343" s="120"/>
+      <c r="AO343" s="120"/>
+      <c r="AP343" s="120"/>
       <c r="AQ343" s="37" t="s">
         <v>5</v>
       </c>
@@ -22002,10 +22993,10 @@
       <c r="AJ344" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="AN344" s="73" t="s">
+      <c r="AN344" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="AO344" s="76" t="s">
+      <c r="AO344" s="113" t="s">
         <v>133</v>
       </c>
       <c r="AP344" s="39" t="s">
@@ -22064,8 +23055,8 @@
       <c r="AJ345" s="65">
         <v>0.79</v>
       </c>
-      <c r="AN345" s="74"/>
-      <c r="AO345" s="77"/>
+      <c r="AN345" s="111"/>
+      <c r="AO345" s="114"/>
       <c r="AP345" s="40" t="s">
         <v>13</v>
       </c>
@@ -22122,8 +23113,8 @@
       <c r="AJ346" s="63">
         <v>0.76</v>
       </c>
-      <c r="AN346" s="74"/>
-      <c r="AO346" s="77"/>
+      <c r="AN346" s="111"/>
+      <c r="AO346" s="114"/>
       <c r="AP346" s="39" t="s">
         <v>12</v>
       </c>
@@ -22180,8 +23171,8 @@
       <c r="AJ347" s="59">
         <v>0.75</v>
       </c>
-      <c r="AN347" s="74"/>
-      <c r="AO347" s="77"/>
+      <c r="AN347" s="111"/>
+      <c r="AO347" s="114"/>
       <c r="AP347" s="41" t="s">
         <v>113</v>
       </c>
@@ -22238,8 +23229,8 @@
       <c r="AJ348" s="60">
         <v>0.75</v>
       </c>
-      <c r="AN348" s="74"/>
-      <c r="AO348" s="78"/>
+      <c r="AN348" s="111"/>
+      <c r="AO348" s="115"/>
       <c r="AP348" s="39" t="s">
         <v>11</v>
       </c>
@@ -22296,8 +23287,8 @@
       <c r="AJ349" s="48">
         <v>0.72</v>
       </c>
-      <c r="AN349" s="74"/>
-      <c r="AO349" s="76" t="s">
+      <c r="AN349" s="111"/>
+      <c r="AO349" s="113" t="s">
         <v>134</v>
       </c>
       <c r="AP349" s="39" t="s">
@@ -22329,8 +23320,8 @@
       </c>
     </row>
     <row r="350" spans="28:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AN350" s="74"/>
-      <c r="AO350" s="77"/>
+      <c r="AN350" s="111"/>
+      <c r="AO350" s="114"/>
       <c r="AP350" s="40" t="s">
         <v>13</v>
       </c>
@@ -22360,8 +23351,8 @@
       </c>
     </row>
     <row r="351" spans="28:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AN351" s="74"/>
-      <c r="AO351" s="77"/>
+      <c r="AN351" s="111"/>
+      <c r="AO351" s="114"/>
       <c r="AP351" s="39" t="s">
         <v>12</v>
       </c>
@@ -22391,8 +23382,8 @@
       </c>
     </row>
     <row r="352" spans="28:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AN352" s="74"/>
-      <c r="AO352" s="77"/>
+      <c r="AN352" s="111"/>
+      <c r="AO352" s="114"/>
       <c r="AP352" s="41" t="s">
         <v>113</v>
       </c>
@@ -22422,8 +23413,8 @@
       </c>
     </row>
     <row r="353" spans="34:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AN353" s="74"/>
-      <c r="AO353" s="78"/>
+      <c r="AN353" s="111"/>
+      <c r="AO353" s="115"/>
       <c r="AP353" s="39" t="s">
         <v>11</v>
       </c>
@@ -22453,8 +23444,8 @@
       </c>
     </row>
     <row r="354" spans="34:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AN354" s="74"/>
-      <c r="AO354" s="76" t="s">
+      <c r="AN354" s="111"/>
+      <c r="AO354" s="113" t="s">
         <v>135</v>
       </c>
       <c r="AP354" s="39" t="s">
@@ -22486,12 +23477,12 @@
       </c>
     </row>
     <row r="355" spans="34:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AI355" s="87" t="s">
+      <c r="AI355" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AJ355" s="86"/>
-      <c r="AN355" s="74"/>
-      <c r="AO355" s="77"/>
+      <c r="AJ355" s="108"/>
+      <c r="AN355" s="111"/>
+      <c r="AO355" s="114"/>
       <c r="AP355" s="40" t="s">
         <v>13</v>
       </c>
@@ -22527,8 +23518,8 @@
       <c r="AJ356" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="AN356" s="74"/>
-      <c r="AO356" s="77"/>
+      <c r="AN356" s="111"/>
+      <c r="AO356" s="114"/>
       <c r="AP356" s="39" t="s">
         <v>12</v>
       </c>
@@ -22567,8 +23558,8 @@
       <c r="AJ357" s="65">
         <v>0.79</v>
       </c>
-      <c r="AN357" s="74"/>
-      <c r="AO357" s="77"/>
+      <c r="AN357" s="111"/>
+      <c r="AO357" s="114"/>
       <c r="AP357" s="41" t="s">
         <v>113</v>
       </c>
@@ -22607,8 +23598,8 @@
       <c r="AJ358" s="63">
         <v>0.76</v>
       </c>
-      <c r="AN358" s="74"/>
-      <c r="AO358" s="78"/>
+      <c r="AN358" s="111"/>
+      <c r="AO358" s="115"/>
       <c r="AP358" s="39" t="s">
         <v>11</v>
       </c>
@@ -22647,8 +23638,8 @@
       <c r="AJ359" s="59">
         <v>0.75</v>
       </c>
-      <c r="AN359" s="74"/>
-      <c r="AO359" s="76" t="s">
+      <c r="AN359" s="111"/>
+      <c r="AO359" s="113" t="s">
         <v>136</v>
       </c>
       <c r="AP359" s="39" t="s">
@@ -22689,8 +23680,8 @@
       <c r="AJ360" s="60">
         <v>0.75</v>
       </c>
-      <c r="AN360" s="74"/>
-      <c r="AO360" s="77"/>
+      <c r="AN360" s="111"/>
+      <c r="AO360" s="114"/>
       <c r="AP360" s="40" t="s">
         <v>13</v>
       </c>
@@ -22729,8 +23720,8 @@
       <c r="AJ361" s="48">
         <v>0.72</v>
       </c>
-      <c r="AN361" s="74"/>
-      <c r="AO361" s="77"/>
+      <c r="AN361" s="111"/>
+      <c r="AO361" s="114"/>
       <c r="AP361" s="39" t="s">
         <v>12</v>
       </c>
@@ -22760,8 +23751,8 @@
       </c>
     </row>
     <row r="362" spans="34:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AN362" s="74"/>
-      <c r="AO362" s="77"/>
+      <c r="AN362" s="111"/>
+      <c r="AO362" s="114"/>
       <c r="AP362" s="41" t="s">
         <v>113</v>
       </c>
@@ -22791,8 +23782,8 @@
       </c>
     </row>
     <row r="363" spans="34:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AN363" s="74"/>
-      <c r="AO363" s="78"/>
+      <c r="AN363" s="111"/>
+      <c r="AO363" s="115"/>
       <c r="AP363" s="39" t="s">
         <v>11</v>
       </c>
@@ -22822,8 +23813,8 @@
       </c>
     </row>
     <row r="364" spans="34:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AN364" s="74"/>
-      <c r="AO364" s="82" t="s">
+      <c r="AN364" s="111"/>
+      <c r="AO364" s="116" t="s">
         <v>114</v>
       </c>
       <c r="AP364" s="47" t="s">
@@ -22855,8 +23846,8 @@
       </c>
     </row>
     <row r="365" spans="34:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AN365" s="74"/>
-      <c r="AO365" s="83"/>
+      <c r="AN365" s="111"/>
+      <c r="AO365" s="117"/>
       <c r="AP365" s="39" t="s">
         <v>13</v>
       </c>
@@ -22886,8 +23877,8 @@
       </c>
     </row>
     <row r="366" spans="34:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AN366" s="74"/>
-      <c r="AO366" s="83"/>
+      <c r="AN366" s="111"/>
+      <c r="AO366" s="117"/>
       <c r="AP366" s="47" t="s">
         <v>12</v>
       </c>
@@ -22917,8 +23908,8 @@
       </c>
     </row>
     <row r="367" spans="34:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AN367" s="74"/>
-      <c r="AO367" s="83"/>
+      <c r="AN367" s="111"/>
+      <c r="AO367" s="117"/>
       <c r="AP367" s="39" t="s">
         <v>113</v>
       </c>
@@ -22948,8 +23939,8 @@
       </c>
     </row>
     <row r="368" spans="34:50" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AN368" s="75"/>
-      <c r="AO368" s="84"/>
+      <c r="AN368" s="112"/>
+      <c r="AO368" s="118"/>
       <c r="AP368" s="47" t="s">
         <v>11</v>
       </c>
@@ -22980,10 +23971,10 @@
     </row>
     <row r="374" spans="34:36" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="375" spans="34:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AI375" s="87" t="s">
+      <c r="AI375" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AJ375" s="86"/>
+      <c r="AJ375" s="108"/>
     </row>
     <row r="376" spans="34:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="AI376" s="37" t="s">
@@ -23026,58 +24017,58 @@
       <c r="AL400" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="AM400" s="88" t="s">
+      <c r="AM400" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="AN400" s="89"/>
-      <c r="AO400" s="89"/>
-      <c r="AP400" s="89"/>
-      <c r="AQ400" s="89"/>
-      <c r="AR400" s="89"/>
-      <c r="AS400" s="89"/>
-      <c r="AT400" s="90"/>
+      <c r="AN400" s="101"/>
+      <c r="AO400" s="101"/>
+      <c r="AP400" s="101"/>
+      <c r="AQ400" s="101"/>
+      <c r="AR400" s="101"/>
+      <c r="AS400" s="101"/>
+      <c r="AT400" s="102"/>
     </row>
     <row r="401" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AJ401" s="91"/>
-      <c r="AK401" s="91"/>
-      <c r="AL401" s="91"/>
-      <c r="AM401" s="85" t="s">
+      <c r="AJ401" s="119"/>
+      <c r="AK401" s="119"/>
+      <c r="AL401" s="119"/>
+      <c r="AM401" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="AN401" s="86"/>
-      <c r="AO401" s="87" t="s">
+      <c r="AN401" s="108"/>
+      <c r="AO401" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="AP401" s="86"/>
-      <c r="AQ401" s="87" t="s">
+      <c r="AP401" s="108"/>
+      <c r="AQ401" s="109" t="s">
         <v>111</v>
       </c>
-      <c r="AR401" s="86"/>
-      <c r="AS401" s="87" t="s">
+      <c r="AR401" s="108"/>
+      <c r="AS401" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AT401" s="86"/>
+      <c r="AT401" s="108"/>
     </row>
     <row r="402" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AA402" s="85" t="s">
+      <c r="AA402" s="107" t="s">
         <v>110</v>
       </c>
-      <c r="AB402" s="86"/>
-      <c r="AC402" s="87" t="s">
+      <c r="AB402" s="108"/>
+      <c r="AC402" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="AD402" s="86"/>
-      <c r="AE402" s="87" t="s">
+      <c r="AD402" s="108"/>
+      <c r="AE402" s="109" t="s">
         <v>111</v>
       </c>
-      <c r="AF402" s="86"/>
-      <c r="AG402" s="87" t="s">
+      <c r="AF402" s="108"/>
+      <c r="AG402" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AH402" s="86"/>
-      <c r="AJ402" s="92"/>
-      <c r="AK402" s="92"/>
-      <c r="AL402" s="92"/>
+      <c r="AH402" s="108"/>
+      <c r="AJ402" s="120"/>
+      <c r="AK402" s="120"/>
+      <c r="AL402" s="120"/>
       <c r="AM402" s="37" t="s">
         <v>5</v>
       </c>
@@ -23128,10 +24119,10 @@
       <c r="AH403" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="AJ403" s="73" t="s">
+      <c r="AJ403" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="AK403" s="76" t="s">
+      <c r="AK403" s="113" t="s">
         <v>133</v>
       </c>
       <c r="AL403" s="39" t="s">
@@ -23190,8 +24181,8 @@
       <c r="AH404" s="64">
         <v>0.79</v>
       </c>
-      <c r="AJ404" s="74"/>
-      <c r="AK404" s="77"/>
+      <c r="AJ404" s="111"/>
+      <c r="AK404" s="114"/>
       <c r="AL404" s="40" t="s">
         <v>13</v>
       </c>
@@ -23248,8 +24239,8 @@
       <c r="AH405" s="58">
         <v>0.78</v>
       </c>
-      <c r="AJ405" s="74"/>
-      <c r="AK405" s="77"/>
+      <c r="AJ405" s="111"/>
+      <c r="AK405" s="114"/>
       <c r="AL405" s="39" t="s">
         <v>12</v>
       </c>
@@ -23306,8 +24297,8 @@
       <c r="AH406" s="65">
         <v>0.8</v>
       </c>
-      <c r="AJ406" s="74"/>
-      <c r="AK406" s="77"/>
+      <c r="AJ406" s="111"/>
+      <c r="AK406" s="114"/>
       <c r="AL406" s="41" t="s">
         <v>113</v>
       </c>
@@ -23364,8 +24355,8 @@
       <c r="AH407" s="64">
         <v>0.79</v>
       </c>
-      <c r="AJ407" s="74"/>
-      <c r="AK407" s="78"/>
+      <c r="AJ407" s="111"/>
+      <c r="AK407" s="115"/>
       <c r="AL407" s="39" t="s">
         <v>11</v>
       </c>
@@ -23422,8 +24413,8 @@
       <c r="AH408" s="58">
         <v>0.74</v>
       </c>
-      <c r="AJ408" s="74"/>
-      <c r="AK408" s="76" t="s">
+      <c r="AJ408" s="111"/>
+      <c r="AK408" s="113" t="s">
         <v>134</v>
       </c>
       <c r="AL408" s="39" t="s">
@@ -23455,8 +24446,8 @@
       </c>
     </row>
     <row r="409" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AJ409" s="74"/>
-      <c r="AK409" s="77"/>
+      <c r="AJ409" s="111"/>
+      <c r="AK409" s="114"/>
       <c r="AL409" s="40" t="s">
         <v>13</v>
       </c>
@@ -23486,8 +24477,8 @@
       </c>
     </row>
     <row r="410" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AJ410" s="74"/>
-      <c r="AK410" s="77"/>
+      <c r="AJ410" s="111"/>
+      <c r="AK410" s="114"/>
       <c r="AL410" s="39" t="s">
         <v>12</v>
       </c>
@@ -23517,12 +24508,12 @@
       </c>
     </row>
     <row r="411" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AA411" s="87" t="s">
+      <c r="AA411" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AB411" s="86"/>
-      <c r="AJ411" s="74"/>
-      <c r="AK411" s="77"/>
+      <c r="AB411" s="108"/>
+      <c r="AJ411" s="111"/>
+      <c r="AK411" s="114"/>
       <c r="AL411" s="41" t="s">
         <v>113</v>
       </c>
@@ -23558,8 +24549,8 @@
       <c r="AB412" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="AJ412" s="74"/>
-      <c r="AK412" s="78"/>
+      <c r="AJ412" s="111"/>
+      <c r="AK412" s="115"/>
       <c r="AL412" s="39" t="s">
         <v>11</v>
       </c>
@@ -23598,8 +24589,8 @@
       <c r="AB413" s="65">
         <v>0.8</v>
       </c>
-      <c r="AJ413" s="74"/>
-      <c r="AK413" s="76" t="s">
+      <c r="AJ413" s="111"/>
+      <c r="AK413" s="113" t="s">
         <v>135</v>
       </c>
       <c r="AL413" s="39" t="s">
@@ -23640,8 +24631,8 @@
       <c r="AB414" s="64">
         <v>0.79</v>
       </c>
-      <c r="AJ414" s="74"/>
-      <c r="AK414" s="77"/>
+      <c r="AJ414" s="111"/>
+      <c r="AK414" s="114"/>
       <c r="AL414" s="40" t="s">
         <v>13</v>
       </c>
@@ -23680,8 +24671,8 @@
       <c r="AB415" s="64">
         <v>0.79</v>
       </c>
-      <c r="AJ415" s="74"/>
-      <c r="AK415" s="77"/>
+      <c r="AJ415" s="111"/>
+      <c r="AK415" s="114"/>
       <c r="AL415" s="39" t="s">
         <v>12</v>
       </c>
@@ -23720,8 +24711,8 @@
       <c r="AB416" s="58">
         <v>0.78</v>
       </c>
-      <c r="AJ416" s="74"/>
-      <c r="AK416" s="77"/>
+      <c r="AJ416" s="111"/>
+      <c r="AK416" s="114"/>
       <c r="AL416" s="41" t="s">
         <v>113</v>
       </c>
@@ -23760,8 +24751,8 @@
       <c r="AB417" s="58">
         <v>0.74</v>
       </c>
-      <c r="AJ417" s="74"/>
-      <c r="AK417" s="78"/>
+      <c r="AJ417" s="111"/>
+      <c r="AK417" s="115"/>
       <c r="AL417" s="39" t="s">
         <v>11</v>
       </c>
@@ -23791,8 +24782,8 @@
       </c>
     </row>
     <row r="418" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AJ418" s="74"/>
-      <c r="AK418" s="79" t="s">
+      <c r="AJ418" s="111"/>
+      <c r="AK418" s="124" t="s">
         <v>105</v>
       </c>
       <c r="AL418" s="39" t="s">
@@ -23824,8 +24815,8 @@
       </c>
     </row>
     <row r="419" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AJ419" s="74"/>
-      <c r="AK419" s="80"/>
+      <c r="AJ419" s="111"/>
+      <c r="AK419" s="125"/>
       <c r="AL419" s="40" t="s">
         <v>13</v>
       </c>
@@ -23855,8 +24846,8 @@
       </c>
     </row>
     <row r="420" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AJ420" s="74"/>
-      <c r="AK420" s="80"/>
+      <c r="AJ420" s="111"/>
+      <c r="AK420" s="125"/>
       <c r="AL420" s="39" t="s">
         <v>12</v>
       </c>
@@ -23886,8 +24877,8 @@
       </c>
     </row>
     <row r="421" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AJ421" s="74"/>
-      <c r="AK421" s="80"/>
+      <c r="AJ421" s="111"/>
+      <c r="AK421" s="125"/>
       <c r="AL421" s="41" t="s">
         <v>113</v>
       </c>
@@ -23917,8 +24908,8 @@
       </c>
     </row>
     <row r="422" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AJ422" s="74"/>
-      <c r="AK422" s="81"/>
+      <c r="AJ422" s="111"/>
+      <c r="AK422" s="126"/>
       <c r="AL422" s="39" t="s">
         <v>11</v>
       </c>
@@ -23948,8 +24939,8 @@
       </c>
     </row>
     <row r="423" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AJ423" s="74"/>
-      <c r="AK423" s="82" t="s">
+      <c r="AJ423" s="111"/>
+      <c r="AK423" s="116" t="s">
         <v>114</v>
       </c>
       <c r="AL423" s="47" t="s">
@@ -23981,8 +24972,8 @@
       </c>
     </row>
     <row r="424" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AJ424" s="74"/>
-      <c r="AK424" s="83"/>
+      <c r="AJ424" s="111"/>
+      <c r="AK424" s="117"/>
       <c r="AL424" s="39" t="s">
         <v>13</v>
       </c>
@@ -24012,8 +25003,8 @@
       </c>
     </row>
     <row r="425" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AJ425" s="74"/>
-      <c r="AK425" s="83"/>
+      <c r="AJ425" s="111"/>
+      <c r="AK425" s="117"/>
       <c r="AL425" s="47" t="s">
         <v>12</v>
       </c>
@@ -24043,8 +25034,8 @@
       </c>
     </row>
     <row r="426" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AJ426" s="74"/>
-      <c r="AK426" s="83"/>
+      <c r="AJ426" s="111"/>
+      <c r="AK426" s="117"/>
       <c r="AL426" s="39" t="s">
         <v>113</v>
       </c>
@@ -24074,12 +25065,12 @@
       </c>
     </row>
     <row r="427" spans="26:46" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="AA427" s="87" t="s">
+      <c r="AA427" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="AB427" s="86"/>
-      <c r="AJ427" s="75"/>
-      <c r="AK427" s="84"/>
+      <c r="AB427" s="108"/>
+      <c r="AJ427" s="112"/>
+      <c r="AK427" s="118"/>
       <c r="AL427" s="47" t="s">
         <v>11</v>
       </c>
@@ -24235,117 +25226,200 @@
     </row>
   </sheetData>
   <mergeCells count="329">
-    <mergeCell ref="K243:L247"/>
-    <mergeCell ref="M243:P247"/>
-    <mergeCell ref="Q243:R243"/>
-    <mergeCell ref="Q244:R244"/>
-    <mergeCell ref="Q245:R245"/>
-    <mergeCell ref="Q246:R246"/>
-    <mergeCell ref="Q247:R247"/>
-    <mergeCell ref="K248:L252"/>
-    <mergeCell ref="M248:P252"/>
-    <mergeCell ref="Q248:R248"/>
-    <mergeCell ref="Q249:R249"/>
-    <mergeCell ref="Q250:R250"/>
-    <mergeCell ref="Q251:R251"/>
-    <mergeCell ref="Q252:R252"/>
-    <mergeCell ref="K233:L237"/>
-    <mergeCell ref="M233:P237"/>
-    <mergeCell ref="Q233:R233"/>
-    <mergeCell ref="Q234:R234"/>
-    <mergeCell ref="Q235:R235"/>
-    <mergeCell ref="Q236:R236"/>
-    <mergeCell ref="Q237:R237"/>
-    <mergeCell ref="K238:L242"/>
-    <mergeCell ref="M238:P242"/>
-    <mergeCell ref="Q238:R238"/>
-    <mergeCell ref="Q239:R239"/>
-    <mergeCell ref="Q240:R240"/>
-    <mergeCell ref="Q241:R241"/>
-    <mergeCell ref="Q242:R242"/>
-    <mergeCell ref="K223:L227"/>
-    <mergeCell ref="M223:P227"/>
-    <mergeCell ref="Q223:R223"/>
-    <mergeCell ref="Q224:R224"/>
-    <mergeCell ref="Q225:R225"/>
-    <mergeCell ref="Q226:R226"/>
-    <mergeCell ref="Q227:R227"/>
-    <mergeCell ref="K228:L232"/>
-    <mergeCell ref="M228:P232"/>
-    <mergeCell ref="Q228:R228"/>
-    <mergeCell ref="Q229:R229"/>
-    <mergeCell ref="Q230:R230"/>
-    <mergeCell ref="Q231:R231"/>
-    <mergeCell ref="Q232:R232"/>
-    <mergeCell ref="K213:L217"/>
-    <mergeCell ref="M213:P217"/>
-    <mergeCell ref="Q213:R213"/>
-    <mergeCell ref="Q214:R214"/>
-    <mergeCell ref="Q215:R215"/>
-    <mergeCell ref="Q216:R216"/>
-    <mergeCell ref="Q217:R217"/>
-    <mergeCell ref="K218:L222"/>
-    <mergeCell ref="M218:P222"/>
-    <mergeCell ref="Q218:R218"/>
-    <mergeCell ref="Q219:R219"/>
-    <mergeCell ref="Q220:R220"/>
-    <mergeCell ref="Q221:R221"/>
-    <mergeCell ref="Q222:R222"/>
-    <mergeCell ref="K203:L207"/>
-    <mergeCell ref="M203:P207"/>
-    <mergeCell ref="Q203:R203"/>
-    <mergeCell ref="Q204:R204"/>
-    <mergeCell ref="Q205:R205"/>
-    <mergeCell ref="Q206:R206"/>
-    <mergeCell ref="Q207:R207"/>
-    <mergeCell ref="K208:L212"/>
-    <mergeCell ref="M208:P212"/>
-    <mergeCell ref="Q208:R208"/>
-    <mergeCell ref="Q209:R209"/>
-    <mergeCell ref="Q210:R210"/>
-    <mergeCell ref="Q211:R211"/>
-    <mergeCell ref="Q212:R212"/>
-    <mergeCell ref="K193:L197"/>
-    <mergeCell ref="M193:P197"/>
-    <mergeCell ref="Q193:R193"/>
-    <mergeCell ref="Q194:R194"/>
-    <mergeCell ref="Q195:R195"/>
-    <mergeCell ref="Q196:R196"/>
-    <mergeCell ref="Q197:R197"/>
-    <mergeCell ref="K198:L202"/>
-    <mergeCell ref="M198:P202"/>
-    <mergeCell ref="Q198:R198"/>
-    <mergeCell ref="Q199:R199"/>
-    <mergeCell ref="Q200:R200"/>
-    <mergeCell ref="Q201:R201"/>
-    <mergeCell ref="Q202:R202"/>
-    <mergeCell ref="K183:L187"/>
-    <mergeCell ref="M183:P187"/>
-    <mergeCell ref="Q183:R183"/>
-    <mergeCell ref="Q184:R184"/>
-    <mergeCell ref="Q185:R185"/>
-    <mergeCell ref="Q186:R186"/>
-    <mergeCell ref="Q187:R187"/>
-    <mergeCell ref="K188:L192"/>
-    <mergeCell ref="M188:P192"/>
-    <mergeCell ref="Q188:R188"/>
-    <mergeCell ref="Q189:R189"/>
-    <mergeCell ref="Q190:R190"/>
-    <mergeCell ref="Q191:R191"/>
-    <mergeCell ref="Q192:R192"/>
-    <mergeCell ref="M173:P177"/>
-    <mergeCell ref="Q173:R173"/>
-    <mergeCell ref="Q174:R174"/>
-    <mergeCell ref="Q175:R175"/>
-    <mergeCell ref="Q176:R176"/>
-    <mergeCell ref="Q177:R177"/>
-    <mergeCell ref="K178:L182"/>
-    <mergeCell ref="M178:P182"/>
-    <mergeCell ref="Q178:R178"/>
-    <mergeCell ref="Q179:R179"/>
-    <mergeCell ref="Q180:R180"/>
-    <mergeCell ref="Q181:R181"/>
-    <mergeCell ref="Q182:R182"/>
+    <mergeCell ref="AJ403:AJ427"/>
+    <mergeCell ref="AK403:AK407"/>
+    <mergeCell ref="AK408:AK412"/>
+    <mergeCell ref="AK413:AK417"/>
+    <mergeCell ref="AK418:AK422"/>
+    <mergeCell ref="AK423:AK427"/>
+    <mergeCell ref="AA402:AB402"/>
+    <mergeCell ref="AC402:AD402"/>
+    <mergeCell ref="AE402:AF402"/>
+    <mergeCell ref="AG402:AH402"/>
+    <mergeCell ref="AA411:AB411"/>
+    <mergeCell ref="AA427:AB427"/>
+    <mergeCell ref="AI375:AJ375"/>
+    <mergeCell ref="AM400:AT400"/>
+    <mergeCell ref="AJ401:AJ402"/>
+    <mergeCell ref="AK401:AK402"/>
+    <mergeCell ref="AL401:AL402"/>
+    <mergeCell ref="AM401:AN401"/>
+    <mergeCell ref="AO401:AP401"/>
+    <mergeCell ref="AQ401:AR401"/>
+    <mergeCell ref="AS401:AT401"/>
+    <mergeCell ref="AN344:AN368"/>
+    <mergeCell ref="AO344:AO348"/>
+    <mergeCell ref="AO349:AO353"/>
+    <mergeCell ref="AO354:AO358"/>
+    <mergeCell ref="AO359:AO363"/>
+    <mergeCell ref="AO364:AO368"/>
+    <mergeCell ref="AC343:AD343"/>
+    <mergeCell ref="AE343:AF343"/>
+    <mergeCell ref="AG343:AH343"/>
+    <mergeCell ref="AI343:AJ343"/>
+    <mergeCell ref="AI355:AJ355"/>
+    <mergeCell ref="AE287:AF287"/>
+    <mergeCell ref="AC263:AD263"/>
+    <mergeCell ref="AE263:AF263"/>
+    <mergeCell ref="AG263:AH263"/>
+    <mergeCell ref="AI263:AJ263"/>
+    <mergeCell ref="AF270:AG270"/>
+    <mergeCell ref="AQ341:AX341"/>
+    <mergeCell ref="AN342:AN343"/>
+    <mergeCell ref="AO342:AO343"/>
+    <mergeCell ref="AP342:AP343"/>
+    <mergeCell ref="AQ342:AR342"/>
+    <mergeCell ref="AS342:AT342"/>
+    <mergeCell ref="AU342:AV342"/>
+    <mergeCell ref="AW342:AX342"/>
+    <mergeCell ref="AK278:AK302"/>
+    <mergeCell ref="AL278:AL282"/>
+    <mergeCell ref="AL283:AL287"/>
+    <mergeCell ref="AL288:AL292"/>
+    <mergeCell ref="AL293:AL297"/>
+    <mergeCell ref="AL298:AL302"/>
+    <mergeCell ref="AN275:AU275"/>
+    <mergeCell ref="AK276:AK277"/>
+    <mergeCell ref="AL276:AL277"/>
+    <mergeCell ref="AM276:AM277"/>
+    <mergeCell ref="AT276:AU276"/>
+    <mergeCell ref="AA276:AB276"/>
+    <mergeCell ref="AC276:AD276"/>
+    <mergeCell ref="AE276:AF276"/>
+    <mergeCell ref="AG276:AH276"/>
+    <mergeCell ref="X139:Y139"/>
+    <mergeCell ref="Z139:AA139"/>
+    <mergeCell ref="AB139:AC139"/>
+    <mergeCell ref="AD139:AE139"/>
+    <mergeCell ref="X148:Y148"/>
+    <mergeCell ref="Z148:AA148"/>
+    <mergeCell ref="AB148:AC148"/>
+    <mergeCell ref="AD148:AE148"/>
+    <mergeCell ref="X156:Y156"/>
+    <mergeCell ref="AG135:AG159"/>
+    <mergeCell ref="AH135:AH139"/>
+    <mergeCell ref="AH140:AH144"/>
+    <mergeCell ref="AH145:AH149"/>
+    <mergeCell ref="AH150:AH154"/>
+    <mergeCell ref="AH155:AH159"/>
+    <mergeCell ref="AN276:AO276"/>
+    <mergeCell ref="AP276:AQ276"/>
+    <mergeCell ref="AR276:AS276"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="AJ132:AQ132"/>
+    <mergeCell ref="AG133:AG134"/>
+    <mergeCell ref="AH133:AH134"/>
+    <mergeCell ref="AI133:AI134"/>
+    <mergeCell ref="AJ133:AK133"/>
+    <mergeCell ref="AL133:AM133"/>
+    <mergeCell ref="AN133:AO133"/>
+    <mergeCell ref="AP133:AQ133"/>
+    <mergeCell ref="K82:L82"/>
+    <mergeCell ref="D68:D87"/>
+    <mergeCell ref="E68:F72"/>
+    <mergeCell ref="G68:J72"/>
+    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="K71:L71"/>
+    <mergeCell ref="K72:L72"/>
+    <mergeCell ref="E73:F77"/>
+    <mergeCell ref="G73:J77"/>
+    <mergeCell ref="K73:L73"/>
+    <mergeCell ref="K74:L74"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="K77:L77"/>
+    <mergeCell ref="E78:F82"/>
+    <mergeCell ref="E83:F87"/>
+    <mergeCell ref="G83:J87"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="G78:J82"/>
+    <mergeCell ref="K84:L84"/>
+    <mergeCell ref="K85:L85"/>
+    <mergeCell ref="G38:J42"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="K66:L66"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="D48:D67"/>
+    <mergeCell ref="E48:F52"/>
+    <mergeCell ref="G48:J52"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="E53:F57"/>
+    <mergeCell ref="G53:J57"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="E58:F62"/>
+    <mergeCell ref="E63:F67"/>
+    <mergeCell ref="G63:J67"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="G58:J62"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="K59:L59"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="D28:D47"/>
+    <mergeCell ref="E28:F32"/>
+    <mergeCell ref="G28:J32"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="E33:F37"/>
+    <mergeCell ref="G33:J37"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="E38:F42"/>
+    <mergeCell ref="E43:F47"/>
+    <mergeCell ref="G43:J47"/>
+    <mergeCell ref="D2:T2"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="E6:F7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D3:T4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K6:L7"/>
+    <mergeCell ref="G6:J7"/>
+    <mergeCell ref="M5:T5"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="S6:T6"/>
     <mergeCell ref="D8:D27"/>
     <mergeCell ref="E13:F17"/>
     <mergeCell ref="G13:J17"/>
@@ -24370,203 +25444,203 @@
     <mergeCell ref="K14:L14"/>
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="K16:L16"/>
-    <mergeCell ref="D2:T2"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="E6:F7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D3:T4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L7"/>
-    <mergeCell ref="G6:J7"/>
-    <mergeCell ref="M5:T5"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="D28:D47"/>
-    <mergeCell ref="E28:F32"/>
-    <mergeCell ref="G28:J32"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="E33:F37"/>
-    <mergeCell ref="G33:J37"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="E38:F42"/>
-    <mergeCell ref="E43:F47"/>
-    <mergeCell ref="G43:J47"/>
-    <mergeCell ref="D48:D67"/>
-    <mergeCell ref="E48:F52"/>
-    <mergeCell ref="G48:J52"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="E53:F57"/>
-    <mergeCell ref="G53:J57"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="E58:F62"/>
-    <mergeCell ref="E63:F67"/>
-    <mergeCell ref="G63:J67"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="G58:J62"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="K59:L59"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="G38:J42"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="K66:L66"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="K79:L79"/>
-    <mergeCell ref="K80:L80"/>
-    <mergeCell ref="K81:L81"/>
-    <mergeCell ref="K82:L82"/>
-    <mergeCell ref="D68:D87"/>
-    <mergeCell ref="E68:F72"/>
-    <mergeCell ref="G68:J72"/>
-    <mergeCell ref="K68:L68"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="K70:L70"/>
-    <mergeCell ref="K71:L71"/>
-    <mergeCell ref="K72:L72"/>
-    <mergeCell ref="E73:F77"/>
-    <mergeCell ref="G73:J77"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="K74:L74"/>
-    <mergeCell ref="K75:L75"/>
-    <mergeCell ref="K76:L76"/>
-    <mergeCell ref="K77:L77"/>
-    <mergeCell ref="E78:F82"/>
-    <mergeCell ref="E83:F87"/>
-    <mergeCell ref="G83:J87"/>
-    <mergeCell ref="K83:L83"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="G78:J82"/>
-    <mergeCell ref="K84:L84"/>
-    <mergeCell ref="K85:L85"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="AJ132:AQ132"/>
-    <mergeCell ref="AG133:AG134"/>
-    <mergeCell ref="AH133:AH134"/>
-    <mergeCell ref="AI133:AI134"/>
-    <mergeCell ref="AJ133:AK133"/>
-    <mergeCell ref="AL133:AM133"/>
-    <mergeCell ref="AN133:AO133"/>
-    <mergeCell ref="AP133:AQ133"/>
-    <mergeCell ref="AG135:AG159"/>
-    <mergeCell ref="AH135:AH139"/>
-    <mergeCell ref="AH140:AH144"/>
-    <mergeCell ref="AH145:AH149"/>
-    <mergeCell ref="AH150:AH154"/>
-    <mergeCell ref="AH155:AH159"/>
-    <mergeCell ref="AN276:AO276"/>
-    <mergeCell ref="AP276:AQ276"/>
-    <mergeCell ref="AR276:AS276"/>
-    <mergeCell ref="AT276:AU276"/>
-    <mergeCell ref="AA276:AB276"/>
-    <mergeCell ref="AC276:AD276"/>
-    <mergeCell ref="AE276:AF276"/>
-    <mergeCell ref="AG276:AH276"/>
-    <mergeCell ref="X139:Y139"/>
-    <mergeCell ref="Z139:AA139"/>
-    <mergeCell ref="AB139:AC139"/>
-    <mergeCell ref="AD139:AE139"/>
-    <mergeCell ref="X148:Y148"/>
-    <mergeCell ref="Z148:AA148"/>
-    <mergeCell ref="AB148:AC148"/>
-    <mergeCell ref="AD148:AE148"/>
-    <mergeCell ref="X156:Y156"/>
-    <mergeCell ref="AE287:AF287"/>
-    <mergeCell ref="AC263:AD263"/>
-    <mergeCell ref="AE263:AF263"/>
-    <mergeCell ref="AG263:AH263"/>
-    <mergeCell ref="AI263:AJ263"/>
-    <mergeCell ref="AF270:AG270"/>
-    <mergeCell ref="AQ341:AX341"/>
-    <mergeCell ref="AN342:AN343"/>
-    <mergeCell ref="AO342:AO343"/>
-    <mergeCell ref="AP342:AP343"/>
-    <mergeCell ref="AQ342:AR342"/>
-    <mergeCell ref="AS342:AT342"/>
-    <mergeCell ref="AU342:AV342"/>
-    <mergeCell ref="AW342:AX342"/>
-    <mergeCell ref="AK278:AK302"/>
-    <mergeCell ref="AL278:AL282"/>
-    <mergeCell ref="AL283:AL287"/>
-    <mergeCell ref="AL288:AL292"/>
-    <mergeCell ref="AL293:AL297"/>
-    <mergeCell ref="AL298:AL302"/>
-    <mergeCell ref="AN275:AU275"/>
-    <mergeCell ref="AK276:AK277"/>
-    <mergeCell ref="AL276:AL277"/>
-    <mergeCell ref="AM276:AM277"/>
-    <mergeCell ref="AN344:AN368"/>
-    <mergeCell ref="AO344:AO348"/>
-    <mergeCell ref="AO349:AO353"/>
-    <mergeCell ref="AO354:AO358"/>
-    <mergeCell ref="AO359:AO363"/>
-    <mergeCell ref="AO364:AO368"/>
-    <mergeCell ref="AC343:AD343"/>
-    <mergeCell ref="AE343:AF343"/>
-    <mergeCell ref="AG343:AH343"/>
-    <mergeCell ref="AI343:AJ343"/>
-    <mergeCell ref="AI355:AJ355"/>
-    <mergeCell ref="AI375:AJ375"/>
-    <mergeCell ref="AM400:AT400"/>
-    <mergeCell ref="AJ401:AJ402"/>
-    <mergeCell ref="AK401:AK402"/>
-    <mergeCell ref="AL401:AL402"/>
-    <mergeCell ref="AM401:AN401"/>
-    <mergeCell ref="AO401:AP401"/>
-    <mergeCell ref="AQ401:AR401"/>
-    <mergeCell ref="AS401:AT401"/>
-    <mergeCell ref="AJ403:AJ427"/>
-    <mergeCell ref="AK403:AK407"/>
-    <mergeCell ref="AK408:AK412"/>
-    <mergeCell ref="AK413:AK417"/>
-    <mergeCell ref="AK418:AK422"/>
-    <mergeCell ref="AK423:AK427"/>
-    <mergeCell ref="AA402:AB402"/>
-    <mergeCell ref="AC402:AD402"/>
-    <mergeCell ref="AE402:AF402"/>
-    <mergeCell ref="AG402:AH402"/>
-    <mergeCell ref="AA411:AB411"/>
-    <mergeCell ref="AA427:AB427"/>
+    <mergeCell ref="M173:P177"/>
+    <mergeCell ref="Q173:R173"/>
+    <mergeCell ref="Q174:R174"/>
+    <mergeCell ref="Q175:R175"/>
+    <mergeCell ref="Q176:R176"/>
+    <mergeCell ref="Q177:R177"/>
+    <mergeCell ref="K178:L182"/>
+    <mergeCell ref="M178:P182"/>
+    <mergeCell ref="Q178:R178"/>
+    <mergeCell ref="Q179:R179"/>
+    <mergeCell ref="Q180:R180"/>
+    <mergeCell ref="Q181:R181"/>
+    <mergeCell ref="Q182:R182"/>
+    <mergeCell ref="K183:L187"/>
+    <mergeCell ref="M183:P187"/>
+    <mergeCell ref="Q183:R183"/>
+    <mergeCell ref="Q184:R184"/>
+    <mergeCell ref="Q185:R185"/>
+    <mergeCell ref="Q186:R186"/>
+    <mergeCell ref="Q187:R187"/>
+    <mergeCell ref="K188:L192"/>
+    <mergeCell ref="M188:P192"/>
+    <mergeCell ref="Q188:R188"/>
+    <mergeCell ref="Q189:R189"/>
+    <mergeCell ref="Q190:R190"/>
+    <mergeCell ref="Q191:R191"/>
+    <mergeCell ref="Q192:R192"/>
+    <mergeCell ref="K193:L197"/>
+    <mergeCell ref="M193:P197"/>
+    <mergeCell ref="Q193:R193"/>
+    <mergeCell ref="Q194:R194"/>
+    <mergeCell ref="Q195:R195"/>
+    <mergeCell ref="Q196:R196"/>
+    <mergeCell ref="Q197:R197"/>
+    <mergeCell ref="K198:L202"/>
+    <mergeCell ref="M198:P202"/>
+    <mergeCell ref="Q198:R198"/>
+    <mergeCell ref="Q199:R199"/>
+    <mergeCell ref="Q200:R200"/>
+    <mergeCell ref="Q201:R201"/>
+    <mergeCell ref="Q202:R202"/>
+    <mergeCell ref="K203:L207"/>
+    <mergeCell ref="M203:P207"/>
+    <mergeCell ref="Q203:R203"/>
+    <mergeCell ref="Q204:R204"/>
+    <mergeCell ref="Q205:R205"/>
+    <mergeCell ref="Q206:R206"/>
+    <mergeCell ref="Q207:R207"/>
+    <mergeCell ref="K208:L212"/>
+    <mergeCell ref="M208:P212"/>
+    <mergeCell ref="Q208:R208"/>
+    <mergeCell ref="Q209:R209"/>
+    <mergeCell ref="Q210:R210"/>
+    <mergeCell ref="Q211:R211"/>
+    <mergeCell ref="Q212:R212"/>
+    <mergeCell ref="K213:L217"/>
+    <mergeCell ref="M213:P217"/>
+    <mergeCell ref="Q213:R213"/>
+    <mergeCell ref="Q214:R214"/>
+    <mergeCell ref="Q215:R215"/>
+    <mergeCell ref="Q216:R216"/>
+    <mergeCell ref="Q217:R217"/>
+    <mergeCell ref="K218:L222"/>
+    <mergeCell ref="M218:P222"/>
+    <mergeCell ref="Q218:R218"/>
+    <mergeCell ref="Q219:R219"/>
+    <mergeCell ref="Q220:R220"/>
+    <mergeCell ref="Q221:R221"/>
+    <mergeCell ref="Q222:R222"/>
+    <mergeCell ref="K223:L227"/>
+    <mergeCell ref="M223:P227"/>
+    <mergeCell ref="Q223:R223"/>
+    <mergeCell ref="Q224:R224"/>
+    <mergeCell ref="Q225:R225"/>
+    <mergeCell ref="Q226:R226"/>
+    <mergeCell ref="Q227:R227"/>
+    <mergeCell ref="K228:L232"/>
+    <mergeCell ref="M228:P232"/>
+    <mergeCell ref="Q228:R228"/>
+    <mergeCell ref="Q229:R229"/>
+    <mergeCell ref="Q230:R230"/>
+    <mergeCell ref="Q231:R231"/>
+    <mergeCell ref="Q232:R232"/>
+    <mergeCell ref="K233:L237"/>
+    <mergeCell ref="M233:P237"/>
+    <mergeCell ref="Q233:R233"/>
+    <mergeCell ref="Q234:R234"/>
+    <mergeCell ref="Q235:R235"/>
+    <mergeCell ref="Q236:R236"/>
+    <mergeCell ref="Q237:R237"/>
+    <mergeCell ref="K238:L242"/>
+    <mergeCell ref="M238:P242"/>
+    <mergeCell ref="Q238:R238"/>
+    <mergeCell ref="Q239:R239"/>
+    <mergeCell ref="Q240:R240"/>
+    <mergeCell ref="Q241:R241"/>
+    <mergeCell ref="Q242:R242"/>
+    <mergeCell ref="K243:L247"/>
+    <mergeCell ref="M243:P247"/>
+    <mergeCell ref="Q243:R243"/>
+    <mergeCell ref="Q244:R244"/>
+    <mergeCell ref="Q245:R245"/>
+    <mergeCell ref="Q246:R246"/>
+    <mergeCell ref="Q247:R247"/>
+    <mergeCell ref="K248:L252"/>
+    <mergeCell ref="M248:P252"/>
+    <mergeCell ref="Q248:R248"/>
+    <mergeCell ref="Q249:R249"/>
+    <mergeCell ref="Q250:R250"/>
+    <mergeCell ref="Q251:R251"/>
+    <mergeCell ref="Q252:R252"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="O16:Q23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="17" spans="15:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P17" s="109" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="108"/>
+    </row>
+    <row r="18" spans="15:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P18" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="15:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O19" t="s">
+        <v>145</v>
+      </c>
+      <c r="P19" s="59">
+        <v>0.83</v>
+      </c>
+      <c r="Q19" s="65">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="20" spans="15:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O20" t="s">
+        <v>142</v>
+      </c>
+      <c r="P20" s="63">
+        <v>0.85</v>
+      </c>
+      <c r="Q20" s="64">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="21" spans="15:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O21" t="s">
+        <v>144</v>
+      </c>
+      <c r="P21" s="63">
+        <v>0.85</v>
+      </c>
+      <c r="Q21" s="64">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="22" spans="15:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O22" t="s">
+        <v>143</v>
+      </c>
+      <c r="P22" s="58">
+        <v>0.8</v>
+      </c>
+      <c r="Q22" s="58">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="23" spans="15:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O23" t="s">
+        <v>146</v>
+      </c>
+      <c r="P23" s="58">
+        <v>0.8</v>
+      </c>
+      <c r="Q23" s="58">
+        <v>0.74</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="P17:Q17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>